--- a/Database.xlsx
+++ b/Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/Documents/Proyecto GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0E34FB-28CF-4142-9AEA-8E2727C0F282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8C21CE-46FB-6D49-A329-4597BD46019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" firstSheet="1" activeTab="8" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="35" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="iPad - Air M4" sheetId="33" r:id="rId6"/>
     <sheet name="iPad - Pro M5" sheetId="32" r:id="rId7"/>
     <sheet name="iPad - Pencil &amp; Keyboard" sheetId="43" r:id="rId8"/>
-    <sheet name="iPhone - Duo" sheetId="48" r:id="rId9"/>
+    <sheet name="iPhone - ⚠️ Duo" sheetId="48" r:id="rId9"/>
     <sheet name="iPhone - 18 Pro Max" sheetId="44" r:id="rId10"/>
     <sheet name="iPhone - 18 Pro" sheetId="45" r:id="rId11"/>
     <sheet name="iPhone - 17 Pro Max" sheetId="41" r:id="rId12"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7183" uniqueCount="5510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7186" uniqueCount="5511">
   <si>
     <t>Accesories</t>
   </si>
@@ -16568,9 +16568,6 @@
     <t>946.114.04487</t>
   </si>
   <si>
-    <t>18 Duo (eSIM)</t>
-  </si>
-  <si>
     <t>Air (eSIM)</t>
   </si>
   <si>
@@ -16599,6 +16596,12 @@
   </si>
   <si>
     <t>BetterRoaming</t>
+  </si>
+  <si>
+    <t>MW2K3AA/A</t>
+  </si>
+  <si>
+    <t>Duo (eSIM) ⚠️ Reservas 16.10 - 14:00 / Disponible 23.10 ⚠️</t>
   </si>
 </sst>
 </file>
@@ -19572,7 +19575,7 @@
         <v>1191</v>
       </c>
       <c r="B13" s="298" t="s">
-        <v>1192</v>
+        <v>5509</v>
       </c>
       <c r="C13" s="298" t="s">
         <v>3752</v>
@@ -19813,7 +19816,7 @@
         <v>1191</v>
       </c>
       <c r="B31" s="298" t="s">
-        <v>1192</v>
+        <v>5509</v>
       </c>
       <c r="C31" s="298" t="s">
         <v>3752</v>
@@ -20068,7 +20071,7 @@
         <v>1191</v>
       </c>
       <c r="B50" s="298" t="s">
-        <v>1192</v>
+        <v>5509</v>
       </c>
       <c r="C50" s="298" t="s">
         <v>3752</v>
@@ -23315,7 +23318,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5500</v>
+        <v>5499</v>
       </c>
       <c r="B1" s="74" t="s">
         <v>76</v>
@@ -30184,7 +30187,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5507</v>
+        <v>5506</v>
       </c>
       <c r="B1" s="74"/>
       <c r="C1" s="72"/>
@@ -30192,7 +30195,7 @@
     </row>
     <row r="2" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="483" t="s">
-        <v>5501</v>
+        <v>5500</v>
       </c>
       <c r="B2" s="483"/>
       <c r="C2" s="483"/>
@@ -30200,7 +30203,7 @@
     </row>
     <row r="3" spans="1:4" s="486" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="485" t="s">
-        <v>5502</v>
+        <v>5501</v>
       </c>
       <c r="B3" s="485"/>
       <c r="C3" s="485"/>
@@ -30208,7 +30211,7 @@
     </row>
     <row r="4" spans="1:4" s="488" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="487" t="s">
-        <v>5503</v>
+        <v>5502</v>
       </c>
       <c r="B4" s="487"/>
       <c r="C4" s="487"/>
@@ -30216,7 +30219,7 @@
     </row>
     <row r="5" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
-        <v>5504</v>
+        <v>5503</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -30224,7 +30227,7 @@
     </row>
     <row r="6" spans="1:4" s="490" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="489" t="s">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="B6" s="489"/>
       <c r="C6" s="489"/>
@@ -30232,7 +30235,7 @@
     </row>
     <row r="7" spans="1:4" s="492" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="491" t="s">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="B7" s="491"/>
       <c r="C7" s="491"/>
@@ -30241,7 +30244,7 @@
     <row r="8" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>5508</v>
+        <v>5507</v>
       </c>
       <c r="B9" s="74"/>
       <c r="C9" s="72"/>
@@ -30249,7 +30252,7 @@
     </row>
     <row r="10" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="483" t="s">
-        <v>5501</v>
+        <v>5500</v>
       </c>
       <c r="B10" s="483"/>
       <c r="C10" s="483"/>
@@ -30257,7 +30260,7 @@
     </row>
     <row r="11" spans="1:4" s="99" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="98" t="s">
-        <v>5509</v>
+        <v>5508</v>
       </c>
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
@@ -30729,7 +30732,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAB60F4-ACDD-BA4C-8806-670692225F6F}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
@@ -30829,7 +30832,7 @@
         <v>1191</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>1192</v>
+        <v>5509</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>3752</v>
@@ -30840,1008 +30843,1019 @@
     </row>
     <row r="9" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
-        <v>3834</v>
+        <v>1191</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>3837</v>
+        <v>1192</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>3836</v>
-      </c>
-      <c r="D9" s="294" t="s">
-        <v>3835</v>
+        <v>3752</v>
+      </c>
+      <c r="D9" s="294">
+        <v>195949376566</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
-        <v>6</v>
+        <v>3834</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>3351</v>
+        <v>3837</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>3352</v>
+        <v>3836</v>
       </c>
       <c r="D10" s="294" t="s">
-        <v>3353</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>3799</v>
+        <v>3351</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>39</v>
+        <v>3352</v>
       </c>
       <c r="D11" s="294" t="s">
-        <v>3750</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>3801</v>
+        <v>3799</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D12" s="294" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="294" t="s">
+        <v>3751</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B14" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C14" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="294" t="s">
+      <c r="D14" s="294" t="s">
         <v>3749</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="294"/>
-    </row>
-    <row r="15" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
+    <row r="15" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="294"/>
+    </row>
+    <row r="16" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="72" t="s">
         <v>1193</v>
       </c>
-      <c r="B15" s="74" t="s">
+      <c r="B16" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="264" t="s">
+      <c r="C16" s="75"/>
+      <c r="D16" s="264" t="s">
         <v>1998</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D16" s="294"/>
     </row>
     <row r="17" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>1197</v>
-      </c>
+        <v>1194</v>
+      </c>
+      <c r="B17" s="56"/>
       <c r="C17" s="56" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D17" s="294"/>
     </row>
     <row r="18" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
-        <v>148</v>
+        <v>1196</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>149</v>
+        <v>1197</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="D18" s="294">
-        <v>195950084658</v>
-      </c>
+        <v>1198</v>
+      </c>
+      <c r="D18" s="294"/>
     </row>
     <row r="19" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56" t="s">
-        <v>2507</v>
+        <v>148</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>2511</v>
+        <v>149</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>2513</v>
-      </c>
-      <c r="D19" s="294" t="s">
-        <v>2509</v>
+        <v>154</v>
+      </c>
+      <c r="D19" s="294">
+        <v>195950084658</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>2511</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D20" s="294" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
         <v>2508</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B21" s="56" t="s">
         <v>2512</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C21" s="56" t="s">
         <v>2514</v>
       </c>
-      <c r="D20" s="294" t="s">
+      <c r="D21" s="294" t="s">
         <v>2510</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="56"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="294"/>
-    </row>
-    <row r="22" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72" t="s">
+    <row r="22" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="294"/>
+    </row>
+    <row r="23" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="72" t="s">
         <v>1199</v>
       </c>
-      <c r="B22" s="74" t="s">
+      <c r="B23" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="264" t="s">
+      <c r="C23" s="75"/>
+      <c r="D23" s="264" t="s">
         <v>1998</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="56" t="s">
-        <v>1200</v>
-      </c>
-      <c r="B23" s="56" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C23" s="56" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D23" s="294"/>
     </row>
     <row r="24" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="D24" s="294"/>
     </row>
     <row r="25" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B25" s="56" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C25" s="56" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D25" s="294"/>
+    </row>
+    <row r="26" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="56" t="s">
         <v>1206</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B26" s="56" t="s">
         <v>1207</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C26" s="56" t="s">
         <v>1208</v>
       </c>
-      <c r="D25" s="294"/>
-    </row>
-    <row r="26" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="56"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
       <c r="D26" s="294"/>
     </row>
     <row r="27" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="56" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B27" s="56" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C27" s="56" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D27" s="294">
-        <v>195949085611</v>
-      </c>
+      <c r="A27" s="56"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="294"/>
     </row>
     <row r="28" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D28" s="294">
+        <v>195949085611</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
         <v>1212</v>
       </c>
-      <c r="B28" s="56" t="s">
+      <c r="B29" s="56" t="s">
         <v>1213</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C29" s="56" t="s">
         <v>1214</v>
       </c>
-      <c r="D28" s="294">
+      <c r="D29" s="294">
         <v>190198496201</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="56"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="294"/>
-    </row>
     <row r="30" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="56" t="s">
-        <v>1215</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>1217</v>
-      </c>
+      <c r="A30" s="56"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="294"/>
     </row>
     <row r="31" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="D31" s="294"/>
     </row>
     <row r="32" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="56" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B32" s="56" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D32" s="294"/>
+    </row>
+    <row r="33" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="56" t="s">
         <v>1221</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B33" s="56" t="s">
         <v>1222</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C33" s="56" t="s">
         <v>1223</v>
       </c>
-      <c r="D32" s="294"/>
-    </row>
-    <row r="33" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="56"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
       <c r="D33" s="294"/>
     </row>
     <row r="34" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="56" t="s">
-        <v>3859</v>
-      </c>
-      <c r="B34" s="56" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>1225</v>
-      </c>
+      <c r="A34" s="56"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
       <c r="D34" s="294"/>
     </row>
     <row r="35" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="56" t="s">
+        <v>3859</v>
+      </c>
+      <c r="B35" s="56" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D35" s="294"/>
+    </row>
+    <row r="36" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56" t="s">
         <v>3860</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56" t="s">
+      <c r="B36" s="56"/>
+      <c r="C36" s="56" t="s">
         <v>1226</v>
       </c>
-      <c r="D35" s="294"/>
-    </row>
-    <row r="36" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D36" s="294"/>
     </row>
     <row r="37" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="72" t="s">
+      <c r="D37" s="294"/>
+    </row>
+    <row r="38" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="72" t="s">
         <v>1227</v>
       </c>
-      <c r="B37" s="74" t="s">
+      <c r="B38" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="264" t="s">
+      <c r="C38" s="75"/>
+      <c r="D38" s="264" t="s">
         <v>1998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="56" t="s">
-        <v>3806</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="D38" s="294">
-        <v>195949371905</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="56" t="s">
-        <v>1228</v>
+        <v>150</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>1229</v>
+        <v>155</v>
       </c>
       <c r="D39" s="294">
-        <v>195949775390</v>
+        <v>195949371905</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="56" t="s">
-        <v>3779</v>
+        <v>1228</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>1230</v>
+        <v>3807</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D40" s="294" t="s">
-        <v>3776</v>
+        <v>1229</v>
+      </c>
+      <c r="D40" s="294">
+        <v>195949775390</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56" t="s">
-        <v>3778</v>
+        <v>3779</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>3774</v>
+        <v>1230</v>
       </c>
       <c r="C41" s="56" t="s">
-        <v>3775</v>
+        <v>1231</v>
       </c>
       <c r="D41" s="294" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56" t="s">
-        <v>1232</v>
+        <v>3778</v>
       </c>
       <c r="B42" s="56" t="s">
-        <v>1233</v>
+        <v>3774</v>
       </c>
       <c r="C42" s="56" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D42" s="294">
-        <v>190198886866</v>
+        <v>3775</v>
+      </c>
+      <c r="D42" s="294" t="s">
+        <v>3777</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="56" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="D43" s="294">
-        <v>888462108454</v>
+        <v>190198886866</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="56" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="D44" s="294">
-        <v>195949122880</v>
+        <v>888462108454</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="56" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="C45" s="56" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="D45" s="294">
-        <v>190198914439</v>
+        <v>195949122880</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="56" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B46" s="56" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D46" s="294">
+        <v>190198914439</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="56" t="s">
         <v>1244</v>
       </c>
-      <c r="B46" s="56" t="s">
+      <c r="B47" s="56" t="s">
         <v>1245</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C47" s="56" t="s">
         <v>1246</v>
       </c>
-      <c r="D46" s="294">
+      <c r="D47" s="294">
         <v>888462075039</v>
       </c>
     </row>
-    <row r="47" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56"/>
-      <c r="B47" s="56"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="294"/>
-    </row>
     <row r="48" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="294"/>
+    </row>
+    <row r="49" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="56" t="s">
         <v>3861</v>
       </c>
-      <c r="B48" s="56" t="s">
+      <c r="B49" s="56" t="s">
         <v>1247</v>
       </c>
-      <c r="C48" s="56" t="s">
+      <c r="C49" s="56" t="s">
         <v>1248</v>
       </c>
-      <c r="D48" s="294">
+      <c r="D49" s="294">
         <v>195949102196</v>
       </c>
     </row>
-    <row r="49" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="294"/>
-    </row>
     <row r="50" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="72" t="s">
+      <c r="D50" s="294"/>
+    </row>
+    <row r="51" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="72" t="s">
         <v>1249</v>
       </c>
-      <c r="B50" s="74" t="s">
+      <c r="B51" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="264" t="s">
+      <c r="C51" s="75"/>
+      <c r="D51" s="264" t="s">
         <v>1998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="B51" s="56" t="s">
-        <v>259</v>
-      </c>
-      <c r="C51" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="D51" s="294">
-        <v>195949655999</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="B52" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="C52" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="D52" s="294">
+        <v>195949655999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="B52" s="56" t="s">
+      <c r="B53" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C53" s="56" t="s">
         <v>263</v>
       </c>
-      <c r="D52" s="294">
+      <c r="D53" s="294">
         <v>195949656118</v>
       </c>
     </row>
-    <row r="53" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="56"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="294"/>
-    </row>
     <row r="54" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="56" t="s">
-        <v>264</v>
-      </c>
-      <c r="B54" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="56" t="s">
-        <v>266</v>
-      </c>
-      <c r="D54" s="294">
-        <v>195949654404</v>
-      </c>
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="294"/>
     </row>
     <row r="55" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="56" t="s">
+        <v>264</v>
+      </c>
+      <c r="B55" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="D55" s="294">
+        <v>195949654404</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B56" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="C55" s="56" t="s">
+      <c r="C56" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="D55" s="294">
+      <c r="D56" s="294">
         <v>195949654510</v>
       </c>
     </row>
-    <row r="56" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="56"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="294"/>
-    </row>
     <row r="57" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
-        <v>270</v>
-      </c>
-      <c r="B57" s="56" t="s">
-        <v>271</v>
-      </c>
-      <c r="C57" s="56" t="s">
-        <v>272</v>
-      </c>
-      <c r="D57" s="294">
-        <v>195949634734</v>
-      </c>
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="294"/>
     </row>
     <row r="58" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C58" s="56" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D58" s="294">
-        <v>195949634048</v>
+        <v>195949634734</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="56" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B59" s="56" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C59" s="56" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D59" s="294">
-        <v>195949655173</v>
+        <v>195949634048</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="C60" s="56" t="s">
+        <v>278</v>
+      </c>
+      <c r="D60" s="294">
+        <v>195949655173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="56" t="s">
         <v>279</v>
       </c>
-      <c r="B60" s="56" t="s">
+      <c r="B61" s="56" t="s">
         <v>280</v>
       </c>
-      <c r="C60" s="56" t="s">
+      <c r="C61" s="56" t="s">
         <v>281</v>
       </c>
-      <c r="D60" s="294">
+      <c r="D61" s="294">
         <v>195949655852</v>
       </c>
     </row>
-    <row r="61" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="294"/>
-    </row>
-    <row r="62" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="72" t="s">
+    <row r="62" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D62" s="294"/>
+    </row>
+    <row r="63" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="72" t="s">
         <v>1250</v>
       </c>
-      <c r="B62" s="74" t="s">
+      <c r="B63" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="75"/>
-      <c r="D62" s="264" t="s">
+      <c r="C63" s="75"/>
+      <c r="D63" s="264" t="s">
         <v>1998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="56" t="s">
-        <v>449</v>
-      </c>
-      <c r="B63" s="56" t="s">
-        <v>450</v>
-      </c>
-      <c r="C63" s="56" t="s">
-        <v>451</v>
-      </c>
-      <c r="D63" s="294">
-        <v>194253687986</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="56" t="s">
-        <v>1251</v>
+        <v>449</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>3803</v>
+        <v>450</v>
       </c>
       <c r="C64" s="56" t="s">
-        <v>1252</v>
+        <v>451</v>
       </c>
       <c r="D64" s="294">
-        <v>195949690457</v>
+        <v>194253687986</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="56" t="s">
-        <v>146</v>
+        <v>1251</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>147</v>
+        <v>3803</v>
       </c>
       <c r="C65" s="56" t="s">
-        <v>153</v>
+        <v>1252</v>
       </c>
       <c r="D65" s="294">
-        <v>195949133695</v>
+        <v>195949690457</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="294">
+        <v>195949133695</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="56" t="s">
+      <c r="B67" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C67" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="D66" s="294">
+      <c r="D67" s="294">
         <v>195949573125</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="56"/>
-      <c r="B67" s="56"/>
-      <c r="C67" s="56"/>
-      <c r="D67" s="294"/>
-    </row>
     <row r="68" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="56" t="s">
-        <v>1253</v>
-      </c>
-      <c r="B68" s="56" t="s">
-        <v>3804</v>
-      </c>
-      <c r="C68" s="56" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D68" s="294">
-        <v>195949775468</v>
-      </c>
+      <c r="A68" s="56"/>
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="294"/>
     </row>
     <row r="69" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="56" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B69" s="56" t="s">
+        <v>3804</v>
+      </c>
+      <c r="C69" s="56" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D69" s="294">
+        <v>195949775468</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="56" t="s">
         <v>1255</v>
       </c>
-      <c r="B69" s="56" t="s">
+      <c r="B70" s="56" t="s">
         <v>3805</v>
       </c>
-      <c r="C69" s="56" t="s">
+      <c r="C70" s="56" t="s">
         <v>1256</v>
       </c>
-      <c r="D69" s="294">
+      <c r="D70" s="294">
         <v>195949442148</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="56"/>
-      <c r="B70" s="56"/>
-      <c r="C70" s="56"/>
-      <c r="D70" s="294"/>
-    </row>
     <row r="71" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="B71" s="56" t="s">
-        <v>447</v>
-      </c>
-      <c r="C71" s="56" t="s">
-        <v>448</v>
-      </c>
-      <c r="D71" s="294">
-        <v>194253417484</v>
-      </c>
+      <c r="A71" s="56"/>
+      <c r="B71" s="56"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="294"/>
     </row>
     <row r="72" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="56" t="s">
-        <v>1259</v>
+        <v>446</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>378</v>
+        <v>447</v>
       </c>
       <c r="C72" s="56" t="s">
-        <v>1260</v>
+        <v>448</v>
       </c>
       <c r="D72" s="294">
-        <v>195950262315</v>
+        <v>194253417484</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="56" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>444</v>
+        <v>378</v>
       </c>
       <c r="C73" s="56" t="s">
-        <v>445</v>
+        <v>1260</v>
       </c>
       <c r="D73" s="294">
-        <v>195950262803</v>
+        <v>195950262315</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="56" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>140</v>
+        <v>444</v>
       </c>
       <c r="C74" s="56" t="s">
-        <v>141</v>
+        <v>445</v>
       </c>
       <c r="D74" s="294">
-        <v>195949482755</v>
+        <v>195950262803</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="56" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B75" s="56" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C75" s="56" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D75" s="294">
-        <v>195949486258</v>
+        <v>195949482755</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="56" t="s">
-        <v>204</v>
+        <v>1258</v>
       </c>
       <c r="B76" s="56" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="C76" s="56" t="s">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="D76" s="294">
-        <v>195949488344</v>
+        <v>195949486258</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="B77" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C77" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="D77" s="294">
+        <v>195949488344</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="56" t="s">
         <v>207</v>
       </c>
-      <c r="B77" s="56" t="s">
+      <c r="B78" s="56" t="s">
         <v>208</v>
       </c>
-      <c r="C77" s="56" t="s">
+      <c r="C78" s="56" t="s">
         <v>209</v>
       </c>
-      <c r="D77" s="294">
+      <c r="D78" s="294">
         <v>195949491023</v>
       </c>
     </row>
-    <row r="78" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="56"/>
-      <c r="B78" s="56"/>
-      <c r="C78" s="56"/>
-      <c r="D78" s="294"/>
-    </row>
     <row r="79" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="72" t="s">
+      <c r="A79" s="56"/>
+      <c r="B79" s="56"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="294"/>
+    </row>
+    <row r="80" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="72" t="s">
         <v>1262</v>
       </c>
-      <c r="B79" s="74" t="s">
+      <c r="B80" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C79" s="75"/>
-      <c r="D79" s="264" t="s">
+      <c r="C80" s="75"/>
+      <c r="D80" s="264" t="s">
         <v>1998</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="56" t="s">
-        <v>1262</v>
-      </c>
-      <c r="B80" s="56" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C80" s="56" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D80" s="294"/>
     </row>
     <row r="81" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="56" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B81" s="56" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="C81" s="56" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="D81" s="294"/>
     </row>
     <row r="82" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="56" t="s">
-        <v>3354</v>
+        <v>1265</v>
       </c>
       <c r="B82" s="56" t="s">
-        <v>3356</v>
+        <v>1266</v>
       </c>
       <c r="C82" s="56" t="s">
-        <v>3357</v>
-      </c>
-      <c r="D82" s="294">
-        <v>195950667387</v>
-      </c>
+        <v>1267</v>
+      </c>
+      <c r="D82" s="294"/>
     </row>
     <row r="83" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="56" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B83" s="56" t="s">
-        <v>3359</v>
+        <v>3356</v>
       </c>
       <c r="C83" s="56" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="D83" s="294">
-        <v>195950667547</v>
+        <v>195950667387</v>
       </c>
     </row>
     <row r="84" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="56" t="s">
-        <v>4686</v>
+        <v>3355</v>
       </c>
       <c r="B84" s="56" t="s">
-        <v>4696</v>
+        <v>3359</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>5351</v>
-      </c>
-      <c r="D84" s="294" t="s">
-        <v>4691</v>
+        <v>3358</v>
+      </c>
+      <c r="D84" s="294">
+        <v>195950667547</v>
       </c>
     </row>
     <row r="85" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="56" t="s">
-        <v>4687</v>
+        <v>4686</v>
       </c>
       <c r="B85" s="56" t="s">
-        <v>4697</v>
+        <v>4696</v>
       </c>
       <c r="C85" s="56" t="s">
-        <v>5352</v>
+        <v>5351</v>
       </c>
       <c r="D85" s="294" t="s">
-        <v>4692</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="86" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="56" t="s">
-        <v>4688</v>
+        <v>4687</v>
       </c>
       <c r="B86" s="56" t="s">
-        <v>4698</v>
+        <v>4697</v>
       </c>
       <c r="C86" s="56" t="s">
-        <v>5353</v>
+        <v>5352</v>
       </c>
       <c r="D86" s="294" t="s">
-        <v>4693</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="87" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56" t="s">
-        <v>4689</v>
+        <v>4688</v>
       </c>
       <c r="B87" s="56" t="s">
-        <v>4699</v>
+        <v>4698</v>
       </c>
       <c r="C87" s="56" t="s">
-        <v>5354</v>
+        <v>5353</v>
       </c>
       <c r="D87" s="294" t="s">
-        <v>4694</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="88" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="56" t="s">
+        <v>4689</v>
+      </c>
+      <c r="B88" s="56" t="s">
+        <v>4699</v>
+      </c>
+      <c r="C88" s="56" t="s">
+        <v>5354</v>
+      </c>
+      <c r="D88" s="294" t="s">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="56" t="s">
         <v>4690</v>
       </c>
-      <c r="B88" s="56" t="s">
+      <c r="B89" s="56" t="s">
         <v>4700</v>
       </c>
-      <c r="C88" s="56" t="s">
+      <c r="C89" s="56" t="s">
         <v>5355</v>
       </c>
-      <c r="D88" s="294" t="s">
+      <c r="D89" s="294" t="s">
         <v>4695</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D89" s="294"/>
-    </row>
     <row r="90" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="72" t="s">
+      <c r="D90" s="294"/>
+    </row>
+    <row r="91" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="72" t="s">
         <v>1291</v>
       </c>
-      <c r="B90" s="74" t="s">
+      <c r="B91" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="75"/>
-      <c r="D90" s="264" t="s">
+      <c r="C91" s="75"/>
+      <c r="D91" s="264" t="s">
         <v>1998</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="56" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B91" s="56" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C91" s="56" t="s">
-        <v>1294</v>
-      </c>
-      <c r="D91" s="294">
-        <v>194253097655</v>
       </c>
     </row>
     <row r="92" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B92" s="56" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C92" s="56" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D92" s="294">
+        <v>194253097655</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="56" t="s">
         <v>1295</v>
       </c>
-      <c r="B92" s="56" t="s">
+      <c r="B93" s="56" t="s">
         <v>1296</v>
       </c>
-      <c r="C92" s="56" t="s">
+      <c r="C93" s="56" t="s">
         <v>1297</v>
       </c>
-      <c r="D92" s="294">
+      <c r="D93" s="294">
         <v>194253097334</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D93" s="296"/>
     </row>
     <row r="94" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D94" s="296"/>
@@ -31863,6 +31877,9 @@
     </row>
     <row r="100" spans="4:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D100" s="296"/>
+    </row>
+    <row r="101" spans="4:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D101" s="296"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -63892,7 +63909,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>5499</v>
+        <v>5510</v>
       </c>
       <c r="B1" s="83" t="s">
         <v>76</v>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/Documents/Proyecto GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8C21CE-46FB-6D49-A329-4597BD46019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E50F50B-75FB-E34A-A6A7-3D5148596CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" firstSheet="1" activeTab="8" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="35" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="iPad - Air M4" sheetId="33" r:id="rId6"/>
     <sheet name="iPad - Pro M5" sheetId="32" r:id="rId7"/>
     <sheet name="iPad - Pencil &amp; Keyboard" sheetId="43" r:id="rId8"/>
-    <sheet name="iPhone - ⚠️ Duo" sheetId="48" r:id="rId9"/>
+    <sheet name="iPhone - Duo" sheetId="48" r:id="rId9"/>
     <sheet name="iPhone - 18 Pro Max" sheetId="44" r:id="rId10"/>
     <sheet name="iPhone - 18 Pro" sheetId="45" r:id="rId11"/>
     <sheet name="iPhone - 17 Pro Max" sheetId="41" r:id="rId12"/>
@@ -16568,6 +16568,9 @@
     <t>946.114.04487</t>
   </si>
   <si>
+    <t>18 Duo (eSIM)</t>
+  </si>
+  <si>
     <t>Air (eSIM)</t>
   </si>
   <si>
@@ -16599,9 +16602,6 @@
   </si>
   <si>
     <t>MW2K3AA/A</t>
-  </si>
-  <si>
-    <t>Duo (eSIM) ⚠️ Reservas 16.10 - 14:00 / Disponible 23.10 ⚠️</t>
   </si>
 </sst>
 </file>
@@ -19575,7 +19575,7 @@
         <v>1191</v>
       </c>
       <c r="B13" s="298" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="C13" s="298" t="s">
         <v>3752</v>
@@ -19816,7 +19816,7 @@
         <v>1191</v>
       </c>
       <c r="B31" s="298" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="C31" s="298" t="s">
         <v>3752</v>
@@ -20071,7 +20071,7 @@
         <v>1191</v>
       </c>
       <c r="B50" s="298" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="C50" s="298" t="s">
         <v>3752</v>
@@ -23318,7 +23318,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5499</v>
+        <v>5500</v>
       </c>
       <c r="B1" s="74" t="s">
         <v>76</v>
@@ -30187,7 +30187,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="B1" s="74"/>
       <c r="C1" s="72"/>
@@ -30195,7 +30195,7 @@
     </row>
     <row r="2" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="483" t="s">
-        <v>5500</v>
+        <v>5501</v>
       </c>
       <c r="B2" s="483"/>
       <c r="C2" s="483"/>
@@ -30203,7 +30203,7 @@
     </row>
     <row r="3" spans="1:4" s="486" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="485" t="s">
-        <v>5501</v>
+        <v>5502</v>
       </c>
       <c r="B3" s="485"/>
       <c r="C3" s="485"/>
@@ -30211,7 +30211,7 @@
     </row>
     <row r="4" spans="1:4" s="488" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="487" t="s">
-        <v>5502</v>
+        <v>5503</v>
       </c>
       <c r="B4" s="487"/>
       <c r="C4" s="487"/>
@@ -30219,7 +30219,7 @@
     </row>
     <row r="5" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
-        <v>5503</v>
+        <v>5504</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -30227,7 +30227,7 @@
     </row>
     <row r="6" spans="1:4" s="490" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="489" t="s">
-        <v>5504</v>
+        <v>5505</v>
       </c>
       <c r="B6" s="489"/>
       <c r="C6" s="489"/>
@@ -30235,7 +30235,7 @@
     </row>
     <row r="7" spans="1:4" s="492" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="491" t="s">
-        <v>5505</v>
+        <v>5506</v>
       </c>
       <c r="B7" s="491"/>
       <c r="C7" s="491"/>
@@ -30244,7 +30244,7 @@
     <row r="8" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="B9" s="74"/>
       <c r="C9" s="72"/>
@@ -30252,7 +30252,7 @@
     </row>
     <row r="10" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="483" t="s">
-        <v>5500</v>
+        <v>5501</v>
       </c>
       <c r="B10" s="483"/>
       <c r="C10" s="483"/>
@@ -30260,7 +30260,7 @@
     </row>
     <row r="11" spans="1:4" s="99" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="98" t="s">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
@@ -30832,7 +30832,7 @@
         <v>1191</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>3752</v>
@@ -63909,7 +63909,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>5510</v>
+        <v>5499</v>
       </c>
       <c r="B1" s="83" t="s">
         <v>76</v>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/Documents/Proyecto GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E50F50B-75FB-E34A-A6A7-3D5148596CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8C21CE-46FB-6D49-A329-4597BD46019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" firstSheet="1" activeTab="8" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="35" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="iPad - Air M4" sheetId="33" r:id="rId6"/>
     <sheet name="iPad - Pro M5" sheetId="32" r:id="rId7"/>
     <sheet name="iPad - Pencil &amp; Keyboard" sheetId="43" r:id="rId8"/>
-    <sheet name="iPhone - Duo" sheetId="48" r:id="rId9"/>
+    <sheet name="iPhone - ⚠️ Duo" sheetId="48" r:id="rId9"/>
     <sheet name="iPhone - 18 Pro Max" sheetId="44" r:id="rId10"/>
     <sheet name="iPhone - 18 Pro" sheetId="45" r:id="rId11"/>
     <sheet name="iPhone - 17 Pro Max" sheetId="41" r:id="rId12"/>
@@ -16568,9 +16568,6 @@
     <t>946.114.04487</t>
   </si>
   <si>
-    <t>18 Duo (eSIM)</t>
-  </si>
-  <si>
     <t>Air (eSIM)</t>
   </si>
   <si>
@@ -16602,6 +16599,9 @@
   </si>
   <si>
     <t>MW2K3AA/A</t>
+  </si>
+  <si>
+    <t>Duo (eSIM) ⚠️ Reservas 16.10 - 14:00 / Disponible 23.10 ⚠️</t>
   </si>
 </sst>
 </file>
@@ -19575,7 +19575,7 @@
         <v>1191</v>
       </c>
       <c r="B13" s="298" t="s">
-        <v>5510</v>
+        <v>5509</v>
       </c>
       <c r="C13" s="298" t="s">
         <v>3752</v>
@@ -19816,7 +19816,7 @@
         <v>1191</v>
       </c>
       <c r="B31" s="298" t="s">
-        <v>5510</v>
+        <v>5509</v>
       </c>
       <c r="C31" s="298" t="s">
         <v>3752</v>
@@ -20071,7 +20071,7 @@
         <v>1191</v>
       </c>
       <c r="B50" s="298" t="s">
-        <v>5510</v>
+        <v>5509</v>
       </c>
       <c r="C50" s="298" t="s">
         <v>3752</v>
@@ -23318,7 +23318,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5500</v>
+        <v>5499</v>
       </c>
       <c r="B1" s="74" t="s">
         <v>76</v>
@@ -30187,7 +30187,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5507</v>
+        <v>5506</v>
       </c>
       <c r="B1" s="74"/>
       <c r="C1" s="72"/>
@@ -30195,7 +30195,7 @@
     </row>
     <row r="2" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="483" t="s">
-        <v>5501</v>
+        <v>5500</v>
       </c>
       <c r="B2" s="483"/>
       <c r="C2" s="483"/>
@@ -30203,7 +30203,7 @@
     </row>
     <row r="3" spans="1:4" s="486" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="485" t="s">
-        <v>5502</v>
+        <v>5501</v>
       </c>
       <c r="B3" s="485"/>
       <c r="C3" s="485"/>
@@ -30211,7 +30211,7 @@
     </row>
     <row r="4" spans="1:4" s="488" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="487" t="s">
-        <v>5503</v>
+        <v>5502</v>
       </c>
       <c r="B4" s="487"/>
       <c r="C4" s="487"/>
@@ -30219,7 +30219,7 @@
     </row>
     <row r="5" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
-        <v>5504</v>
+        <v>5503</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -30227,7 +30227,7 @@
     </row>
     <row r="6" spans="1:4" s="490" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="489" t="s">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="B6" s="489"/>
       <c r="C6" s="489"/>
@@ -30235,7 +30235,7 @@
     </row>
     <row r="7" spans="1:4" s="492" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="491" t="s">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="B7" s="491"/>
       <c r="C7" s="491"/>
@@ -30244,7 +30244,7 @@
     <row r="8" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>5508</v>
+        <v>5507</v>
       </c>
       <c r="B9" s="74"/>
       <c r="C9" s="72"/>
@@ -30252,7 +30252,7 @@
     </row>
     <row r="10" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="483" t="s">
-        <v>5501</v>
+        <v>5500</v>
       </c>
       <c r="B10" s="483"/>
       <c r="C10" s="483"/>
@@ -30260,7 +30260,7 @@
     </row>
     <row r="11" spans="1:4" s="99" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="98" t="s">
-        <v>5509</v>
+        <v>5508</v>
       </c>
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
@@ -30832,7 +30832,7 @@
         <v>1191</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>5510</v>
+        <v>5509</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>3752</v>
@@ -63909,7 +63909,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>5499</v>
+        <v>5510</v>
       </c>
       <c r="B1" s="83" t="s">
         <v>76</v>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/Documents/Proyecto GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8C21CE-46FB-6D49-A329-4597BD46019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD1472E-1821-A44B-A72D-A894DB34DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="22840" windowHeight="20040" firstSheet="1" activeTab="8" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16980" windowHeight="21480" firstSheet="3" activeTab="6" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="35" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7186" uniqueCount="5511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7284" uniqueCount="5621">
   <si>
     <t>Accesories</t>
   </si>
@@ -14888,21 +14888,12 @@
     <t>195951376646</t>
   </si>
   <si>
-    <t>195951376677</t>
-  </si>
-  <si>
     <t>195951376707</t>
   </si>
   <si>
-    <t>195951376738</t>
-  </si>
-  <si>
     <t>195951376769</t>
   </si>
   <si>
-    <t>195951376790</t>
-  </si>
-  <si>
     <t>195951376899</t>
   </si>
   <si>
@@ -14969,21 +14960,12 @@
     <t>MKAQ4ZM/A</t>
   </si>
   <si>
-    <t>MKAU4ZM/A</t>
-  </si>
-  <si>
     <t>MKAV4ZM/A</t>
   </si>
   <si>
-    <t>MKAX4ZM/A</t>
-  </si>
-  <si>
     <t>MKAY4ZM/A</t>
   </si>
   <si>
-    <t>MKD04ZM/A</t>
-  </si>
-  <si>
     <t>MKDW4ZM/A</t>
   </si>
   <si>
@@ -15059,21 +15041,12 @@
     <t>195951352442</t>
   </si>
   <si>
-    <t>195951352459</t>
-  </si>
-  <si>
     <t>195951352466</t>
   </si>
   <si>
-    <t>195951352473</t>
-  </si>
-  <si>
     <t>195951352480</t>
   </si>
   <si>
-    <t>195951352497</t>
-  </si>
-  <si>
     <t>MK0A4ZM/A</t>
   </si>
   <si>
@@ -15122,21 +15095,12 @@
     <t>MK7K4ZM/A</t>
   </si>
   <si>
-    <t>MK7L4ZM/A</t>
-  </si>
-  <si>
     <t>MK7M4ZM/A</t>
   </si>
   <si>
-    <t>MK7N4ZM/A</t>
-  </si>
-  <si>
     <t>MK7P4ZM/A</t>
   </si>
   <si>
-    <t>MK7Q4ZM/A</t>
-  </si>
-  <si>
     <t>40mm Burgundy Plaid Sport Loop</t>
   </si>
   <si>
@@ -15350,9 +15314,6 @@
     <t>42mm Camel Modern Buckle - Medium</t>
   </si>
   <si>
-    <t>42mm Camel Modern Buckle - L</t>
-  </si>
-  <si>
     <t>42mm Sage Modern Buckle - Small</t>
   </si>
   <si>
@@ -16475,21 +16436,12 @@
     <t>49mm Translucent Grey Ocean Band - Black Titanium</t>
   </si>
   <si>
-    <t>49mm Translucent Grey Ocean Band Extension - Black Titanium</t>
-  </si>
-  <si>
     <t>49mm Translucent Kelp Ocean Band - Black Titanium</t>
   </si>
   <si>
-    <t>49mm Translucent Kelp Ocean Band Extension - Black Titanium</t>
-  </si>
-  <si>
     <t>49mm Translucent Black Ocean Band - Black Titanium</t>
   </si>
   <si>
-    <t>49mm Translucent Black Ocean Band Extension - Black Titanium</t>
-  </si>
-  <si>
     <t>49mm Dark Olive Alpine Loop - Small - Black Titanium</t>
   </si>
   <si>
@@ -16517,21 +16469,12 @@
     <t>49mm Desert Alpine Loop - Large - Black Titanium</t>
   </si>
   <si>
-    <t>49mm Translucent Black Ocean Band Extension - Natural Titanium</t>
-  </si>
-  <si>
     <t>49mm Translucent Black Ocean Band - Natural Titanium</t>
   </si>
   <si>
-    <t>49mm Translucent Kelp Ocean Band Extension - Natural Titanium</t>
-  </si>
-  <si>
     <t>49mm Translucent Kelp Ocean Band - Natural Titanium</t>
   </si>
   <si>
-    <t>49mm Translucent Grey Ocean Band Extension - Natural Titanium</t>
-  </si>
-  <si>
     <t>49mm Translucent Grey Ocean Band - Natural Titanium</t>
   </si>
   <si>
@@ -16602,6 +16545,393 @@
   </si>
   <si>
     <t>Duo (eSIM) ⚠️ Reservas 16.10 - 14:00 / Disponible 23.10 ⚠️</t>
+  </si>
+  <si>
+    <t>946.108.14777</t>
+  </si>
+  <si>
+    <t>946.108.14785</t>
+  </si>
+  <si>
+    <t>946.108.14793</t>
+  </si>
+  <si>
+    <t>946.108.14801</t>
+  </si>
+  <si>
+    <t>946.108.14819</t>
+  </si>
+  <si>
+    <t>946.108.14827</t>
+  </si>
+  <si>
+    <t>946.108.14835</t>
+  </si>
+  <si>
+    <t>946.108.14843</t>
+  </si>
+  <si>
+    <t>946.108.14850</t>
+  </si>
+  <si>
+    <t>946.108.14868</t>
+  </si>
+  <si>
+    <t>946.108.14876</t>
+  </si>
+  <si>
+    <t>946.108.14884</t>
+  </si>
+  <si>
+    <t>946.108.14892</t>
+  </si>
+  <si>
+    <t>946.108.14900</t>
+  </si>
+  <si>
+    <t>946.108.14918</t>
+  </si>
+  <si>
+    <t>946.108.14926</t>
+  </si>
+  <si>
+    <t>946.108.14934</t>
+  </si>
+  <si>
+    <t>946.108.14942</t>
+  </si>
+  <si>
+    <t>946.108.14959</t>
+  </si>
+  <si>
+    <t>946.108.14967</t>
+  </si>
+  <si>
+    <t>946.108.14975</t>
+  </si>
+  <si>
+    <t>946.108.14983</t>
+  </si>
+  <si>
+    <t>946.108.14991</t>
+  </si>
+  <si>
+    <t>946.108.15006</t>
+  </si>
+  <si>
+    <t>946.108.15014</t>
+  </si>
+  <si>
+    <t>946.108.15022</t>
+  </si>
+  <si>
+    <t>946.108.15030</t>
+  </si>
+  <si>
+    <t>946.108.15048</t>
+  </si>
+  <si>
+    <t>946.108.15055</t>
+  </si>
+  <si>
+    <t>946.108.15063</t>
+  </si>
+  <si>
+    <t>946.108.13282</t>
+  </si>
+  <si>
+    <t>946.108.13274</t>
+  </si>
+  <si>
+    <t>946.108.13266</t>
+  </si>
+  <si>
+    <t>946.108.13316</t>
+  </si>
+  <si>
+    <t>946.108.13308</t>
+  </si>
+  <si>
+    <t>946.108.13290</t>
+  </si>
+  <si>
+    <t>946.108.13365</t>
+  </si>
+  <si>
+    <t>946.108.13373</t>
+  </si>
+  <si>
+    <t>946.108.13340</t>
+  </si>
+  <si>
+    <t>946.108.13357</t>
+  </si>
+  <si>
+    <t>946.108.13324</t>
+  </si>
+  <si>
+    <t>946.108.13332</t>
+  </si>
+  <si>
+    <t>946.108.13381</t>
+  </si>
+  <si>
+    <t>946.108.13399</t>
+  </si>
+  <si>
+    <t>946.108.13407</t>
+  </si>
+  <si>
+    <t>946.108.13423</t>
+  </si>
+  <si>
+    <t>946.201.04581</t>
+  </si>
+  <si>
+    <t>946.108.14629</t>
+  </si>
+  <si>
+    <t>946.108.14637</t>
+  </si>
+  <si>
+    <t>946.108.14645</t>
+  </si>
+  <si>
+    <t>946.108.14652</t>
+  </si>
+  <si>
+    <t>946.108.14660</t>
+  </si>
+  <si>
+    <t>946.108.14678</t>
+  </si>
+  <si>
+    <t>946.108.14686</t>
+  </si>
+  <si>
+    <t>946.108.14702</t>
+  </si>
+  <si>
+    <t>946.108.14694</t>
+  </si>
+  <si>
+    <t>946.108.14710</t>
+  </si>
+  <si>
+    <t>946.108.14728</t>
+  </si>
+  <si>
+    <t>946.108.14736</t>
+  </si>
+  <si>
+    <t>946.108.14744</t>
+  </si>
+  <si>
+    <t>946.108.14751</t>
+  </si>
+  <si>
+    <t>946.108.14769</t>
+  </si>
+  <si>
+    <t>946.108.15238</t>
+  </si>
+  <si>
+    <t>946.108.15246</t>
+  </si>
+  <si>
+    <t>946.108.15253</t>
+  </si>
+  <si>
+    <t>946.108.15261</t>
+  </si>
+  <si>
+    <t>946.108.15279</t>
+  </si>
+  <si>
+    <t>946.108.15287</t>
+  </si>
+  <si>
+    <t>946.108.15295</t>
+  </si>
+  <si>
+    <t>946.108.15303</t>
+  </si>
+  <si>
+    <t>946.108.15311</t>
+  </si>
+  <si>
+    <t>946.108.15329</t>
+  </si>
+  <si>
+    <t>946.108.15337</t>
+  </si>
+  <si>
+    <t>946.108.15345</t>
+  </si>
+  <si>
+    <t>42mm Camel Modern Buckle - Large</t>
+  </si>
+  <si>
+    <t>946.108.14355</t>
+  </si>
+  <si>
+    <t>946.108.14363</t>
+  </si>
+  <si>
+    <t>946.108.14371</t>
+  </si>
+  <si>
+    <t>946.108.14389</t>
+  </si>
+  <si>
+    <t>946.108.14397</t>
+  </si>
+  <si>
+    <t>946.108.14405</t>
+  </si>
+  <si>
+    <t>946.108.13993</t>
+  </si>
+  <si>
+    <t>946.108.14009</t>
+  </si>
+  <si>
+    <t>946.108.14017</t>
+  </si>
+  <si>
+    <t>946.108.14025</t>
+  </si>
+  <si>
+    <t>946.108.14033</t>
+  </si>
+  <si>
+    <t>946.108.14041</t>
+  </si>
+  <si>
+    <t>946.108.14058</t>
+  </si>
+  <si>
+    <t>946.108.14066</t>
+  </si>
+  <si>
+    <t>946.108.14074</t>
+  </si>
+  <si>
+    <t>946.108.14082</t>
+  </si>
+  <si>
+    <t>946.108.14108</t>
+  </si>
+  <si>
+    <t>946.108.14124</t>
+  </si>
+  <si>
+    <t>946.108.13928</t>
+  </si>
+  <si>
+    <t>946.108.13936</t>
+  </si>
+  <si>
+    <t>946.108.13944</t>
+  </si>
+  <si>
+    <t>946.108.14413</t>
+  </si>
+  <si>
+    <t>946.108.14421</t>
+  </si>
+  <si>
+    <t>946.108.14439</t>
+  </si>
+  <si>
+    <t>946.108.14447</t>
+  </si>
+  <si>
+    <t>946.108.14454</t>
+  </si>
+  <si>
+    <t>946.108.14462</t>
+  </si>
+  <si>
+    <t>946.108.14538</t>
+  </si>
+  <si>
+    <t>946.108.14546</t>
+  </si>
+  <si>
+    <t>946.108.14553</t>
+  </si>
+  <si>
+    <t>946.108.14561</t>
+  </si>
+  <si>
+    <t>946.108.14579</t>
+  </si>
+  <si>
+    <t>946.108.14587</t>
+  </si>
+  <si>
+    <t>946.108.14595</t>
+  </si>
+  <si>
+    <t>946.108.14603</t>
+  </si>
+  <si>
+    <t>946.108.14611</t>
+  </si>
+  <si>
+    <t>946.108.14470</t>
+  </si>
+  <si>
+    <t>946.108.14496</t>
+  </si>
+  <si>
+    <t>946.108.14512</t>
+  </si>
+  <si>
+    <t>946.108.13951</t>
+  </si>
+  <si>
+    <t>946.108.13969</t>
+  </si>
+  <si>
+    <t>946.108.13977</t>
+  </si>
+  <si>
+    <t>195950403862</t>
+  </si>
+  <si>
+    <t>195950404104</t>
+  </si>
+  <si>
+    <t>195950404340</t>
+  </si>
+  <si>
+    <t>195950404586</t>
+  </si>
+  <si>
+    <t>195950404821</t>
+  </si>
+  <si>
+    <t>195950405064</t>
+  </si>
+  <si>
+    <t>195950405309</t>
+  </si>
+  <si>
+    <t>195950405545</t>
+  </si>
+  <si>
+    <t>195950405781</t>
+  </si>
+  <si>
+    <t>195950406023</t>
+  </si>
+  <si>
+    <t>195950406269</t>
+  </si>
+  <si>
+    <t>195950406504</t>
   </si>
 </sst>
 </file>
@@ -18482,7 +18812,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="493">
+  <cellXfs count="495">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -19044,6 +19374,10 @@
     <xf numFmtId="0" fontId="0" fillId="295" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="296" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="297" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="259" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="259" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19575,7 +19909,7 @@
         <v>1191</v>
       </c>
       <c r="B13" s="298" t="s">
-        <v>5509</v>
+        <v>5490</v>
       </c>
       <c r="C13" s="298" t="s">
         <v>3752</v>
@@ -19816,7 +20150,7 @@
         <v>1191</v>
       </c>
       <c r="B31" s="298" t="s">
-        <v>5509</v>
+        <v>5490</v>
       </c>
       <c r="C31" s="298" t="s">
         <v>3752</v>
@@ -20071,7 +20405,7 @@
         <v>1191</v>
       </c>
       <c r="B50" s="298" t="s">
-        <v>5509</v>
+        <v>5490</v>
       </c>
       <c r="C50" s="298" t="s">
         <v>3752</v>
@@ -23318,7 +23652,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5499</v>
+        <v>5480</v>
       </c>
       <c r="B1" s="74" t="s">
         <v>76</v>
@@ -24067,7 +24401,7 @@
         <v>642</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>5367</v>
+        <v>5354</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
@@ -24081,7 +24415,7 @@
         <v>644</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>5368</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="50" customFormat="1" ht="17" x14ac:dyDescent="0.25">
@@ -24095,7 +24429,7 @@
         <v>646</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>5369</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="52" customFormat="1" ht="17" x14ac:dyDescent="0.25">
@@ -24109,7 +24443,7 @@
         <v>1290</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>5370</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="54" customFormat="1" ht="17" x14ac:dyDescent="0.25">
@@ -24123,7 +24457,7 @@
         <v>649</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>5371</v>
+        <v>5358</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -24591,14 +24925,14 @@
     </row>
     <row r="25" spans="1:4" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="150" t="s">
-        <v>5305</v>
+        <v>5292</v>
       </c>
       <c r="B25" s="150" t="s">
-        <v>5307</v>
+        <v>5294</v>
       </c>
       <c r="C25" s="150"/>
       <c r="D25" s="151" t="s">
-        <v>5306</v>
+        <v>5293</v>
       </c>
     </row>
   </sheetData>
@@ -24632,142 +24966,142 @@
     </row>
     <row r="2" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>5325</v>
+        <v>5312</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>5345</v>
+        <v>5332</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>5356</v>
+        <v>5343</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>5335</v>
+        <v>5322</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="56" t="s">
-        <v>5326</v>
+        <v>5313</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>5346</v>
+        <v>5333</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>5357</v>
+        <v>5344</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>5336</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="56" t="s">
-        <v>5321</v>
+        <v>5308</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>5341</v>
+        <v>5328</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>5358</v>
+        <v>5345</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>5331</v>
+        <v>5318</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
-        <v>5322</v>
+        <v>5309</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>5342</v>
+        <v>5329</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>5359</v>
+        <v>5346</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>5332</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
-        <v>5323</v>
+        <v>5310</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>5343</v>
+        <v>5330</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>5360</v>
+        <v>5347</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>5333</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="56" t="s">
-        <v>5324</v>
+        <v>5311</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>5344</v>
+        <v>5331</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>5361</v>
+        <v>5348</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>5334</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
-        <v>5327</v>
+        <v>5314</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>5347</v>
+        <v>5334</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>5362</v>
+        <v>5349</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>5337</v>
+        <v>5324</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
-        <v>5328</v>
+        <v>5315</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>5348</v>
+        <v>5335</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>5363</v>
+        <v>5350</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>5338</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
-        <v>5329</v>
+        <v>5316</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>5349</v>
+        <v>5336</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>5364</v>
+        <v>5351</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>5339</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
-        <v>5330</v>
+        <v>5317</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>5350</v>
+        <v>5337</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>5365</v>
+        <v>5352</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>5340</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
@@ -26731,7 +27065,7 @@
         <v>4288</v>
       </c>
       <c r="C57" s="71" t="s">
-        <v>5498</v>
+        <v>5479</v>
       </c>
       <c r="D57" s="190" t="s">
         <v>4280</v>
@@ -26787,7 +27121,7 @@
         <v>4292</v>
       </c>
       <c r="C61" s="68" t="s">
-        <v>5497</v>
+        <v>5478</v>
       </c>
       <c r="D61" s="187" t="s">
         <v>4284</v>
@@ -27377,12 +27711,12 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2394A6-B4D1-2B4A-AF55-BD85C6000C3F}">
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.83203125" style="141" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="141" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="141" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="141" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" style="141" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" style="141" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="10.83203125" style="141"/>
@@ -27404,296 +27738,296 @@
     </row>
     <row r="2" spans="1:4" s="416" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="415" t="s">
-        <v>5022</v>
+        <v>5010</v>
       </c>
       <c r="B2" s="415" t="s">
-        <v>5064</v>
+        <v>5052</v>
       </c>
       <c r="C2" s="415" t="s">
-        <v>5372</v>
+        <v>5359</v>
       </c>
       <c r="D2" s="416" t="s">
-        <v>5043</v>
+        <v>5031</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="418" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="417" t="s">
-        <v>5023</v>
+        <v>5011</v>
       </c>
       <c r="B3" s="417" t="s">
-        <v>5065</v>
+        <v>5053</v>
       </c>
       <c r="C3" s="417" t="s">
-        <v>5373</v>
+        <v>5360</v>
       </c>
       <c r="D3" s="418" t="s">
-        <v>5044</v>
+        <v>5032</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="422" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="421" t="s">
-        <v>5024</v>
+        <v>5012</v>
       </c>
       <c r="B4" s="421" t="s">
-        <v>5066</v>
+        <v>5054</v>
       </c>
       <c r="C4" s="421" t="s">
-        <v>5374</v>
+        <v>5361</v>
       </c>
       <c r="D4" s="422" t="s">
-        <v>5045</v>
+        <v>5033</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="408" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="407" t="s">
-        <v>5025</v>
+        <v>5013</v>
       </c>
       <c r="B5" s="407" t="s">
-        <v>5067</v>
+        <v>5055</v>
       </c>
       <c r="C5" s="407" t="s">
-        <v>5375</v>
+        <v>5362</v>
       </c>
       <c r="D5" s="408" t="s">
-        <v>5046</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="401" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="402" t="s">
-        <v>5026</v>
+        <v>5014</v>
       </c>
       <c r="B6" s="402" t="s">
-        <v>5068</v>
+        <v>5056</v>
       </c>
       <c r="C6" s="402" t="s">
-        <v>5376</v>
+        <v>5363</v>
       </c>
       <c r="D6" s="401" t="s">
-        <v>5047</v>
+        <v>5035</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="420" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="419" t="s">
-        <v>5027</v>
+        <v>5015</v>
       </c>
       <c r="B7" s="419" t="s">
-        <v>5069</v>
+        <v>5057</v>
       </c>
       <c r="C7" s="419" t="s">
-        <v>5377</v>
+        <v>5364</v>
       </c>
       <c r="D7" s="420" t="s">
-        <v>5048</v>
+        <v>5036</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="397" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="396" t="s">
-        <v>5028</v>
+        <v>5016</v>
       </c>
       <c r="B8" s="396" t="s">
-        <v>5070</v>
+        <v>5058</v>
       </c>
       <c r="C8" s="396" t="s">
-        <v>5378</v>
+        <v>5365</v>
       </c>
       <c r="D8" s="397" t="s">
-        <v>5049</v>
+        <v>5037</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="416" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="415" t="s">
-        <v>5029</v>
+        <v>5017</v>
       </c>
       <c r="B9" s="415" t="s">
-        <v>5071</v>
+        <v>5059</v>
       </c>
       <c r="C9" s="415" t="s">
-        <v>5379</v>
+        <v>5366</v>
       </c>
       <c r="D9" s="416" t="s">
-        <v>5050</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="418" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="418" t="s">
-        <v>5030</v>
+        <v>5018</v>
       </c>
       <c r="B10" s="418" t="s">
-        <v>5072</v>
+        <v>5060</v>
       </c>
       <c r="C10" s="417" t="s">
-        <v>5380</v>
+        <v>5367</v>
       </c>
       <c r="D10" s="418" t="s">
-        <v>5051</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="422" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="422" t="s">
-        <v>5031</v>
+        <v>5019</v>
       </c>
       <c r="B11" s="422" t="s">
-        <v>5073</v>
+        <v>5061</v>
       </c>
       <c r="C11" s="421" t="s">
-        <v>5381</v>
+        <v>5368</v>
       </c>
       <c r="D11" s="422" t="s">
-        <v>5052</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="408" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="408" t="s">
-        <v>5032</v>
+        <v>5020</v>
       </c>
       <c r="B12" s="408" t="s">
-        <v>5074</v>
+        <v>5062</v>
       </c>
       <c r="C12" s="407" t="s">
-        <v>5382</v>
+        <v>5369</v>
       </c>
       <c r="D12" s="408" t="s">
-        <v>5053</v>
+        <v>5041</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="401" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="401" t="s">
-        <v>5033</v>
+        <v>5021</v>
       </c>
       <c r="B13" s="401" t="s">
-        <v>5075</v>
+        <v>5063</v>
       </c>
       <c r="C13" s="402" t="s">
-        <v>5383</v>
+        <v>5370</v>
       </c>
       <c r="D13" s="401" t="s">
-        <v>5054</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="420" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="420" t="s">
-        <v>5034</v>
+        <v>5022</v>
       </c>
       <c r="B14" s="420" t="s">
-        <v>5076</v>
+        <v>5064</v>
       </c>
       <c r="C14" s="419" t="s">
-        <v>5384</v>
+        <v>5371</v>
       </c>
       <c r="D14" s="420" t="s">
-        <v>5055</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="397" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="397" t="s">
-        <v>5035</v>
+        <v>5023</v>
       </c>
       <c r="B15" s="397" t="s">
-        <v>5077</v>
+        <v>5065</v>
       </c>
       <c r="C15" s="396" t="s">
-        <v>5385</v>
+        <v>5372</v>
       </c>
       <c r="D15" s="397" t="s">
-        <v>5056</v>
+        <v>5044</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="416" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="416" t="s">
-        <v>5036</v>
+        <v>5024</v>
       </c>
       <c r="B16" s="416" t="s">
-        <v>5078</v>
+        <v>5066</v>
       </c>
       <c r="C16" s="415" t="s">
-        <v>5386</v>
+        <v>5373</v>
       </c>
       <c r="D16" s="416" t="s">
-        <v>5057</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="418" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="418" t="s">
-        <v>5037</v>
+        <v>5025</v>
       </c>
       <c r="B17" s="418" t="s">
-        <v>5079</v>
+        <v>5067</v>
       </c>
       <c r="C17" s="417" t="s">
-        <v>5387</v>
+        <v>5374</v>
       </c>
       <c r="D17" s="418" t="s">
-        <v>5058</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="422" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="422" t="s">
-        <v>5038</v>
+        <v>5026</v>
       </c>
       <c r="B18" s="422" t="s">
-        <v>5080</v>
+        <v>5068</v>
       </c>
       <c r="C18" s="421" t="s">
-        <v>5388</v>
+        <v>5375</v>
       </c>
       <c r="D18" s="422" t="s">
-        <v>5059</v>
+        <v>5047</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="408" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="408" t="s">
-        <v>5039</v>
+        <v>5027</v>
       </c>
       <c r="B19" s="408" t="s">
-        <v>5081</v>
+        <v>5069</v>
       </c>
       <c r="C19" s="407" t="s">
-        <v>5389</v>
+        <v>5376</v>
       </c>
       <c r="D19" s="408" t="s">
-        <v>5060</v>
+        <v>5048</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="401" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="401" t="s">
-        <v>5040</v>
+        <v>5028</v>
       </c>
       <c r="B20" s="401" t="s">
-        <v>5082</v>
+        <v>5070</v>
       </c>
       <c r="C20" s="402" t="s">
-        <v>5390</v>
+        <v>5377</v>
       </c>
       <c r="D20" s="401" t="s">
-        <v>5061</v>
+        <v>5049</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="420" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="420" t="s">
-        <v>5041</v>
+        <v>5029</v>
       </c>
       <c r="B21" s="420" t="s">
-        <v>5083</v>
+        <v>5071</v>
       </c>
       <c r="C21" s="419" t="s">
-        <v>5391</v>
+        <v>5378</v>
       </c>
       <c r="D21" s="420" t="s">
-        <v>5062</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="397" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="397" t="s">
-        <v>5042</v>
+        <v>5030</v>
       </c>
       <c r="B22" s="397" t="s">
-        <v>5084</v>
+        <v>5072</v>
       </c>
       <c r="C22" s="396" t="s">
-        <v>5392</v>
+        <v>5379</v>
       </c>
       <c r="D22" s="397" t="s">
-        <v>5063</v>
+        <v>5051</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
@@ -27704,7 +28038,7 @@
     </row>
     <row r="24" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="72" t="s">
-        <v>5260</v>
+        <v>5247</v>
       </c>
       <c r="B24" s="74" t="s">
         <v>76</v>
@@ -27718,13 +28052,13 @@
     </row>
     <row r="25" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="409" t="s">
-        <v>5261</v>
+        <v>5248</v>
       </c>
       <c r="B25" s="409" t="s">
-        <v>5290</v>
+        <v>5277</v>
       </c>
       <c r="C25" s="409" t="s">
-        <v>5393</v>
+        <v>5380</v>
       </c>
       <c r="D25" s="429">
         <v>195951393865</v>
@@ -27732,198 +28066,198 @@
     </row>
     <row r="26" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="434" t="s">
-        <v>5262</v>
+        <v>5249</v>
       </c>
       <c r="B26" s="434" t="s">
-        <v>5291</v>
+        <v>5278</v>
       </c>
       <c r="C26" s="434" t="s">
-        <v>5394</v>
+        <v>5381</v>
       </c>
       <c r="D26" s="435" t="s">
-        <v>5276</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="432" t="s">
-        <v>5263</v>
+        <v>5250</v>
       </c>
       <c r="B27" s="432" t="s">
-        <v>5292</v>
+        <v>5279</v>
       </c>
       <c r="C27" s="432" t="s">
-        <v>5395</v>
+        <v>5382</v>
       </c>
       <c r="D27" s="433" t="s">
-        <v>5277</v>
+        <v>5264</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="430" t="s">
-        <v>5264</v>
+        <v>5251</v>
       </c>
       <c r="B28" s="430" t="s">
-        <v>5293</v>
+        <v>5280</v>
       </c>
       <c r="C28" s="430" t="s">
-        <v>5396</v>
+        <v>5383</v>
       </c>
       <c r="D28" s="431" t="s">
-        <v>5278</v>
+        <v>5265</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="436" t="s">
-        <v>5265</v>
+        <v>5252</v>
       </c>
       <c r="B29" s="436" t="s">
-        <v>5294</v>
+        <v>5281</v>
       </c>
       <c r="C29" s="436" t="s">
-        <v>5397</v>
+        <v>5384</v>
       </c>
       <c r="D29" s="437" t="s">
-        <v>5279</v>
+        <v>5266</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="409" t="s">
-        <v>5266</v>
+        <v>5253</v>
       </c>
       <c r="B30" s="409" t="s">
-        <v>5295</v>
+        <v>5282</v>
       </c>
       <c r="C30" s="409" t="s">
-        <v>5398</v>
+        <v>5385</v>
       </c>
       <c r="D30" s="410" t="s">
-        <v>5280</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="434" t="s">
-        <v>5267</v>
+        <v>5254</v>
       </c>
       <c r="B31" s="434" t="s">
-        <v>5296</v>
+        <v>5283</v>
       </c>
       <c r="C31" s="434" t="s">
-        <v>5399</v>
+        <v>5386</v>
       </c>
       <c r="D31" s="435" t="s">
-        <v>5281</v>
+        <v>5268</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="432" t="s">
-        <v>5268</v>
+        <v>5255</v>
       </c>
       <c r="B32" s="432" t="s">
-        <v>5297</v>
+        <v>5284</v>
       </c>
       <c r="C32" s="432" t="s">
-        <v>5400</v>
+        <v>5387</v>
       </c>
       <c r="D32" s="433" t="s">
-        <v>5282</v>
+        <v>5269</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="431" t="s">
-        <v>5269</v>
+        <v>5256</v>
       </c>
       <c r="B33" s="431" t="s">
-        <v>5298</v>
+        <v>5285</v>
       </c>
       <c r="C33" s="430" t="s">
-        <v>5401</v>
+        <v>5388</v>
       </c>
       <c r="D33" s="431" t="s">
-        <v>5283</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="437" t="s">
-        <v>5270</v>
+        <v>5257</v>
       </c>
       <c r="B34" s="437" t="s">
-        <v>5299</v>
+        <v>5286</v>
       </c>
       <c r="C34" s="436" t="s">
-        <v>5402</v>
+        <v>5389</v>
       </c>
       <c r="D34" s="437" t="s">
-        <v>5284</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="410" t="s">
-        <v>5271</v>
+        <v>5258</v>
       </c>
       <c r="B35" s="410" t="s">
-        <v>5300</v>
+        <v>5287</v>
       </c>
       <c r="C35" s="409" t="s">
-        <v>5403</v>
+        <v>5390</v>
       </c>
       <c r="D35" s="410" t="s">
-        <v>5285</v>
+        <v>5272</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="435" t="s">
-        <v>5272</v>
+        <v>5259</v>
       </c>
       <c r="B36" s="435" t="s">
-        <v>5301</v>
+        <v>5288</v>
       </c>
       <c r="C36" s="434" t="s">
-        <v>5404</v>
+        <v>5391</v>
       </c>
       <c r="D36" s="435" t="s">
-        <v>5286</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="433" t="s">
-        <v>5273</v>
+        <v>5260</v>
       </c>
       <c r="B37" s="433" t="s">
-        <v>5302</v>
+        <v>5289</v>
       </c>
       <c r="C37" s="432" t="s">
-        <v>5405</v>
+        <v>5392</v>
       </c>
       <c r="D37" s="433" t="s">
-        <v>5287</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="431" t="s">
-        <v>5274</v>
+        <v>5261</v>
       </c>
       <c r="B38" s="431" t="s">
-        <v>5303</v>
+        <v>5290</v>
       </c>
       <c r="C38" s="430" t="s">
-        <v>5406</v>
+        <v>5393</v>
       </c>
       <c r="D38" s="431" t="s">
-        <v>5288</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="437" t="s">
-        <v>5275</v>
+        <v>5262</v>
       </c>
       <c r="B39" s="437" t="s">
-        <v>5304</v>
+        <v>5291</v>
       </c>
       <c r="C39" s="436" t="s">
-        <v>5407</v>
+        <v>5394</v>
       </c>
       <c r="D39" s="437" t="s">
-        <v>5289</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
@@ -27954,7 +28288,7 @@
         <v>4878</v>
       </c>
       <c r="C42" s="396" t="s">
-        <v>5408</v>
+        <v>5395</v>
       </c>
       <c r="D42" s="397" t="s">
         <v>4830</v>
@@ -27968,7 +28302,7 @@
         <v>4879</v>
       </c>
       <c r="C43" s="396" t="s">
-        <v>5409</v>
+        <v>5396</v>
       </c>
       <c r="D43" s="400" t="s">
         <v>4831</v>
@@ -27982,7 +28316,7 @@
         <v>4880</v>
       </c>
       <c r="C44" s="411" t="s">
-        <v>5410</v>
+        <v>5397</v>
       </c>
       <c r="D44" s="412" t="s">
         <v>4832</v>
@@ -27996,7 +28330,7 @@
         <v>4881</v>
       </c>
       <c r="C45" s="411" t="s">
-        <v>5411</v>
+        <v>5398</v>
       </c>
       <c r="D45" s="412" t="s">
         <v>4833</v>
@@ -28010,7 +28344,7 @@
         <v>4882</v>
       </c>
       <c r="C46" s="407" t="s">
-        <v>5412</v>
+        <v>5399</v>
       </c>
       <c r="D46" s="408" t="s">
         <v>4834</v>
@@ -28024,7 +28358,7 @@
         <v>4883</v>
       </c>
       <c r="C47" s="407" t="s">
-        <v>5413</v>
+        <v>5400</v>
       </c>
       <c r="D47" s="408" t="s">
         <v>4835</v>
@@ -28038,7 +28372,7 @@
         <v>4884</v>
       </c>
       <c r="C48" s="403" t="s">
-        <v>5414</v>
+        <v>5401</v>
       </c>
       <c r="D48" s="404" t="s">
         <v>4836</v>
@@ -28052,7 +28386,7 @@
         <v>4885</v>
       </c>
       <c r="C49" s="403" t="s">
-        <v>5415</v>
+        <v>5402</v>
       </c>
       <c r="D49" s="404" t="s">
         <v>4837</v>
@@ -28066,7 +28400,7 @@
         <v>4886</v>
       </c>
       <c r="C50" s="409" t="s">
-        <v>5416</v>
+        <v>5403</v>
       </c>
       <c r="D50" s="410" t="s">
         <v>4838</v>
@@ -28080,7 +28414,7 @@
         <v>4887</v>
       </c>
       <c r="C51" s="409" t="s">
-        <v>5417</v>
+        <v>5404</v>
       </c>
       <c r="D51" s="410" t="s">
         <v>4839</v>
@@ -28094,7 +28428,7 @@
         <v>4888</v>
       </c>
       <c r="C52" s="402" t="s">
-        <v>5418</v>
+        <v>5405</v>
       </c>
       <c r="D52" s="401" t="s">
         <v>4840</v>
@@ -28108,7 +28442,7 @@
         <v>4889</v>
       </c>
       <c r="C53" s="402" t="s">
-        <v>5419</v>
+        <v>5406</v>
       </c>
       <c r="D53" s="401" t="s">
         <v>4841</v>
@@ -28122,7 +28456,7 @@
         <v>4890</v>
       </c>
       <c r="C54" s="414" t="s">
-        <v>5420</v>
+        <v>5407</v>
       </c>
       <c r="D54" s="413" t="s">
         <v>4842</v>
@@ -28136,7 +28470,7 @@
         <v>4891</v>
       </c>
       <c r="C55" s="414" t="s">
-        <v>5419</v>
+        <v>5406</v>
       </c>
       <c r="D55" s="413" t="s">
         <v>4843</v>
@@ -28150,7 +28484,7 @@
         <v>4892</v>
       </c>
       <c r="C56" s="406" t="s">
-        <v>5421</v>
+        <v>5408</v>
       </c>
       <c r="D56" s="405" t="s">
         <v>4844</v>
@@ -28164,7 +28498,7 @@
         <v>4893</v>
       </c>
       <c r="C57" s="406" t="s">
-        <v>5422</v>
+        <v>5409</v>
       </c>
       <c r="D57" s="405" t="s">
         <v>4845</v>
@@ -28178,7 +28512,7 @@
         <v>4894</v>
       </c>
       <c r="C58" s="396" t="s">
-        <v>5423</v>
+        <v>5410</v>
       </c>
       <c r="D58" s="397" t="s">
         <v>4846</v>
@@ -28192,7 +28526,7 @@
         <v>4895</v>
       </c>
       <c r="C59" s="396" t="s">
-        <v>5424</v>
+        <v>5411</v>
       </c>
       <c r="D59" s="397" t="s">
         <v>4847</v>
@@ -28206,7 +28540,7 @@
         <v>4896</v>
       </c>
       <c r="C60" s="411" t="s">
-        <v>5425</v>
+        <v>5412</v>
       </c>
       <c r="D60" s="412" t="s">
         <v>4848</v>
@@ -28220,7 +28554,7 @@
         <v>4897</v>
       </c>
       <c r="C61" s="411" t="s">
-        <v>5426</v>
+        <v>5413</v>
       </c>
       <c r="D61" s="412" t="s">
         <v>4849</v>
@@ -28234,7 +28568,7 @@
         <v>4898</v>
       </c>
       <c r="C62" s="407" t="s">
-        <v>5427</v>
+        <v>5414</v>
       </c>
       <c r="D62" s="408" t="s">
         <v>4850</v>
@@ -28248,7 +28582,7 @@
         <v>4899</v>
       </c>
       <c r="C63" s="407" t="s">
-        <v>5428</v>
+        <v>5415</v>
       </c>
       <c r="D63" s="408" t="s">
         <v>4851</v>
@@ -28262,7 +28596,7 @@
         <v>4900</v>
       </c>
       <c r="C64" s="403" t="s">
-        <v>5429</v>
+        <v>5416</v>
       </c>
       <c r="D64" s="404" t="s">
         <v>4852</v>
@@ -28276,7 +28610,7 @@
         <v>4901</v>
       </c>
       <c r="C65" s="403" t="s">
-        <v>5430</v>
+        <v>5417</v>
       </c>
       <c r="D65" s="404" t="s">
         <v>4853</v>
@@ -28290,7 +28624,7 @@
         <v>4902</v>
       </c>
       <c r="C66" s="409" t="s">
-        <v>5431</v>
+        <v>5418</v>
       </c>
       <c r="D66" s="410" t="s">
         <v>4854</v>
@@ -28304,7 +28638,7 @@
         <v>4903</v>
       </c>
       <c r="C67" s="409" t="s">
-        <v>5432</v>
+        <v>5419</v>
       </c>
       <c r="D67" s="410" t="s">
         <v>4855</v>
@@ -28318,7 +28652,7 @@
         <v>4904</v>
       </c>
       <c r="C68" s="402" t="s">
-        <v>5433</v>
+        <v>5420</v>
       </c>
       <c r="D68" s="401" t="s">
         <v>4856</v>
@@ -28332,7 +28666,7 @@
         <v>4905</v>
       </c>
       <c r="C69" s="402" t="s">
-        <v>5434</v>
+        <v>5421</v>
       </c>
       <c r="D69" s="401" t="s">
         <v>4857</v>
@@ -28346,7 +28680,7 @@
         <v>4906</v>
       </c>
       <c r="C70" s="414" t="s">
-        <v>5435</v>
+        <v>5422</v>
       </c>
       <c r="D70" s="413" t="s">
         <v>4858</v>
@@ -28360,7 +28694,7 @@
         <v>4907</v>
       </c>
       <c r="C71" s="414" t="s">
-        <v>5436</v>
+        <v>5423</v>
       </c>
       <c r="D71" s="413" t="s">
         <v>4859</v>
@@ -28374,7 +28708,7 @@
         <v>4908</v>
       </c>
       <c r="C72" s="406" t="s">
-        <v>5437</v>
+        <v>5424</v>
       </c>
       <c r="D72" s="405" t="s">
         <v>4860</v>
@@ -28388,7 +28722,7 @@
         <v>4909</v>
       </c>
       <c r="C73" s="406" t="s">
-        <v>5438</v>
+        <v>5425</v>
       </c>
       <c r="D73" s="405" t="s">
         <v>4861</v>
@@ -28402,7 +28736,7 @@
         <v>4910</v>
       </c>
       <c r="C74" s="396" t="s">
-        <v>5439</v>
+        <v>5426</v>
       </c>
       <c r="D74" s="397" t="s">
         <v>4862</v>
@@ -28416,7 +28750,7 @@
         <v>4911</v>
       </c>
       <c r="C75" s="396" t="s">
-        <v>5440</v>
+        <v>5427</v>
       </c>
       <c r="D75" s="397" t="s">
         <v>4863</v>
@@ -28430,7 +28764,7 @@
         <v>4912</v>
       </c>
       <c r="C76" s="411" t="s">
-        <v>5441</v>
+        <v>5428</v>
       </c>
       <c r="D76" s="412" t="s">
         <v>4864</v>
@@ -28444,7 +28778,7 @@
         <v>4913</v>
       </c>
       <c r="C77" s="411" t="s">
-        <v>5442</v>
+        <v>5429</v>
       </c>
       <c r="D77" s="412" t="s">
         <v>4865</v>
@@ -28458,7 +28792,7 @@
         <v>4914</v>
       </c>
       <c r="C78" s="407" t="s">
-        <v>5443</v>
+        <v>5430</v>
       </c>
       <c r="D78" s="408" t="s">
         <v>4866</v>
@@ -28472,7 +28806,7 @@
         <v>4915</v>
       </c>
       <c r="C79" s="407" t="s">
-        <v>5444</v>
+        <v>5431</v>
       </c>
       <c r="D79" s="408" t="s">
         <v>4867</v>
@@ -28486,7 +28820,7 @@
         <v>4916</v>
       </c>
       <c r="C80" s="403" t="s">
-        <v>5445</v>
+        <v>5432</v>
       </c>
       <c r="D80" s="404" t="s">
         <v>4868</v>
@@ -28500,7 +28834,7 @@
         <v>4917</v>
       </c>
       <c r="C81" s="403" t="s">
-        <v>5446</v>
+        <v>5433</v>
       </c>
       <c r="D81" s="404" t="s">
         <v>4869</v>
@@ -28514,7 +28848,7 @@
         <v>4918</v>
       </c>
       <c r="C82" s="409" t="s">
-        <v>5447</v>
+        <v>5434</v>
       </c>
       <c r="D82" s="410" t="s">
         <v>4870</v>
@@ -28528,7 +28862,7 @@
         <v>4919</v>
       </c>
       <c r="C83" s="409" t="s">
-        <v>5448</v>
+        <v>5435</v>
       </c>
       <c r="D83" s="410" t="s">
         <v>4871</v>
@@ -28542,7 +28876,7 @@
         <v>4920</v>
       </c>
       <c r="C84" s="402" t="s">
-        <v>5449</v>
+        <v>5436</v>
       </c>
       <c r="D84" s="401" t="s">
         <v>4872</v>
@@ -28556,7 +28890,7 @@
         <v>4921</v>
       </c>
       <c r="C85" s="402" t="s">
-        <v>5450</v>
+        <v>5437</v>
       </c>
       <c r="D85" s="401" t="s">
         <v>4873</v>
@@ -28570,7 +28904,7 @@
         <v>4922</v>
       </c>
       <c r="C86" s="414" t="s">
-        <v>5451</v>
+        <v>5438</v>
       </c>
       <c r="D86" s="413" t="s">
         <v>4874</v>
@@ -28584,7 +28918,7 @@
         <v>4923</v>
       </c>
       <c r="C87" s="414" t="s">
-        <v>5452</v>
+        <v>5439</v>
       </c>
       <c r="D87" s="413" t="s">
         <v>4875</v>
@@ -28598,7 +28932,7 @@
         <v>4924</v>
       </c>
       <c r="C88" s="406" t="s">
-        <v>5453</v>
+        <v>5440</v>
       </c>
       <c r="D88" s="405" t="s">
         <v>4876</v>
@@ -28612,7 +28946,7 @@
         <v>4925</v>
       </c>
       <c r="C89" s="406" t="s">
-        <v>5454</v>
+        <v>5441</v>
       </c>
       <c r="D89" s="405" t="s">
         <v>4877</v>
@@ -28621,7 +28955,7 @@
     <row r="90" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="72" t="s">
-        <v>5169</v>
+        <v>5156</v>
       </c>
       <c r="B91" s="74" t="s">
         <v>76</v>
@@ -28635,362 +28969,422 @@
     </row>
     <row r="92" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="409" t="s">
-        <v>5170</v>
+        <v>5157</v>
       </c>
       <c r="B92" s="409" t="s">
-        <v>5230</v>
-      </c>
-      <c r="C92" s="409"/>
+        <v>5217</v>
+      </c>
+      <c r="C92" s="409" t="s">
+        <v>5492</v>
+      </c>
       <c r="D92" s="410" t="s">
-        <v>5200</v>
+        <v>5187</v>
       </c>
     </row>
     <row r="93" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="426" t="s">
-        <v>5171</v>
+        <v>5158</v>
       </c>
       <c r="B93" s="427" t="s">
-        <v>5231</v>
-      </c>
-      <c r="C93" s="409"/>
+        <v>5218</v>
+      </c>
+      <c r="C93" s="409" t="s">
+        <v>5493</v>
+      </c>
       <c r="D93" s="428" t="s">
-        <v>5201</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="94" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="430" t="s">
-        <v>5172</v>
+        <v>5159</v>
       </c>
       <c r="B94" s="430" t="s">
-        <v>5232</v>
-      </c>
-      <c r="C94" s="430"/>
+        <v>5219</v>
+      </c>
+      <c r="C94" s="430" t="s">
+        <v>5494</v>
+      </c>
       <c r="D94" s="431" t="s">
-        <v>5202</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="95" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="430" t="s">
-        <v>5173</v>
+        <v>5160</v>
       </c>
       <c r="B95" s="430" t="s">
-        <v>5233</v>
-      </c>
-      <c r="C95" s="430"/>
+        <v>5220</v>
+      </c>
+      <c r="C95" s="430" t="s">
+        <v>5495</v>
+      </c>
       <c r="D95" s="431" t="s">
-        <v>5203</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="96" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="432" t="s">
-        <v>5174</v>
+        <v>5161</v>
       </c>
       <c r="B96" s="432" t="s">
-        <v>5234</v>
-      </c>
-      <c r="C96" s="432"/>
+        <v>5221</v>
+      </c>
+      <c r="C96" s="432" t="s">
+        <v>5496</v>
+      </c>
       <c r="D96" s="433" t="s">
-        <v>5204</v>
+        <v>5191</v>
       </c>
     </row>
     <row r="97" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="432" t="s">
-        <v>5175</v>
+        <v>5162</v>
       </c>
       <c r="B97" s="432" t="s">
-        <v>5235</v>
-      </c>
-      <c r="C97" s="432"/>
+        <v>5222</v>
+      </c>
+      <c r="C97" s="432" t="s">
+        <v>5497</v>
+      </c>
       <c r="D97" s="433" t="s">
-        <v>5205</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="98" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="434" t="s">
-        <v>5176</v>
+        <v>5163</v>
       </c>
       <c r="B98" s="434" t="s">
-        <v>5236</v>
-      </c>
-      <c r="C98" s="434"/>
+        <v>5223</v>
+      </c>
+      <c r="C98" s="434" t="s">
+        <v>5498</v>
+      </c>
       <c r="D98" s="435" t="s">
-        <v>5206</v>
+        <v>5193</v>
       </c>
     </row>
     <row r="99" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="434" t="s">
-        <v>5177</v>
+        <v>5164</v>
       </c>
       <c r="B99" s="434" t="s">
-        <v>5237</v>
-      </c>
-      <c r="C99" s="434"/>
+        <v>5224</v>
+      </c>
+      <c r="C99" s="434" t="s">
+        <v>5499</v>
+      </c>
       <c r="D99" s="435" t="s">
-        <v>5207</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="100" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="436" t="s">
-        <v>5178</v>
+        <v>5165</v>
       </c>
       <c r="B100" s="436" t="s">
-        <v>5238</v>
-      </c>
-      <c r="C100" s="436"/>
+        <v>5225</v>
+      </c>
+      <c r="C100" s="436" t="s">
+        <v>5500</v>
+      </c>
       <c r="D100" s="437" t="s">
-        <v>5208</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="101" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="436" t="s">
-        <v>5179</v>
+        <v>5166</v>
       </c>
       <c r="B101" s="436" t="s">
-        <v>5239</v>
-      </c>
-      <c r="C101" s="436"/>
+        <v>5226</v>
+      </c>
+      <c r="C101" s="436" t="s">
+        <v>5501</v>
+      </c>
       <c r="D101" s="437" t="s">
-        <v>5209</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="102" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="410" t="s">
-        <v>5180</v>
+        <v>5167</v>
       </c>
       <c r="B102" s="410" t="s">
-        <v>5240</v>
-      </c>
-      <c r="C102" s="409"/>
+        <v>5227</v>
+      </c>
+      <c r="C102" s="409" t="s">
+        <v>5502</v>
+      </c>
       <c r="D102" s="410" t="s">
-        <v>5210</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="103" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="410" t="s">
-        <v>5181</v>
+        <v>5168</v>
       </c>
       <c r="B103" s="410" t="s">
-        <v>5241</v>
-      </c>
-      <c r="C103" s="409"/>
+        <v>5228</v>
+      </c>
+      <c r="C103" s="409" t="s">
+        <v>5503</v>
+      </c>
       <c r="D103" s="410" t="s">
-        <v>5211</v>
+        <v>5198</v>
       </c>
     </row>
     <row r="104" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="431" t="s">
-        <v>5182</v>
+        <v>5169</v>
       </c>
       <c r="B104" s="431" t="s">
-        <v>5242</v>
-      </c>
-      <c r="C104" s="430"/>
+        <v>5229</v>
+      </c>
+      <c r="C104" s="430" t="s">
+        <v>5504</v>
+      </c>
       <c r="D104" s="431" t="s">
-        <v>5212</v>
+        <v>5199</v>
       </c>
     </row>
     <row r="105" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="431" t="s">
-        <v>5183</v>
+        <v>5170</v>
       </c>
       <c r="B105" s="431" t="s">
-        <v>5243</v>
-      </c>
-      <c r="C105" s="430"/>
+        <v>5230</v>
+      </c>
+      <c r="C105" s="430" t="s">
+        <v>5505</v>
+      </c>
       <c r="D105" s="431" t="s">
-        <v>5213</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="106" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="433" t="s">
-        <v>5184</v>
+        <v>5171</v>
       </c>
       <c r="B106" s="433" t="s">
-        <v>5244</v>
-      </c>
-      <c r="C106" s="432"/>
+        <v>5231</v>
+      </c>
+      <c r="C106" s="432" t="s">
+        <v>5506</v>
+      </c>
       <c r="D106" s="433" t="s">
-        <v>5214</v>
+        <v>5201</v>
       </c>
     </row>
     <row r="107" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="433" t="s">
-        <v>5185</v>
+        <v>5172</v>
       </c>
       <c r="B107" s="433" t="s">
-        <v>5245</v>
-      </c>
-      <c r="C107" s="432"/>
+        <v>5232</v>
+      </c>
+      <c r="C107" s="432" t="s">
+        <v>5507</v>
+      </c>
       <c r="D107" s="433" t="s">
-        <v>5215</v>
+        <v>5202</v>
       </c>
     </row>
     <row r="108" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="435" t="s">
-        <v>5186</v>
+        <v>5173</v>
       </c>
       <c r="B108" s="435" t="s">
-        <v>5246</v>
-      </c>
-      <c r="C108" s="434"/>
+        <v>5233</v>
+      </c>
+      <c r="C108" s="434" t="s">
+        <v>5508</v>
+      </c>
       <c r="D108" s="435" t="s">
-        <v>5216</v>
+        <v>5203</v>
       </c>
     </row>
     <row r="109" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="435" t="s">
-        <v>5187</v>
+        <v>5174</v>
       </c>
       <c r="B109" s="435" t="s">
-        <v>5247</v>
-      </c>
-      <c r="C109" s="434"/>
+        <v>5234</v>
+      </c>
+      <c r="C109" s="434" t="s">
+        <v>5509</v>
+      </c>
       <c r="D109" s="435" t="s">
-        <v>5217</v>
+        <v>5204</v>
       </c>
     </row>
     <row r="110" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="437" t="s">
-        <v>5188</v>
+        <v>5175</v>
       </c>
       <c r="B110" s="437" t="s">
-        <v>5248</v>
-      </c>
-      <c r="C110" s="436"/>
+        <v>5235</v>
+      </c>
+      <c r="C110" s="436" t="s">
+        <v>5510</v>
+      </c>
       <c r="D110" s="437" t="s">
-        <v>5218</v>
+        <v>5205</v>
       </c>
     </row>
     <row r="111" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="437" t="s">
-        <v>5189</v>
+        <v>5176</v>
       </c>
       <c r="B111" s="437" t="s">
-        <v>5249</v>
-      </c>
-      <c r="C111" s="436"/>
+        <v>5236</v>
+      </c>
+      <c r="C111" s="436" t="s">
+        <v>5511</v>
+      </c>
       <c r="D111" s="437" t="s">
-        <v>5219</v>
+        <v>5206</v>
       </c>
     </row>
     <row r="112" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="410" t="s">
-        <v>5190</v>
+        <v>5177</v>
       </c>
       <c r="B112" s="410" t="s">
-        <v>5250</v>
-      </c>
-      <c r="C112" s="409"/>
+        <v>5237</v>
+      </c>
+      <c r="C112" s="409" t="s">
+        <v>5512</v>
+      </c>
       <c r="D112" s="410" t="s">
-        <v>5220</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="113" spans="1:4" s="410" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="410" t="s">
-        <v>5191</v>
+        <v>5178</v>
       </c>
       <c r="B113" s="410" t="s">
-        <v>5251</v>
-      </c>
-      <c r="C113" s="409"/>
+        <v>5238</v>
+      </c>
+      <c r="C113" s="409" t="s">
+        <v>5513</v>
+      </c>
       <c r="D113" s="410" t="s">
-        <v>5221</v>
+        <v>5208</v>
       </c>
     </row>
     <row r="114" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="431" t="s">
-        <v>5192</v>
+        <v>5179</v>
       </c>
       <c r="B114" s="431" t="s">
-        <v>5252</v>
-      </c>
-      <c r="C114" s="430"/>
+        <v>5239</v>
+      </c>
+      <c r="C114" s="430" t="s">
+        <v>5514</v>
+      </c>
       <c r="D114" s="431" t="s">
-        <v>5222</v>
+        <v>5209</v>
       </c>
     </row>
     <row r="115" spans="1:4" s="431" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="431" t="s">
-        <v>5193</v>
+        <v>5180</v>
       </c>
       <c r="B115" s="431" t="s">
-        <v>5253</v>
-      </c>
-      <c r="C115" s="430"/>
+        <v>5240</v>
+      </c>
+      <c r="C115" s="430" t="s">
+        <v>5515</v>
+      </c>
       <c r="D115" s="431" t="s">
-        <v>5223</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="116" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="433" t="s">
-        <v>5194</v>
+        <v>5181</v>
       </c>
       <c r="B116" s="433" t="s">
-        <v>5254</v>
-      </c>
-      <c r="C116" s="432"/>
+        <v>5241</v>
+      </c>
+      <c r="C116" s="432" t="s">
+        <v>5516</v>
+      </c>
       <c r="D116" s="433" t="s">
-        <v>5224</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="117" spans="1:4" s="433" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="433" t="s">
-        <v>5195</v>
+        <v>5182</v>
       </c>
       <c r="B117" s="433" t="s">
-        <v>5255</v>
-      </c>
-      <c r="C117" s="432"/>
+        <v>5242</v>
+      </c>
+      <c r="C117" s="432" t="s">
+        <v>5517</v>
+      </c>
       <c r="D117" s="433" t="s">
-        <v>5225</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="118" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="435" t="s">
-        <v>5196</v>
+        <v>5183</v>
       </c>
       <c r="B118" s="435" t="s">
-        <v>5256</v>
-      </c>
-      <c r="C118" s="434"/>
+        <v>5243</v>
+      </c>
+      <c r="C118" s="434" t="s">
+        <v>5518</v>
+      </c>
       <c r="D118" s="435" t="s">
-        <v>5226</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="119" spans="1:4" s="435" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="435" t="s">
-        <v>5197</v>
+        <v>5184</v>
       </c>
       <c r="B119" s="435" t="s">
-        <v>5257</v>
-      </c>
-      <c r="C119" s="434"/>
+        <v>5244</v>
+      </c>
+      <c r="C119" s="434" t="s">
+        <v>5519</v>
+      </c>
       <c r="D119" s="435" t="s">
-        <v>5227</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="120" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="437" t="s">
-        <v>5198</v>
+        <v>5185</v>
       </c>
       <c r="B120" s="437" t="s">
-        <v>5258</v>
-      </c>
-      <c r="C120" s="436"/>
+        <v>5245</v>
+      </c>
+      <c r="C120" s="436" t="s">
+        <v>5520</v>
+      </c>
       <c r="D120" s="437" t="s">
-        <v>5228</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="121" spans="1:4" s="437" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="437" t="s">
-        <v>5199</v>
+        <v>5186</v>
       </c>
       <c r="B121" s="437" t="s">
-        <v>5259</v>
-      </c>
-      <c r="C121" s="436"/>
+        <v>5246</v>
+      </c>
+      <c r="C121" s="436" t="s">
+        <v>5521</v>
+      </c>
       <c r="D121" s="437" t="s">
-        <v>5229</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="122" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -29015,7 +29409,9 @@
       <c r="B124" s="235" t="s">
         <v>4751</v>
       </c>
-      <c r="C124" s="235"/>
+      <c r="C124" s="235" t="s">
+        <v>5522</v>
+      </c>
       <c r="D124" s="236" t="s">
         <v>4750</v>
       </c>
@@ -29027,7 +29423,9 @@
       <c r="B125" s="439" t="s">
         <v>4754</v>
       </c>
-      <c r="C125" s="439"/>
+      <c r="C125" s="439" t="s">
+        <v>5523</v>
+      </c>
       <c r="D125" s="438" t="s">
         <v>4753</v>
       </c>
@@ -29039,7 +29437,9 @@
       <c r="B126" s="424" t="s">
         <v>4757</v>
       </c>
-      <c r="C126" s="424"/>
+      <c r="C126" s="424" t="s">
+        <v>5524</v>
+      </c>
       <c r="D126" s="425" t="s">
         <v>4756</v>
       </c>
@@ -29051,7 +29451,9 @@
       <c r="B127" s="235" t="s">
         <v>4765</v>
       </c>
-      <c r="C127" s="235"/>
+      <c r="C127" s="235" t="s">
+        <v>5525</v>
+      </c>
       <c r="D127" s="236" t="s">
         <v>4764</v>
       </c>
@@ -29063,7 +29465,9 @@
       <c r="B128" s="439" t="s">
         <v>4763</v>
       </c>
-      <c r="C128" s="439"/>
+      <c r="C128" s="439" t="s">
+        <v>5526</v>
+      </c>
       <c r="D128" s="438" t="s">
         <v>4762</v>
       </c>
@@ -29075,7 +29479,9 @@
       <c r="B129" s="424" t="s">
         <v>4760</v>
       </c>
-      <c r="C129" s="424"/>
+      <c r="C129" s="424" t="s">
+        <v>5527</v>
+      </c>
       <c r="D129" s="425" t="s">
         <v>4759</v>
       </c>
@@ -29087,7 +29493,9 @@
       <c r="B130" s="235" t="s">
         <v>4780</v>
       </c>
-      <c r="C130" s="235"/>
+      <c r="C130" s="235" t="s">
+        <v>5528</v>
+      </c>
       <c r="D130" s="236" t="s">
         <v>4778</v>
       </c>
@@ -29099,7 +29507,9 @@
       <c r="B131" s="235" t="s">
         <v>4781</v>
       </c>
-      <c r="C131" s="235"/>
+      <c r="C131" s="235" t="s">
+        <v>5529</v>
+      </c>
       <c r="D131" s="236" t="s">
         <v>4779</v>
       </c>
@@ -29111,7 +29521,9 @@
       <c r="B132" s="441" t="s">
         <v>4776</v>
       </c>
-      <c r="C132" s="439"/>
+      <c r="C132" s="439" t="s">
+        <v>5530</v>
+      </c>
       <c r="D132" s="442" t="s">
         <v>4774</v>
       </c>
@@ -29123,7 +29535,9 @@
       <c r="B133" s="439" t="s">
         <v>4777</v>
       </c>
-      <c r="C133" s="439"/>
+      <c r="C133" s="439" t="s">
+        <v>5531</v>
+      </c>
       <c r="D133" s="438" t="s">
         <v>4775</v>
       </c>
@@ -29135,7 +29549,9 @@
       <c r="B134" s="424" t="s">
         <v>4772</v>
       </c>
-      <c r="C134" s="424"/>
+      <c r="C134" s="424" t="s">
+        <v>5532</v>
+      </c>
       <c r="D134" s="425" t="s">
         <v>4770</v>
       </c>
@@ -29147,7 +29563,9 @@
       <c r="B135" s="424" t="s">
         <v>4773</v>
       </c>
-      <c r="C135" s="424"/>
+      <c r="C135" s="424" t="s">
+        <v>5533</v>
+      </c>
       <c r="D135" s="425" t="s">
         <v>4771</v>
       </c>
@@ -29155,7 +29573,7 @@
     <row r="136" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="137" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="72" t="s">
-        <v>5308</v>
+        <v>5295</v>
       </c>
       <c r="B137" s="74" t="s">
         <v>76</v>
@@ -29169,50 +29587,58 @@
     </row>
     <row r="138" spans="1:4" s="438" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="438" t="s">
-        <v>5309</v>
+        <v>5296</v>
       </c>
       <c r="B138" s="438" t="s">
-        <v>5317</v>
-      </c>
-      <c r="C138" s="439"/>
+        <v>5304</v>
+      </c>
+      <c r="C138" s="439" t="s">
+        <v>5534</v>
+      </c>
       <c r="D138" s="438" t="s">
-        <v>5313</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="139" spans="1:4" s="443" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="443" t="s">
-        <v>5310</v>
+        <v>5297</v>
       </c>
       <c r="B139" s="443" t="s">
-        <v>5318</v>
-      </c>
-      <c r="C139" s="444"/>
+        <v>5305</v>
+      </c>
+      <c r="C139" s="444" t="s">
+        <v>5535</v>
+      </c>
       <c r="D139" s="443" t="s">
-        <v>5314</v>
+        <v>5301</v>
       </c>
     </row>
     <row r="140" spans="1:4" s="438" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="438" t="s">
-        <v>5311</v>
+        <v>5298</v>
       </c>
       <c r="B140" s="438" t="s">
-        <v>5319</v>
-      </c>
-      <c r="C140" s="439"/>
+        <v>5306</v>
+      </c>
+      <c r="C140" s="439" t="s">
+        <v>5536</v>
+      </c>
       <c r="D140" s="438" t="s">
-        <v>5315</v>
+        <v>5302</v>
       </c>
     </row>
     <row r="141" spans="1:4" s="443" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="443" t="s">
-        <v>5312</v>
+        <v>5299</v>
       </c>
       <c r="B141" s="443" t="s">
-        <v>5320</v>
-      </c>
-      <c r="C141" s="444"/>
+        <v>5307</v>
+      </c>
+      <c r="C141" s="444" t="s">
+        <v>5537</v>
+      </c>
       <c r="D141" s="443" t="s">
-        <v>5316</v>
+        <v>5303</v>
       </c>
     </row>
     <row r="142" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -29232,194 +29658,226 @@
     </row>
     <row r="144" spans="1:4" s="452" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="452" t="s">
-        <v>5121</v>
+        <v>5108</v>
       </c>
       <c r="B144" s="452" t="s">
-        <v>5153</v>
-      </c>
-      <c r="C144" s="453"/>
+        <v>5140</v>
+      </c>
+      <c r="C144" s="453" t="s">
+        <v>5538</v>
+      </c>
       <c r="D144" s="452" t="s">
-        <v>5137</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="145" spans="1:4" s="452" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="452" t="s">
-        <v>5122</v>
+        <v>5109</v>
       </c>
       <c r="B145" s="452" t="s">
-        <v>5154</v>
-      </c>
-      <c r="C145" s="453"/>
+        <v>5141</v>
+      </c>
+      <c r="C145" s="453" t="s">
+        <v>5539</v>
+      </c>
       <c r="D145" s="452" t="s">
-        <v>5138</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="146" spans="1:4" s="457" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="457" t="s">
-        <v>5123</v>
+        <v>5110</v>
       </c>
       <c r="B146" s="457" t="s">
-        <v>5155</v>
-      </c>
-      <c r="C146" s="458"/>
+        <v>5142</v>
+      </c>
+      <c r="C146" s="458" t="s">
+        <v>5540</v>
+      </c>
       <c r="D146" s="457" t="s">
-        <v>5139</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="147" spans="1:4" s="457" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="457" t="s">
-        <v>5124</v>
+        <v>5111</v>
       </c>
       <c r="B147" s="457" t="s">
-        <v>5156</v>
-      </c>
-      <c r="C147" s="458"/>
+        <v>5143</v>
+      </c>
+      <c r="C147" s="458" t="s">
+        <v>5541</v>
+      </c>
       <c r="D147" s="457" t="s">
-        <v>5140</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="148" spans="1:4" s="459" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="459" t="s">
-        <v>5125</v>
+        <v>5112</v>
       </c>
       <c r="B148" s="459" t="s">
-        <v>5157</v>
-      </c>
-      <c r="C148" s="460"/>
+        <v>5144</v>
+      </c>
+      <c r="C148" s="460" t="s">
+        <v>5542</v>
+      </c>
       <c r="D148" s="459" t="s">
-        <v>5141</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="149" spans="1:4" s="459" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="459" t="s">
-        <v>5126</v>
+        <v>5113</v>
       </c>
       <c r="B149" s="459" t="s">
-        <v>5158</v>
-      </c>
-      <c r="C149" s="460"/>
+        <v>5145</v>
+      </c>
+      <c r="C149" s="460" t="s">
+        <v>5543</v>
+      </c>
       <c r="D149" s="459" t="s">
-        <v>5142</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="150" spans="1:4" s="461" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="461" t="s">
-        <v>5127</v>
+        <v>5114</v>
       </c>
       <c r="B150" s="461" t="s">
-        <v>5159</v>
-      </c>
-      <c r="C150" s="462"/>
+        <v>5146</v>
+      </c>
+      <c r="C150" s="462" t="s">
+        <v>5544</v>
+      </c>
       <c r="D150" s="461" t="s">
-        <v>5143</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="151" spans="1:4" s="461" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="461" t="s">
-        <v>5128</v>
+        <v>5115</v>
       </c>
       <c r="B151" s="461" t="s">
-        <v>5160</v>
-      </c>
-      <c r="C151" s="462"/>
+        <v>5147</v>
+      </c>
+      <c r="C151" s="462" t="s">
+        <v>5545</v>
+      </c>
       <c r="D151" s="461" t="s">
-        <v>5144</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="152" spans="1:4" s="452" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="454" t="s">
-        <v>5129</v>
+        <v>5116</v>
       </c>
       <c r="B152" s="455" t="s">
-        <v>5161</v>
-      </c>
-      <c r="C152" s="453"/>
+        <v>5148</v>
+      </c>
+      <c r="C152" s="453" t="s">
+        <v>5546</v>
+      </c>
       <c r="D152" s="456" t="s">
-        <v>5145</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="153" spans="1:4" s="452" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="452" t="s">
-        <v>5130</v>
+        <v>5117</v>
       </c>
       <c r="B153" s="452" t="s">
-        <v>5162</v>
-      </c>
-      <c r="C153" s="453"/>
+        <v>5149</v>
+      </c>
+      <c r="C153" s="453" t="s">
+        <v>5547</v>
+      </c>
       <c r="D153" s="452" t="s">
-        <v>5146</v>
+        <v>5133</v>
       </c>
     </row>
     <row r="154" spans="1:4" s="457" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="457" t="s">
-        <v>5131</v>
+        <v>5118</v>
       </c>
       <c r="B154" s="457" t="s">
-        <v>5163</v>
-      </c>
-      <c r="C154" s="458"/>
+        <v>5150</v>
+      </c>
+      <c r="C154" s="458" t="s">
+        <v>5548</v>
+      </c>
       <c r="D154" s="457" t="s">
-        <v>5147</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="155" spans="1:4" s="457" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="457" t="s">
-        <v>5132</v>
+        <v>5119</v>
       </c>
       <c r="B155" s="457" t="s">
-        <v>5164</v>
-      </c>
-      <c r="C155" s="458"/>
+        <v>5151</v>
+      </c>
+      <c r="C155" s="458" t="s">
+        <v>5549</v>
+      </c>
       <c r="D155" s="457" t="s">
-        <v>5148</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="156" spans="1:4" s="459" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="459" t="s">
-        <v>5133</v>
+        <v>5120</v>
       </c>
       <c r="B156" s="459" t="s">
-        <v>5165</v>
-      </c>
-      <c r="C156" s="460"/>
+        <v>5152</v>
+      </c>
+      <c r="C156" s="460" t="s">
+        <v>5550</v>
+      </c>
       <c r="D156" s="459" t="s">
-        <v>5149</v>
+        <v>5136</v>
       </c>
     </row>
     <row r="157" spans="1:4" s="459" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="459" t="s">
-        <v>5134</v>
+        <v>5121</v>
       </c>
       <c r="B157" s="459" t="s">
-        <v>5166</v>
-      </c>
-      <c r="C157" s="460"/>
+        <v>5153</v>
+      </c>
+      <c r="C157" s="460" t="s">
+        <v>5551</v>
+      </c>
       <c r="D157" s="459" t="s">
-        <v>5150</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="158" spans="1:4" s="461" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="461" t="s">
-        <v>5135</v>
+        <v>5122</v>
       </c>
       <c r="B158" s="461" t="s">
-        <v>5167</v>
-      </c>
-      <c r="C158" s="462"/>
+        <v>5154</v>
+      </c>
+      <c r="C158" s="462" t="s">
+        <v>5552</v>
+      </c>
       <c r="D158" s="461" t="s">
-        <v>5151</v>
+        <v>5138</v>
       </c>
     </row>
     <row r="159" spans="1:4" s="461" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="461" t="s">
-        <v>5136</v>
+        <v>5123</v>
       </c>
       <c r="B159" s="461" t="s">
-        <v>5168</v>
-      </c>
-      <c r="C159" s="462"/>
+        <v>5155</v>
+      </c>
+      <c r="C159" s="462" t="s">
+        <v>5553</v>
+      </c>
       <c r="D159" s="461" t="s">
-        <v>5152</v>
+        <v>5139</v>
       </c>
     </row>
     <row r="160" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -29439,143 +29897,170 @@
     </row>
     <row r="162" spans="1:4" s="445" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="445" t="s">
-        <v>5085</v>
+        <v>5073</v>
       </c>
       <c r="B162" s="445" t="s">
-        <v>5109</v>
-      </c>
-      <c r="C162" s="446"/>
+        <v>5096</v>
+      </c>
+      <c r="C162" s="446" t="s">
+        <v>5554</v>
+      </c>
       <c r="D162" s="445" t="s">
-        <v>5097</v>
+        <v>5084</v>
       </c>
     </row>
     <row r="163" spans="1:4" s="445" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="445" t="s">
-        <v>5086</v>
+        <v>5074</v>
       </c>
       <c r="B163" s="445" t="s">
-        <v>5110</v>
-      </c>
-      <c r="C163" s="446"/>
+        <v>5097</v>
+      </c>
+      <c r="C163" s="446" t="s">
+        <v>5555</v>
+      </c>
       <c r="D163" s="445" t="s">
-        <v>5098</v>
+        <v>5085</v>
       </c>
     </row>
     <row r="164" spans="1:4" s="445" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="445" t="s">
-        <v>5087</v>
+        <v>5075</v>
       </c>
       <c r="B164" s="445" t="s">
-        <v>5111</v>
-      </c>
-      <c r="C164" s="446"/>
+        <v>5098</v>
+      </c>
+      <c r="C164" s="446" t="s">
+        <v>5556</v>
+      </c>
       <c r="D164" s="445" t="s">
-        <v>5099</v>
+        <v>5086</v>
       </c>
     </row>
     <row r="165" spans="1:4" s="447" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="447" t="s">
-        <v>5088</v>
+        <v>5076</v>
       </c>
       <c r="B165" s="447" t="s">
-        <v>5112</v>
-      </c>
-      <c r="C165" s="448"/>
+        <v>5099</v>
+      </c>
+      <c r="C165" s="448" t="s">
+        <v>5557</v>
+      </c>
       <c r="D165" s="447" t="s">
-        <v>5100</v>
+        <v>5087</v>
       </c>
     </row>
     <row r="166" spans="1:4" s="447" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="447" t="s">
-        <v>5089</v>
+        <v>5077</v>
       </c>
       <c r="B166" s="447" t="s">
-        <v>5113</v>
-      </c>
-      <c r="C166" s="448"/>
+        <v>5100</v>
+      </c>
+      <c r="C166" s="448" t="s">
+        <v>5558</v>
+      </c>
       <c r="D166" s="447" t="s">
-        <v>5101</v>
+        <v>5088</v>
       </c>
     </row>
     <row r="167" spans="1:4" s="447" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="447" t="s">
-        <v>5090</v>
+        <v>5078</v>
       </c>
       <c r="B167" s="447" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C167" s="448"/>
+        <v>5101</v>
+      </c>
+      <c r="C167" s="448" t="s">
+        <v>5559</v>
+      </c>
       <c r="D167" s="447" t="s">
-        <v>5102</v>
+        <v>5089</v>
       </c>
     </row>
     <row r="168" spans="1:4" s="449" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="449" t="s">
-        <v>5091</v>
+        <v>5079</v>
       </c>
       <c r="B168" s="449" t="s">
-        <v>5115</v>
-      </c>
-      <c r="C168" s="450"/>
+        <v>5102</v>
+      </c>
+      <c r="C168" s="450" t="s">
+        <v>5560</v>
+      </c>
       <c r="D168" s="449" t="s">
-        <v>5103</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="169" spans="1:4" s="449" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="449" t="s">
-        <v>5092</v>
+        <v>5080</v>
       </c>
       <c r="B169" s="449" t="s">
-        <v>5116</v>
-      </c>
-      <c r="C169" s="450"/>
+        <v>5103</v>
+      </c>
+      <c r="C169" s="450" t="s">
+        <v>5561</v>
+      </c>
       <c r="D169" s="449" t="s">
-        <v>5104</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="170" spans="1:4" s="449" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="449" t="s">
-        <v>5093</v>
+        <v>5566</v>
       </c>
       <c r="B170" s="449" t="s">
-        <v>5117</v>
-      </c>
-      <c r="C170" s="450"/>
+        <v>5104</v>
+      </c>
+      <c r="C170" s="450" t="s">
+        <v>5562</v>
+      </c>
       <c r="D170" s="449" t="s">
-        <v>5105</v>
+        <v>5092</v>
       </c>
     </row>
     <row r="171" spans="1:4" s="451" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="451" t="s">
-        <v>5094</v>
+        <v>5081</v>
       </c>
       <c r="B171" s="451" t="s">
-        <v>5118</v>
+        <v>5105</v>
+      </c>
+      <c r="C171" s="493" t="s">
+        <v>5563</v>
       </c>
       <c r="D171" s="451" t="s">
-        <v>5106</v>
+        <v>5093</v>
       </c>
     </row>
     <row r="172" spans="1:4" s="451" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="451" t="s">
-        <v>5095</v>
+        <v>5082</v>
       </c>
       <c r="B172" s="451" t="s">
-        <v>5119</v>
+        <v>5106</v>
+      </c>
+      <c r="C172" s="494" t="s">
+        <v>5564</v>
       </c>
       <c r="D172" s="451" t="s">
-        <v>5107</v>
+        <v>5094</v>
       </c>
     </row>
     <row r="173" spans="1:4" s="451" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="451" t="s">
-        <v>5096</v>
+        <v>5083</v>
       </c>
       <c r="B173" s="451" t="s">
-        <v>5120</v>
+        <v>5107</v>
+      </c>
+      <c r="C173" s="494" t="s">
+        <v>5565</v>
       </c>
       <c r="D173" s="451" t="s">
-        <v>5108</v>
+        <v>5095</v>
       </c>
     </row>
     <row r="174" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -29595,578 +30080,590 @@
     </row>
     <row r="176" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="463" t="s">
-        <v>5455</v>
+        <v>5442</v>
       </c>
       <c r="B176" s="463" t="s">
-        <v>4953</v>
-      </c>
-      <c r="C176" s="464"/>
+        <v>4950</v>
+      </c>
+      <c r="C176" s="464" t="s">
+        <v>5567</v>
+      </c>
       <c r="D176" s="463" t="s">
         <v>4926</v>
       </c>
     </row>
     <row r="177" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="463" t="s">
-        <v>5456</v>
+        <v>5443</v>
       </c>
       <c r="B177" s="463" t="s">
-        <v>4954</v>
-      </c>
-      <c r="C177" s="464"/>
+        <v>4951</v>
+      </c>
+      <c r="C177" s="464" t="s">
+        <v>5568</v>
+      </c>
       <c r="D177" s="463" t="s">
         <v>4927</v>
       </c>
     </row>
     <row r="178" spans="1:4" s="475" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="475" t="s">
-        <v>5457</v>
+        <v>5444</v>
       </c>
       <c r="B178" s="475" t="s">
-        <v>4955</v>
-      </c>
-      <c r="C178" s="476"/>
+        <v>4952</v>
+      </c>
+      <c r="C178" s="476" t="s">
+        <v>5569</v>
+      </c>
       <c r="D178" s="475" t="s">
         <v>4928</v>
       </c>
     </row>
     <row r="179" spans="1:4" s="475" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="475" t="s">
-        <v>5458</v>
+        <v>5445</v>
       </c>
       <c r="B179" s="475" t="s">
-        <v>4956</v>
-      </c>
-      <c r="C179" s="476"/>
+        <v>4953</v>
+      </c>
+      <c r="C179" s="476" t="s">
+        <v>5570</v>
+      </c>
       <c r="D179" s="475" t="s">
         <v>4929</v>
       </c>
     </row>
     <row r="180" spans="1:4" s="477" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="477" t="s">
-        <v>5459</v>
+        <v>5446</v>
       </c>
       <c r="B180" s="477" t="s">
-        <v>4957</v>
-      </c>
-      <c r="C180" s="478"/>
+        <v>4954</v>
+      </c>
+      <c r="C180" s="478" t="s">
+        <v>5571</v>
+      </c>
       <c r="D180" s="477" t="s">
         <v>4930</v>
       </c>
     </row>
     <row r="181" spans="1:4" s="477" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="477" t="s">
-        <v>5460</v>
+        <v>5447</v>
       </c>
       <c r="B181" s="477" t="s">
-        <v>4958</v>
-      </c>
-      <c r="C181" s="478"/>
+        <v>4955</v>
+      </c>
+      <c r="C181" s="478" t="s">
+        <v>5572</v>
+      </c>
       <c r="D181" s="477" t="s">
         <v>4931</v>
       </c>
     </row>
     <row r="182" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="465" t="s">
-        <v>5496</v>
+        <v>5477</v>
       </c>
       <c r="B182" s="465" t="s">
-        <v>5007</v>
-      </c>
-      <c r="C182" s="466"/>
+        <v>4998</v>
+      </c>
+      <c r="C182" s="466" t="s">
+        <v>5573</v>
+      </c>
       <c r="D182" s="465" t="s">
-        <v>4986</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="183" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="465" t="s">
-        <v>5495</v>
+        <v>5476</v>
       </c>
       <c r="B183" s="465" t="s">
-        <v>5008</v>
-      </c>
-      <c r="C183" s="466"/>
+        <v>4999</v>
+      </c>
+      <c r="C183" s="466" t="s">
+        <v>5574</v>
+      </c>
       <c r="D183" s="465" t="s">
-        <v>4987</v>
+        <v>4981</v>
       </c>
     </row>
     <row r="184" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="465" t="s">
-        <v>5494</v>
+        <v>5475</v>
       </c>
       <c r="B184" s="465" t="s">
-        <v>5009</v>
-      </c>
-      <c r="C184" s="466"/>
+        <v>5000</v>
+      </c>
+      <c r="C184" s="466" t="s">
+        <v>5575</v>
+      </c>
       <c r="D184" s="465" t="s">
-        <v>4988</v>
+        <v>4982</v>
       </c>
     </row>
     <row r="185" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="463" t="s">
-        <v>5493</v>
+        <v>5474</v>
       </c>
       <c r="B185" s="463" t="s">
-        <v>5010</v>
-      </c>
-      <c r="C185" s="464"/>
+        <v>5001</v>
+      </c>
+      <c r="C185" s="464" t="s">
+        <v>5576</v>
+      </c>
       <c r="D185" s="463" t="s">
-        <v>4989</v>
+        <v>4983</v>
       </c>
     </row>
     <row r="186" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="463" t="s">
-        <v>5492</v>
+        <v>5473</v>
       </c>
       <c r="B186" s="463" t="s">
-        <v>5011</v>
-      </c>
-      <c r="C186" s="464"/>
+        <v>5002</v>
+      </c>
+      <c r="C186" s="464" t="s">
+        <v>5577</v>
+      </c>
       <c r="D186" s="463" t="s">
-        <v>4990</v>
+        <v>4984</v>
       </c>
     </row>
     <row r="187" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="464" t="s">
-        <v>5491</v>
+        <v>5472</v>
       </c>
       <c r="B187" s="464" t="s">
-        <v>5012</v>
-      </c>
-      <c r="C187" s="464"/>
+        <v>5003</v>
+      </c>
+      <c r="C187" s="464" t="s">
+        <v>5578</v>
+      </c>
       <c r="D187" s="463" t="s">
-        <v>4991</v>
+        <v>4985</v>
       </c>
     </row>
     <row r="188" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="468" t="s">
-        <v>5490</v>
+        <v>5471</v>
       </c>
       <c r="B188" s="468" t="s">
-        <v>5013</v>
-      </c>
-      <c r="C188" s="468"/>
+        <v>5004</v>
+      </c>
+      <c r="C188" s="468" t="s">
+        <v>5579</v>
+      </c>
       <c r="D188" s="467" t="s">
-        <v>4992</v>
+        <v>4986</v>
       </c>
     </row>
     <row r="189" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="468" t="s">
-        <v>5489</v>
+        <v>5470</v>
       </c>
       <c r="B189" s="468" t="s">
-        <v>5014</v>
-      </c>
-      <c r="C189" s="468"/>
+        <v>5005</v>
+      </c>
+      <c r="C189" s="468" t="s">
+        <v>5580</v>
+      </c>
       <c r="D189" s="467" t="s">
-        <v>4993</v>
+        <v>4987</v>
       </c>
     </row>
     <row r="190" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="468" t="s">
-        <v>5488</v>
+        <v>5469</v>
       </c>
       <c r="B190" s="468" t="s">
-        <v>5015</v>
-      </c>
-      <c r="C190" s="468"/>
+        <v>5006</v>
+      </c>
+      <c r="C190" s="468" t="s">
+        <v>5581</v>
+      </c>
       <c r="D190" s="467" t="s">
-        <v>4994</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="191" spans="1:4" s="469" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="470" t="s">
-        <v>5487</v>
+        <v>5468</v>
       </c>
       <c r="B191" s="470" t="s">
-        <v>5016</v>
-      </c>
-      <c r="C191" s="470"/>
+        <v>5007</v>
+      </c>
+      <c r="C191" s="470" t="s">
+        <v>5582</v>
+      </c>
       <c r="D191" s="469" t="s">
+        <v>4989</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" s="471" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="472" t="s">
+        <v>5467</v>
+      </c>
+      <c r="B192" s="472" t="s">
+        <v>5008</v>
+      </c>
+      <c r="C192" s="472" t="s">
+        <v>5583</v>
+      </c>
+      <c r="D192" s="471" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" s="473" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="474" t="s">
+        <v>5466</v>
+      </c>
+      <c r="B193" s="474" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C193" s="474" t="s">
+        <v>5584</v>
+      </c>
+      <c r="D193" s="473" t="s">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" s="479" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="479" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B194" s="479" t="s">
+        <v>4992</v>
+      </c>
+      <c r="C194" s="480" t="s">
+        <v>5585</v>
+      </c>
+      <c r="D194" s="479" t="s">
+        <v>4974</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" s="479" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="479" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B195" s="479" t="s">
+        <v>4993</v>
+      </c>
+      <c r="C195" s="480" t="s">
+        <v>5586</v>
+      </c>
+      <c r="D195" s="479" t="s">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" s="479" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="479" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B196" s="479" t="s">
+        <v>4994</v>
+      </c>
+      <c r="C196" s="480" t="s">
+        <v>5587</v>
+      </c>
+      <c r="D196" s="479" t="s">
+        <v>4976</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="463" t="s">
+        <v>5448</v>
+      </c>
+      <c r="B197" s="463" t="s">
+        <v>4956</v>
+      </c>
+      <c r="C197" s="464" t="s">
+        <v>5588</v>
+      </c>
+      <c r="D197" s="463" t="s">
+        <v>4932</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="463" t="s">
+        <v>5449</v>
+      </c>
+      <c r="B198" s="463" t="s">
+        <v>4957</v>
+      </c>
+      <c r="C198" s="464" t="s">
+        <v>5589</v>
+      </c>
+      <c r="D198" s="463" t="s">
+        <v>4933</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" s="475" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="475" t="s">
+        <v>5450</v>
+      </c>
+      <c r="B199" s="475" t="s">
+        <v>4958</v>
+      </c>
+      <c r="C199" s="476" t="s">
+        <v>5590</v>
+      </c>
+      <c r="D199" s="475" t="s">
+        <v>4934</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" s="475" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="475" t="s">
+        <v>5451</v>
+      </c>
+      <c r="B200" s="475" t="s">
+        <v>4959</v>
+      </c>
+      <c r="C200" s="476" t="s">
+        <v>5591</v>
+      </c>
+      <c r="D200" s="475" t="s">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" s="477" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="477" t="s">
+        <v>5452</v>
+      </c>
+      <c r="B201" s="477" t="s">
+        <v>4960</v>
+      </c>
+      <c r="C201" s="478" t="s">
+        <v>5592</v>
+      </c>
+      <c r="D201" s="477" t="s">
+        <v>4936</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" s="477" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="477" t="s">
+        <v>5453</v>
+      </c>
+      <c r="B202" s="477" t="s">
+        <v>4961</v>
+      </c>
+      <c r="C202" s="478" t="s">
+        <v>5593</v>
+      </c>
+      <c r="D202" s="477" t="s">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="465" t="s">
+        <v>5457</v>
+      </c>
+      <c r="B203" s="465" t="s">
+        <v>4965</v>
+      </c>
+      <c r="C203" s="466" t="s">
+        <v>5594</v>
+      </c>
+      <c r="D203" s="465" t="s">
+        <v>4941</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="465" t="s">
+        <v>5458</v>
+      </c>
+      <c r="B204" s="465" t="s">
+        <v>4966</v>
+      </c>
+      <c r="C204" s="466" t="s">
+        <v>5595</v>
+      </c>
+      <c r="D204" s="465" t="s">
+        <v>4942</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="465" t="s">
+        <v>5459</v>
+      </c>
+      <c r="B205" s="465" t="s">
+        <v>4967</v>
+      </c>
+      <c r="C205" s="466" t="s">
+        <v>5596</v>
+      </c>
+      <c r="D205" s="465" t="s">
+        <v>4943</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="463" t="s">
+        <v>5460</v>
+      </c>
+      <c r="B206" s="463" t="s">
+        <v>4968</v>
+      </c>
+      <c r="C206" s="464" t="s">
+        <v>5597</v>
+      </c>
+      <c r="D206" s="463" t="s">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="463" t="s">
+        <v>5461</v>
+      </c>
+      <c r="B207" s="463" t="s">
+        <v>4969</v>
+      </c>
+      <c r="C207" s="464" t="s">
+        <v>5598</v>
+      </c>
+      <c r="D207" s="463" t="s">
+        <v>4945</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="463" t="s">
+        <v>5462</v>
+      </c>
+      <c r="B208" s="463" t="s">
+        <v>4970</v>
+      </c>
+      <c r="C208" s="464" t="s">
+        <v>5599</v>
+      </c>
+      <c r="D208" s="463" t="s">
+        <v>4946</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="467" t="s">
+        <v>5463</v>
+      </c>
+      <c r="B209" s="467" t="s">
+        <v>4971</v>
+      </c>
+      <c r="C209" s="468" t="s">
+        <v>5600</v>
+      </c>
+      <c r="D209" s="467" t="s">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="467" t="s">
+        <v>5464</v>
+      </c>
+      <c r="B210" s="467" t="s">
+        <v>4972</v>
+      </c>
+      <c r="C210" s="468" t="s">
+        <v>5601</v>
+      </c>
+      <c r="D210" s="467" t="s">
+        <v>4948</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="467" t="s">
+        <v>5465</v>
+      </c>
+      <c r="B211" s="467" t="s">
+        <v>4973</v>
+      </c>
+      <c r="C211" s="468" t="s">
+        <v>5602</v>
+      </c>
+      <c r="D211" s="467" t="s">
+        <v>4949</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" s="469" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="469" t="s">
+        <v>5454</v>
+      </c>
+      <c r="B212" s="469" t="s">
+        <v>4962</v>
+      </c>
+      <c r="C212" s="470" t="s">
+        <v>5603</v>
+      </c>
+      <c r="D212" s="469" t="s">
+        <v>4938</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" s="471" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="471" t="s">
+        <v>5455</v>
+      </c>
+      <c r="B213" s="471" t="s">
+        <v>4963</v>
+      </c>
+      <c r="C213" s="472" t="s">
+        <v>5604</v>
+      </c>
+      <c r="D213" s="471" t="s">
+        <v>4939</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" s="473" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="473" t="s">
+        <v>5456</v>
+      </c>
+      <c r="B214" s="473" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C214" s="474" t="s">
+        <v>5605</v>
+      </c>
+      <c r="D214" s="473" t="s">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" s="481" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="481" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B215" s="481" t="s">
         <v>4995</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" s="469" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="469" t="s">
-        <v>5486</v>
-      </c>
-      <c r="B192" s="469" t="s">
-        <v>5017</v>
-      </c>
-      <c r="C192" s="470"/>
-      <c r="D192" s="469" t="s">
+      <c r="C215" s="482" t="s">
+        <v>5606</v>
+      </c>
+      <c r="D215" s="481" t="s">
+        <v>4977</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" s="481" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="481" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B216" s="481" t="s">
         <v>4996</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" s="471" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="472" t="s">
-        <v>5485</v>
-      </c>
-      <c r="B193" s="472" t="s">
-        <v>5018</v>
-      </c>
-      <c r="C193" s="472"/>
-      <c r="D193" s="471" t="s">
+      <c r="C216" s="482" t="s">
+        <v>5607</v>
+      </c>
+      <c r="D216" s="481" t="s">
+        <v>4978</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" s="481" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="481" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B217" s="481" t="s">
         <v>4997</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" s="471" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="472" t="s">
-        <v>5484</v>
-      </c>
-      <c r="B194" s="472" t="s">
-        <v>5019</v>
-      </c>
-      <c r="C194" s="472"/>
-      <c r="D194" s="471" t="s">
-        <v>4998</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" s="473" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="474" t="s">
-        <v>5483</v>
-      </c>
-      <c r="B195" s="474" t="s">
-        <v>5020</v>
-      </c>
-      <c r="C195" s="474"/>
-      <c r="D195" s="473" t="s">
-        <v>4999</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" s="473" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="473" t="s">
-        <v>5482</v>
-      </c>
-      <c r="B196" s="473" t="s">
-        <v>5021</v>
-      </c>
-      <c r="C196" s="474"/>
-      <c r="D196" s="473" t="s">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" s="479" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="479" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B197" s="479" t="s">
-        <v>5001</v>
-      </c>
-      <c r="C197" s="480"/>
-      <c r="D197" s="479" t="s">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" s="479" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="479" t="s">
-        <v>2658</v>
-      </c>
-      <c r="B198" s="479" t="s">
-        <v>5002</v>
-      </c>
-      <c r="C198" s="480"/>
-      <c r="D198" s="479" t="s">
-        <v>4981</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" s="479" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="479" t="s">
-        <v>2659</v>
-      </c>
-      <c r="B199" s="479" t="s">
-        <v>5003</v>
-      </c>
-      <c r="C199" s="480"/>
-      <c r="D199" s="479" t="s">
-        <v>4982</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="463" t="s">
-        <v>5461</v>
-      </c>
-      <c r="B200" s="463" t="s">
-        <v>4959</v>
-      </c>
-      <c r="C200" s="464"/>
-      <c r="D200" s="463" t="s">
-        <v>4932</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="463" t="s">
-        <v>5462</v>
-      </c>
-      <c r="B201" s="463" t="s">
-        <v>4960</v>
-      </c>
-      <c r="C201" s="464"/>
-      <c r="D201" s="463" t="s">
-        <v>4933</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" s="475" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="475" t="s">
-        <v>5463</v>
-      </c>
-      <c r="B202" s="475" t="s">
-        <v>4961</v>
-      </c>
-      <c r="C202" s="476"/>
-      <c r="D202" s="475" t="s">
-        <v>4934</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" s="475" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="475" t="s">
-        <v>5464</v>
-      </c>
-      <c r="B203" s="475" t="s">
-        <v>4962</v>
-      </c>
-      <c r="C203" s="476"/>
-      <c r="D203" s="475" t="s">
-        <v>4935</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" s="477" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="477" t="s">
-        <v>5465</v>
-      </c>
-      <c r="B204" s="477" t="s">
-        <v>4963</v>
-      </c>
-      <c r="C204" s="478"/>
-      <c r="D204" s="477" t="s">
-        <v>4936</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" s="477" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="477" t="s">
-        <v>5466</v>
-      </c>
-      <c r="B205" s="477" t="s">
-        <v>4964</v>
-      </c>
-      <c r="C205" s="478"/>
-      <c r="D205" s="477" t="s">
-        <v>4937</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="465" t="s">
-        <v>5473</v>
-      </c>
-      <c r="B206" s="465" t="s">
-        <v>4971</v>
-      </c>
-      <c r="C206" s="466"/>
-      <c r="D206" s="465" t="s">
-        <v>4944</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="465" t="s">
-        <v>5474</v>
-      </c>
-      <c r="B207" s="465" t="s">
-        <v>4972</v>
-      </c>
-      <c r="C207" s="466"/>
-      <c r="D207" s="465" t="s">
-        <v>4945</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" s="465" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="465" t="s">
-        <v>5475</v>
-      </c>
-      <c r="B208" s="465" t="s">
-        <v>4973</v>
-      </c>
-      <c r="C208" s="466"/>
-      <c r="D208" s="465" t="s">
-        <v>4946</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="463" t="s">
-        <v>5476</v>
-      </c>
-      <c r="B209" s="463" t="s">
-        <v>4974</v>
-      </c>
-      <c r="C209" s="464"/>
-      <c r="D209" s="463" t="s">
-        <v>4947</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="463" t="s">
-        <v>5477</v>
-      </c>
-      <c r="B210" s="463" t="s">
-        <v>4975</v>
-      </c>
-      <c r="C210" s="464"/>
-      <c r="D210" s="463" t="s">
-        <v>4948</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" s="463" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="463" t="s">
-        <v>5478</v>
-      </c>
-      <c r="B211" s="463" t="s">
-        <v>4976</v>
-      </c>
-      <c r="C211" s="464"/>
-      <c r="D211" s="463" t="s">
-        <v>4949</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="467" t="s">
-        <v>5479</v>
-      </c>
-      <c r="B212" s="467" t="s">
-        <v>4977</v>
-      </c>
-      <c r="C212" s="468"/>
-      <c r="D212" s="467" t="s">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="467" t="s">
-        <v>5480</v>
-      </c>
-      <c r="B213" s="467" t="s">
-        <v>4978</v>
-      </c>
-      <c r="C213" s="468"/>
-      <c r="D213" s="467" t="s">
-        <v>4951</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" s="467" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="467" t="s">
-        <v>5481</v>
-      </c>
-      <c r="B214" s="467" t="s">
+      <c r="C217" s="482" t="s">
+        <v>5608</v>
+      </c>
+      <c r="D217" s="481" t="s">
         <v>4979</v>
-      </c>
-      <c r="C214" s="468"/>
-      <c r="D214" s="467" t="s">
-        <v>4952</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" s="469" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="469" t="s">
-        <v>5467</v>
-      </c>
-      <c r="B215" s="469" t="s">
-        <v>4965</v>
-      </c>
-      <c r="C215" s="470"/>
-      <c r="D215" s="469" t="s">
-        <v>4938</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" s="469" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="469" t="s">
-        <v>5468</v>
-      </c>
-      <c r="B216" s="469" t="s">
-        <v>4966</v>
-      </c>
-      <c r="C216" s="470"/>
-      <c r="D216" s="469" t="s">
-        <v>4939</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" s="471" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="471" t="s">
-        <v>5469</v>
-      </c>
-      <c r="B217" s="471" t="s">
-        <v>4967</v>
-      </c>
-      <c r="C217" s="472"/>
-      <c r="D217" s="471" t="s">
-        <v>4940</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" s="471" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="471" t="s">
-        <v>5470</v>
-      </c>
-      <c r="B218" s="471" t="s">
-        <v>4968</v>
-      </c>
-      <c r="C218" s="472"/>
-      <c r="D218" s="471" t="s">
-        <v>4941</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" s="473" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="473" t="s">
-        <v>5471</v>
-      </c>
-      <c r="B219" s="473" t="s">
-        <v>4969</v>
-      </c>
-      <c r="C219" s="474"/>
-      <c r="D219" s="473" t="s">
-        <v>4942</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" s="473" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="473" t="s">
-        <v>5472</v>
-      </c>
-      <c r="B220" s="473" t="s">
-        <v>4970</v>
-      </c>
-      <c r="C220" s="474"/>
-      <c r="D220" s="473" t="s">
-        <v>4943</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" s="481" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="481" t="s">
-        <v>2660</v>
-      </c>
-      <c r="B221" s="481" t="s">
-        <v>5004</v>
-      </c>
-      <c r="C221" s="482"/>
-      <c r="D221" s="481" t="s">
-        <v>4983</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" s="481" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="481" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B222" s="481" t="s">
-        <v>5005</v>
-      </c>
-      <c r="C222" s="482"/>
-      <c r="D222" s="481" t="s">
-        <v>4984</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" s="481" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="481" t="s">
-        <v>2662</v>
-      </c>
-      <c r="B223" s="481" t="s">
-        <v>5006</v>
-      </c>
-      <c r="C223" s="482"/>
-      <c r="D223" s="481" t="s">
-        <v>4985</v>
       </c>
     </row>
   </sheetData>
@@ -30187,7 +30684,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="72" t="s">
-        <v>5506</v>
+        <v>5487</v>
       </c>
       <c r="B1" s="74"/>
       <c r="C1" s="72"/>
@@ -30195,7 +30692,7 @@
     </row>
     <row r="2" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="483" t="s">
-        <v>5500</v>
+        <v>5481</v>
       </c>
       <c r="B2" s="483"/>
       <c r="C2" s="483"/>
@@ -30203,7 +30700,7 @@
     </row>
     <row r="3" spans="1:4" s="486" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="485" t="s">
-        <v>5501</v>
+        <v>5482</v>
       </c>
       <c r="B3" s="485"/>
       <c r="C3" s="485"/>
@@ -30211,7 +30708,7 @@
     </row>
     <row r="4" spans="1:4" s="488" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="487" t="s">
-        <v>5502</v>
+        <v>5483</v>
       </c>
       <c r="B4" s="487"/>
       <c r="C4" s="487"/>
@@ -30219,7 +30716,7 @@
     </row>
     <row r="5" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
-        <v>5503</v>
+        <v>5484</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -30227,7 +30724,7 @@
     </row>
     <row r="6" spans="1:4" s="490" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="489" t="s">
-        <v>5504</v>
+        <v>5485</v>
       </c>
       <c r="B6" s="489"/>
       <c r="C6" s="489"/>
@@ -30235,7 +30732,7 @@
     </row>
     <row r="7" spans="1:4" s="492" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="491" t="s">
-        <v>5505</v>
+        <v>5486</v>
       </c>
       <c r="B7" s="491"/>
       <c r="C7" s="491"/>
@@ -30244,7 +30741,7 @@
     <row r="8" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>5507</v>
+        <v>5488</v>
       </c>
       <c r="B9" s="74"/>
       <c r="C9" s="72"/>
@@ -30252,7 +30749,7 @@
     </row>
     <row r="10" spans="1:4" s="484" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="483" t="s">
-        <v>5500</v>
+        <v>5481</v>
       </c>
       <c r="B10" s="483"/>
       <c r="C10" s="483"/>
@@ -30260,7 +30757,7 @@
     </row>
     <row r="11" spans="1:4" s="99" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="98" t="s">
-        <v>5508</v>
+        <v>5489</v>
       </c>
       <c r="B11" s="98"/>
       <c r="C11" s="98"/>
@@ -30387,7 +30884,7 @@
     </row>
     <row r="3" spans="1:4" s="34" customFormat="1" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="56" t="s">
-        <v>5366</v>
+        <v>5353</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>4547</v>
@@ -30832,7 +31329,7 @@
         <v>1191</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>5509</v>
+        <v>5490</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>3752</v>
@@ -31752,7 +32249,7 @@
         <v>4696</v>
       </c>
       <c r="C85" s="56" t="s">
-        <v>5351</v>
+        <v>5338</v>
       </c>
       <c r="D85" s="294" t="s">
         <v>4691</v>
@@ -31766,7 +32263,7 @@
         <v>4697</v>
       </c>
       <c r="C86" s="56" t="s">
-        <v>5352</v>
+        <v>5339</v>
       </c>
       <c r="D86" s="294" t="s">
         <v>4692</v>
@@ -31780,7 +32277,7 @@
         <v>4698</v>
       </c>
       <c r="C87" s="56" t="s">
-        <v>5353</v>
+        <v>5340</v>
       </c>
       <c r="D87" s="294" t="s">
         <v>4693</v>
@@ -31794,7 +32291,7 @@
         <v>4699</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>5354</v>
+        <v>5341</v>
       </c>
       <c r="D88" s="294" t="s">
         <v>4694</v>
@@ -31808,7 +32305,7 @@
         <v>4700</v>
       </c>
       <c r="C89" s="56" t="s">
-        <v>5355</v>
+        <v>5342</v>
       </c>
       <c r="D89" s="294" t="s">
         <v>4695</v>
@@ -33044,7 +33541,7 @@
     <row r="110" spans="1:16384" s="33" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C110" s="82"/>
     </row>
-    <row r="111" spans="1:16384" s="15" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16384" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="80" t="s">
         <v>3190</v>
       </c>
@@ -63200,7 +63697,7 @@
         <v>3333</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>3256</v>
+        <v>5609</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63214,7 +63711,7 @@
         <v>3334</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>3258</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63228,7 +63725,7 @@
         <v>3335</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>3260</v>
+        <v>5611</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63242,7 +63739,7 @@
         <v>3336</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>3262</v>
+        <v>5612</v>
       </c>
     </row>
     <row r="55" spans="1:4" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63256,7 +63753,7 @@
         <v>3337</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>3264</v>
+        <v>5613</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63270,7 +63767,7 @@
         <v>3339</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>3268</v>
+        <v>5614</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63284,7 +63781,7 @@
         <v>3338</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>3266</v>
+        <v>5615</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63298,7 +63795,7 @@
         <v>3340</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>3270</v>
+        <v>5616</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63312,7 +63809,7 @@
         <v>3341</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>3272</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63326,7 +63823,7 @@
         <v>3343</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>3276</v>
+        <v>5618</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63340,7 +63837,7 @@
         <v>3342</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>3274</v>
+        <v>5619</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63354,7 +63851,7 @@
         <v>3344</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>3278</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="22" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -63909,7 +64406,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>5510</v>
+        <v>5491</v>
       </c>
       <c r="B1" s="83" t="s">
         <v>76</v>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/Documents/Proyecto GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD1472E-1821-A44B-A72D-A894DB34DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A43E346-2D20-284E-A3A7-1B4A84FB43F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="16980" windowHeight="21480" firstSheet="3" activeTab="6" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
+    <workbookView xWindow="420" yWindow="760" windowWidth="26920" windowHeight="20180" firstSheet="17" activeTab="17" xr2:uid="{48C7426D-96CF-2E43-8D4F-15CCB058F2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="35" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7284" uniqueCount="5621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7289" uniqueCount="5623">
   <si>
     <t>Accesories</t>
   </si>
@@ -16932,6 +16932,12 @@
   </si>
   <si>
     <t>195950406504</t>
+  </si>
+  <si>
+    <t>Light Gray</t>
+  </si>
+  <si>
+    <t>890.504.45058</t>
   </si>
 </sst>
 </file>
@@ -17016,7 +17022,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="298">
+  <fills count="324">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -18799,6 +18805,162 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE46A7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE46A7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1E3FA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1E3FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF865968"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF865968"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF968C73"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF968C73"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8A857F"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8A857F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC44EA9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC44EA9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF656567"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF656567"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF746A4F"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF746A4F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7D92B2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7D92B2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF616581"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF616581"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8A919C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8A919C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F1EA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F1EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF3F6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF3F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -18812,7 +18974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="495">
+  <cellXfs count="521">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -19378,6 +19540,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="259" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="298" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="299" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="300" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="301" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="302" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="303" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="304" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="305" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="306" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="307" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="308" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="309" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="310" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="311" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="312" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="313" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="314" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="315" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="316" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="317" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="318" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="319" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="320" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="321" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="322" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="323" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19386,16 +19574,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFF41A3"/>
-      <color rgb="FFE70000"/>
-      <color rgb="FFF67800"/>
-      <color rgb="FF6BADD7"/>
-      <color rgb="FF64AE31"/>
-      <color rgb="FF989291"/>
-      <color rgb="FFCAC0B6"/>
-      <color rgb="FFC4AB8F"/>
-      <color rgb="FF916256"/>
-      <color rgb="FFA4A39C"/>
+      <color rgb="FFEFF3F6"/>
+      <color rgb="FFF9F1EA"/>
+      <color rgb="FF8A919C"/>
+      <color rgb="FF616581"/>
+      <color rgb="FF7D92B2"/>
+      <color rgb="FF746A4F"/>
+      <color rgb="FF656567"/>
+      <color rgb="FFC44EA9"/>
+      <color rgb="FF8A857F"/>
+      <color rgb="FFD1E3FA"/>
     </mruColors>
   </colors>
   <extLst>
@@ -24604,7 +24792,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C97BAD1B-EAD5-E74D-97CF-1443634E6364}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5" style="141" bestFit="1" customWidth="1"/>
@@ -24627,311 +24815,327 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="194" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="193" t="s">
+    <row r="2" spans="1:4" s="506" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="505" t="s">
         <v>4591</v>
       </c>
-      <c r="B2" s="193" t="s">
+      <c r="B2" s="505" t="s">
         <v>4607</v>
       </c>
-      <c r="C2" s="193" t="s">
+      <c r="C2" s="505" t="s">
         <v>4731</v>
       </c>
-      <c r="D2" s="193" t="s">
+      <c r="D2" s="505" t="s">
         <v>4599</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="145" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="144" t="s">
+    <row r="3" spans="1:4" s="500" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="499" t="s">
         <v>4592</v>
       </c>
-      <c r="B3" s="144" t="s">
+      <c r="B3" s="499" t="s">
         <v>4608</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="499" t="s">
         <v>4732</v>
       </c>
-      <c r="D3" s="144" t="s">
+      <c r="D3" s="499" t="s">
         <v>4600</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="196" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="195" t="s">
+    <row r="4" spans="1:4" s="498" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="497" t="s">
         <v>4593</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="497" t="s">
         <v>4609</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="497" t="s">
         <v>4733</v>
       </c>
-      <c r="D4" s="195" t="s">
+      <c r="D4" s="497" t="s">
         <v>4601</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="198" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="197" t="s">
+    <row r="5" spans="1:4" s="502" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="501" t="s">
         <v>4594</v>
       </c>
-      <c r="B5" s="197" t="s">
+      <c r="B5" s="501" t="s">
         <v>4610</v>
       </c>
-      <c r="C5" s="197" t="s">
+      <c r="C5" s="501" t="s">
         <v>4734</v>
       </c>
-      <c r="D5" s="197" t="s">
+      <c r="D5" s="501" t="s">
         <v>4602</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="200" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="199" t="s">
+    <row r="6" spans="1:4" s="516" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="515" t="s">
         <v>4595</v>
       </c>
-      <c r="B6" s="199" t="s">
+      <c r="B6" s="515" t="s">
         <v>4611</v>
       </c>
-      <c r="C6" s="199" t="s">
+      <c r="C6" s="515" t="s">
         <v>4735</v>
       </c>
-      <c r="D6" s="199" t="s">
+      <c r="D6" s="515" t="s">
         <v>4603</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="202" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="201" t="s">
+    <row r="7" spans="1:4" s="518" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="517" t="s">
         <v>4596</v>
       </c>
-      <c r="B7" s="201" t="s">
+      <c r="B7" s="517" t="s">
         <v>4612</v>
       </c>
-      <c r="C7" s="201" t="s">
+      <c r="C7" s="517" t="s">
         <v>4736</v>
       </c>
-      <c r="D7" s="201" t="s">
+      <c r="D7" s="517" t="s">
         <v>4604</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="204" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="203" t="s">
+    <row r="8" spans="1:4" s="508" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="507" t="s">
         <v>4597</v>
       </c>
-      <c r="B8" s="203" t="s">
+      <c r="B8" s="507" t="s">
         <v>4613</v>
       </c>
-      <c r="C8" s="203" t="s">
+      <c r="C8" s="507" t="s">
         <v>4737</v>
       </c>
-      <c r="D8" s="203" t="s">
+      <c r="D8" s="507" t="s">
         <v>4605</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="150" t="s">
+    <row r="9" spans="1:4" s="504" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="503" t="s">
         <v>4598</v>
       </c>
-      <c r="B9" s="150" t="s">
+      <c r="B9" s="503" t="s">
         <v>4614</v>
       </c>
-      <c r="C9" s="150" t="s">
+      <c r="C9" s="503" t="s">
         <v>4738</v>
       </c>
-      <c r="D9" s="150" t="s">
+      <c r="D9" s="503" t="s">
         <v>4606</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+    <row r="10" spans="1:4" s="520" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="519" t="s">
+        <v>5621</v>
+      </c>
+      <c r="B10" s="519" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C10" s="519" t="s">
+        <v>2547</v>
+      </c>
+      <c r="D10" s="519" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="72" t="s">
         <v>4661</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B12" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C12" s="74" t="s">
         <v>1924</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D12" s="74" t="s">
         <v>1998</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="194" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="13" spans="1:4" s="506" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="505" t="s">
         <v>4591</v>
       </c>
-      <c r="B12" s="193" t="s">
+      <c r="B13" s="505" t="s">
         <v>4668</v>
       </c>
-      <c r="C12" s="193" t="s">
+      <c r="C13" s="505" t="s">
         <v>4739</v>
       </c>
-      <c r="D12" s="193" t="s">
+      <c r="D13" s="505" t="s">
         <v>4662</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="145" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144" t="s">
+    <row r="14" spans="1:4" s="500" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="499" t="s">
         <v>4592</v>
       </c>
-      <c r="B13" s="144" t="s">
+      <c r="B14" s="499" t="s">
         <v>4669</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C14" s="499" t="s">
         <v>4740</v>
       </c>
-      <c r="D13" s="144" t="s">
+      <c r="D14" s="499" t="s">
         <v>4663</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="196" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="195" t="s">
+    <row r="15" spans="1:4" s="498" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="497" t="s">
         <v>4593</v>
       </c>
-      <c r="B14" s="195" t="s">
+      <c r="B15" s="497" t="s">
         <v>4670</v>
       </c>
-      <c r="C14" s="195" t="s">
+      <c r="C15" s="497" t="s">
         <v>4741</v>
       </c>
-      <c r="D14" s="195" t="s">
+      <c r="D15" s="497" t="s">
         <v>4664</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="198" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="197" t="s">
+    <row r="16" spans="1:4" s="502" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="501" t="s">
         <v>4594</v>
       </c>
-      <c r="B15" s="197" t="s">
+      <c r="B16" s="501" t="s">
         <v>4671</v>
       </c>
-      <c r="C15" s="197" t="s">
+      <c r="C16" s="501" t="s">
         <v>4742</v>
       </c>
-      <c r="D15" s="197" t="s">
+      <c r="D16" s="501" t="s">
         <v>4665</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="204" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="203" t="s">
+    <row r="17" spans="1:4" s="508" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="507" t="s">
         <v>4597</v>
       </c>
-      <c r="B16" s="203" t="s">
+      <c r="B17" s="507" t="s">
         <v>4672</v>
       </c>
-      <c r="C16" s="203" t="s">
+      <c r="C17" s="507" t="s">
         <v>4743</v>
       </c>
-      <c r="D16" s="203" t="s">
+      <c r="D17" s="507" t="s">
         <v>4666</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="150" t="s">
+    <row r="18" spans="1:4" s="504" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="503" t="s">
         <v>4598</v>
       </c>
-      <c r="B17" s="150" t="s">
+      <c r="B18" s="503" t="s">
         <v>4673</v>
       </c>
-      <c r="C17" s="150" t="s">
+      <c r="C18" s="503" t="s">
         <v>4744</v>
       </c>
-      <c r="D17" s="150" t="s">
+      <c r="D18" s="503" t="s">
         <v>4667</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="72" t="s">
+    <row r="19" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:4" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="72" t="s">
         <v>2453</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B20" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C20" s="74" t="s">
         <v>1924</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D20" s="74" t="s">
         <v>1998</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="173" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="172" t="s">
+    <row r="21" spans="1:4" s="506" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="505" t="s">
         <v>4591</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B21" s="505" t="s">
         <v>4622</v>
       </c>
-      <c r="C20" s="172" t="s">
+      <c r="C21" s="505" t="s">
         <v>4745</v>
       </c>
-      <c r="D20" s="173" t="s">
+      <c r="D21" s="506" t="s">
         <v>4617</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="179" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="178" t="s">
+    <row r="22" spans="1:4" s="500" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="499" t="s">
         <v>4592</v>
       </c>
-      <c r="B21" s="178" t="s">
+      <c r="B22" s="499" t="s">
         <v>4623</v>
       </c>
-      <c r="C21" s="178" t="s">
+      <c r="C22" s="499" t="s">
         <v>4747</v>
       </c>
-      <c r="D21" s="179" t="s">
+      <c r="D22" s="500" t="s">
         <v>4618</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="175" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="174" t="s">
+    <row r="23" spans="1:4" s="512" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="511" t="s">
         <v>4615</v>
       </c>
-      <c r="B22" s="174" t="s">
+      <c r="B23" s="511" t="s">
         <v>4624</v>
       </c>
-      <c r="C22" s="174" t="s">
+      <c r="C23" s="511" t="s">
         <v>4746</v>
       </c>
-      <c r="D22" s="175" t="s">
+      <c r="D23" s="512" t="s">
         <v>4619</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="177" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="176" t="s">
+    <row r="24" spans="1:4" s="510" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="509" t="s">
         <v>4616</v>
       </c>
-      <c r="B23" s="176" t="s">
+      <c r="B24" s="509" t="s">
         <v>4625</v>
       </c>
-      <c r="C23" s="176" t="s">
+      <c r="C24" s="509" t="s">
         <v>4748</v>
       </c>
-      <c r="D23" s="177" t="s">
+      <c r="D24" s="510" t="s">
         <v>4620</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="150" t="s">
+    <row r="25" spans="1:4" s="508" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="507" t="s">
         <v>4597</v>
       </c>
-      <c r="B24" s="150" t="s">
+      <c r="B25" s="507" t="s">
         <v>4626</v>
       </c>
-      <c r="C24" s="150" t="s">
+      <c r="C25" s="507" t="s">
         <v>4749</v>
       </c>
-      <c r="D24" s="151" t="s">
+      <c r="D25" s="508" t="s">
         <v>4621</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="150" t="s">
+    <row r="26" spans="1:4" s="514" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="513" t="s">
         <v>5292</v>
       </c>
-      <c r="B25" s="150" t="s">
+      <c r="B26" s="513" t="s">
         <v>5294</v>
       </c>
-      <c r="C25" s="150"/>
-      <c r="D25" s="151" t="s">
+      <c r="C26" s="513" t="s">
+        <v>5622</v>
+      </c>
+      <c r="D26" s="514" t="s">
         <v>5293</v>
       </c>
     </row>
@@ -28784,17 +28988,17 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="78" spans="1:4" s="408" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="408" t="s">
+    <row r="78" spans="1:4" s="495" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="495" t="s">
         <v>4818</v>
       </c>
-      <c r="B78" s="408" t="s">
+      <c r="B78" s="495" t="s">
         <v>4914</v>
       </c>
-      <c r="C78" s="407" t="s">
+      <c r="C78" s="496" t="s">
         <v>5430</v>
       </c>
-      <c r="D78" s="408" t="s">
+      <c r="D78" s="495" t="s">
         <v>4866</v>
       </c>
     </row>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967E47B6-34E1-6749-8A4E-F5D2AD3ECCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12840" yWindow="760" windowWidth="17820" windowHeight="20080" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12840" yWindow="760" windowWidth="17820" windowHeight="20080" firstSheet="12" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="1" r:id="rId1"/>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,49 +8,63 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/EnterpriseAssistant/WebReferencias 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967E47B6-34E1-6749-8A4E-F5D2AD3ECCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F558348A-17DA-7A41-901B-5985A99A9A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12840" yWindow="760" windowWidth="17820" windowHeight="20080" firstSheet="12" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6880" yWindow="760" windowWidth="27780" windowHeight="20080" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="1" r:id="rId1"/>
     <sheet name="Mac - Mac" sheetId="35" r:id="rId2"/>
     <sheet name="Display" sheetId="3" r:id="rId3"/>
     <sheet name="iPad - A16" sheetId="4" r:id="rId4"/>
-    <sheet name="iPad - Mini 7" sheetId="5" r:id="rId5"/>
-    <sheet name="iPad - Air M4" sheetId="6" r:id="rId6"/>
-    <sheet name="iPad - Pro M5" sheetId="7" r:id="rId7"/>
-    <sheet name="iPad - Pencil &amp; Keyboard" sheetId="8" r:id="rId8"/>
-    <sheet name="iPhone - Duo" sheetId="9" r:id="rId9"/>
-    <sheet name="iPhone - 18" sheetId="10" r:id="rId10"/>
-    <sheet name="iPhone - 17" sheetId="12" r:id="rId11"/>
-    <sheet name="iPhone - Air" sheetId="15" r:id="rId12"/>
-    <sheet name="iPhone - 16" sheetId="17" r:id="rId13"/>
-    <sheet name="iPhone - Strap &amp; Wallet" sheetId="18" r:id="rId14"/>
-    <sheet name="iPhone - DEMO" sheetId="19" r:id="rId15"/>
-    <sheet name="Watch - SE3" sheetId="20" r:id="rId16"/>
-    <sheet name="Watch - Series 12" sheetId="21" r:id="rId17"/>
-    <sheet name="Watch - Ultra 4" sheetId="22" r:id="rId18"/>
-    <sheet name="Watch - Bands" sheetId="23" r:id="rId19"/>
-    <sheet name="Watch - Compatibility" sheetId="24" r:id="rId20"/>
-    <sheet name="Audio" sheetId="25" r:id="rId21"/>
-    <sheet name="Apple TV &amp; Acc." sheetId="26" r:id="rId22"/>
-    <sheet name="EOL - MacBook" sheetId="27" r:id="rId23"/>
-    <sheet name="EOL - Mac" sheetId="28" r:id="rId24"/>
-    <sheet name="EOL - iPad" sheetId="29" r:id="rId25"/>
-    <sheet name="EOL - iPhone" sheetId="30" r:id="rId26"/>
-    <sheet name="EOL - Strap &amp; Wallet" sheetId="31" r:id="rId27"/>
-    <sheet name="EOL - Apple Watch" sheetId="32" r:id="rId28"/>
-    <sheet name="EOL - Bands" sheetId="33" r:id="rId29"/>
-    <sheet name="EOL - Audio" sheetId="34" r:id="rId30"/>
-    <sheet name="EOL - Apple TV &amp; Acc." sheetId="36" r:id="rId31"/>
+    <sheet name="iPad - Mini 8" sheetId="37" r:id="rId5"/>
+    <sheet name="iPad - Mini 7" sheetId="5" r:id="rId6"/>
+    <sheet name="iPad - Air M4" sheetId="6" r:id="rId7"/>
+    <sheet name="iPad - Pro M5" sheetId="7" r:id="rId8"/>
+    <sheet name="iPad - Pencil &amp; Keyboard" sheetId="8" r:id="rId9"/>
+    <sheet name="iPhone - Duo" sheetId="9" r:id="rId10"/>
+    <sheet name="iPhone - 18" sheetId="10" r:id="rId11"/>
+    <sheet name="iPhone - 17" sheetId="12" r:id="rId12"/>
+    <sheet name="iPhone - Air" sheetId="15" r:id="rId13"/>
+    <sheet name="iPhone - 16" sheetId="17" r:id="rId14"/>
+    <sheet name="iPhone - Strap &amp; Wallet" sheetId="18" r:id="rId15"/>
+    <sheet name="iPhone - DEMO" sheetId="19" r:id="rId16"/>
+    <sheet name="Watch - SE3" sheetId="20" r:id="rId17"/>
+    <sheet name="Watch - Series 12" sheetId="21" r:id="rId18"/>
+    <sheet name="Watch - Ultra 4" sheetId="22" r:id="rId19"/>
+    <sheet name="Watch - Bands" sheetId="23" r:id="rId20"/>
+    <sheet name="Watch - Compatibility" sheetId="24" r:id="rId21"/>
+    <sheet name="Audio" sheetId="25" r:id="rId22"/>
+    <sheet name="Apple TV &amp; Acc." sheetId="26" r:id="rId23"/>
+    <sheet name="EOL - MacBook" sheetId="27" r:id="rId24"/>
+    <sheet name="EOL - Mac" sheetId="28" r:id="rId25"/>
+    <sheet name="EOL - iPad" sheetId="29" r:id="rId26"/>
+    <sheet name="EOL - iPhone" sheetId="30" r:id="rId27"/>
+    <sheet name="EOL - Strap &amp; Wallet" sheetId="31" r:id="rId28"/>
+    <sheet name="EOL - Apple Watch" sheetId="32" r:id="rId29"/>
+    <sheet name="EOL - Bands" sheetId="33" r:id="rId30"/>
+    <sheet name="EOL - Audio" sheetId="34" r:id="rId31"/>
+    <sheet name="EOL - Apple TV &amp; Acc." sheetId="36" r:id="rId32"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7918" uniqueCount="5754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8056" uniqueCount="5823">
   <si>
     <t>40mm Aluminium GPS</t>
   </si>
@@ -17312,6 +17326,213 @@
   </si>
   <si>
     <t>Duo (eSIM)</t>
+  </si>
+  <si>
+    <t>Mini 8ª Wifi</t>
+  </si>
+  <si>
+    <t>Mini 8ª LTE (eSIM)</t>
+  </si>
+  <si>
+    <t>MJ6F4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15336</t>
+  </si>
+  <si>
+    <t>152.170.15328</t>
+  </si>
+  <si>
+    <t>MJ6J4TY/A</t>
+  </si>
+  <si>
+    <t>MJ6R4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15344</t>
+  </si>
+  <si>
+    <t>152.170.15351</t>
+  </si>
+  <si>
+    <t>MJ6Q4TY/A</t>
+  </si>
+  <si>
+    <t>MJ6W4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15369</t>
+  </si>
+  <si>
+    <t>152.170.15377</t>
+  </si>
+  <si>
+    <t>MJ6V4TY/A</t>
+  </si>
+  <si>
+    <t>ML2T4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15385</t>
+  </si>
+  <si>
+    <t>152.170.15393</t>
+  </si>
+  <si>
+    <t>ML2Q4TY/A</t>
+  </si>
+  <si>
+    <t>MJ6X4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15419</t>
+  </si>
+  <si>
+    <t>152.170.15401</t>
+  </si>
+  <si>
+    <t>MJ6Y4TY/A</t>
+  </si>
+  <si>
+    <t>MJ684TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15427</t>
+  </si>
+  <si>
+    <t>MJ674TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15435</t>
+  </si>
+  <si>
+    <t>152.170.15443</t>
+  </si>
+  <si>
+    <t>MJ6D4TY/A</t>
+  </si>
+  <si>
+    <t>MJ6C4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15450</t>
+  </si>
+  <si>
+    <t>MJ6K4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15468</t>
+  </si>
+  <si>
+    <t>152.170.15476</t>
+  </si>
+  <si>
+    <t>MJ6H4TY/A</t>
+  </si>
+  <si>
+    <t>ML2X4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15484</t>
+  </si>
+  <si>
+    <t>152.170.15492</t>
+  </si>
+  <si>
+    <t>ML2W4TY/A</t>
+  </si>
+  <si>
+    <t>MJ6P4TY/A</t>
+  </si>
+  <si>
+    <t>152.170.15500</t>
+  </si>
+  <si>
+    <t>152.170.15518</t>
+  </si>
+  <si>
+    <t>MJ6M4TY/A</t>
+  </si>
+  <si>
+    <t>128GB Midnight</t>
+  </si>
+  <si>
+    <t>256GB Midnight</t>
+  </si>
+  <si>
+    <t>512GB Midnight</t>
+  </si>
+  <si>
+    <t>256GB Midnight NANO</t>
+  </si>
+  <si>
+    <t>256GB Starlight NANO</t>
+  </si>
+  <si>
+    <t>512GB Midnight NANO</t>
+  </si>
+  <si>
+    <t>512GB Starlight NANO</t>
+  </si>
+  <si>
+    <t>0195951205441</t>
+  </si>
+  <si>
+    <t>0195951205663</t>
+  </si>
+  <si>
+    <t>0195951422893</t>
+  </si>
+  <si>
+    <t>0195951207421</t>
+  </si>
+  <si>
+    <t>0195951268958</t>
+  </si>
+  <si>
+    <t>0195951269177</t>
+  </si>
+  <si>
+    <t>0195951207209</t>
+  </si>
+  <si>
+    <t>0195951269610</t>
+  </si>
+  <si>
+    <t>0195951403892</t>
+  </si>
+  <si>
+    <t>0195951206325</t>
+  </si>
+  <si>
+    <t>0195951268514</t>
+  </si>
+  <si>
+    <t>0195951268736</t>
+  </si>
+  <si>
+    <t>0195951207865</t>
+  </si>
+  <si>
+    <t>0195951269832</t>
+  </si>
+  <si>
+    <t>0195951269399</t>
+  </si>
+  <si>
+    <t>0195951207643</t>
+  </si>
+  <si>
+    <t>0195951206547</t>
+  </si>
+  <si>
+    <t>0195951270050</t>
+  </si>
+  <si>
+    <t>0195951404110</t>
+  </si>
+  <si>
+    <t>0195951423098</t>
   </si>
 </sst>
 </file>
@@ -17417,7 +17638,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="341">
+  <fills count="342">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -19458,6 +19679,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98A6AF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -19471,7 +19698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="612">
+  <cellXfs count="614">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -20152,6 +20379,8 @@
     <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="333" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="334" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="341" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="341" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20160,6 +20389,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDFDAD2"/>
+      <color rgb="FF98A6AF"/>
       <color rgb="FFADADAD"/>
       <color rgb="FFE2D1D4"/>
       <color rgb="FF7598C2"/>
@@ -21861,6 +22092,375 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D72"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A1" s="76" t="s">
+        <v>5753</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="316" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="315" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B3" s="315" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C3" s="316" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D3" s="316" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="316" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="315" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B5" s="315" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C5" s="316" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D5" s="316" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="317" customFormat="1" ht="17" customHeight="1">
+      <c r="A7" s="315" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B7" s="315" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C7" s="316" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D7" s="316" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="44" customFormat="1" ht="17" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="317" customFormat="1" ht="17" customHeight="1">
+      <c r="A9" s="315" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B9" s="316" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C9" s="316" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D9" s="316" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+    </row>
+    <row r="11" spans="1:4" s="580" customFormat="1" ht="17" customHeight="1">
+      <c r="A11" s="578" t="s">
+        <v>5633</v>
+      </c>
+      <c r="B11" s="579" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="579" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="579" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="13" t="s">
+        <v>5614</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="481" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="273" customFormat="1" ht="17" customHeight="1">
+      <c r="A13" s="272" t="s">
+        <v>5722</v>
+      </c>
+      <c r="B13" s="272" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="272" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="482" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>5717</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="481" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>5612</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D15" s="279" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>5613</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D16" s="279" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="581" customFormat="1" ht="15" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>5604</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D17" s="481" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="D18" s="481" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="336" customFormat="1" ht="15" customHeight="1">
+      <c r="A19" s="335" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B19" s="335" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C19" s="335" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D19" s="335" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="338" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="337" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B20" s="337" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C20" s="337" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D20" s="337" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="340" customFormat="1" ht="15" customHeight="1">
+      <c r="A21" s="339" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B21" s="339" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C21" s="339" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D21" s="339" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="342" customFormat="1" ht="15" customHeight="1">
+      <c r="A22" s="341" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B22" s="341" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C22" s="341" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D22" s="341" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="30" customFormat="1"/>
+    <row r="24" spans="1:4" s="30" customFormat="1"/>
+    <row r="25" spans="1:4" s="30" customFormat="1"/>
+    <row r="26" spans="1:4" s="30" customFormat="1"/>
+    <row r="27" spans="1:4" s="30" customFormat="1"/>
+    <row r="28" spans="1:4" s="30" customFormat="1"/>
+    <row r="29" spans="1:4" s="30" customFormat="1"/>
+    <row r="30" spans="1:4" s="30" customFormat="1"/>
+    <row r="31" spans="1:4" s="30" customFormat="1"/>
+    <row r="32" spans="1:4" s="30" customFormat="1"/>
+    <row r="33" s="30" customFormat="1"/>
+    <row r="34" s="30" customFormat="1"/>
+    <row r="35" s="30" customFormat="1"/>
+    <row r="36" s="30" customFormat="1"/>
+    <row r="37" s="30" customFormat="1"/>
+    <row r="38" s="30" customFormat="1"/>
+    <row r="39" s="30" customFormat="1"/>
+    <row r="40" s="30" customFormat="1"/>
+    <row r="41" s="30" customFormat="1"/>
+    <row r="42" s="30" customFormat="1"/>
+    <row r="43" s="30" customFormat="1"/>
+    <row r="44" s="30" customFormat="1"/>
+    <row r="45" s="30" customFormat="1"/>
+    <row r="46" s="30" customFormat="1"/>
+    <row r="47" s="30" customFormat="1"/>
+    <row r="48" s="30" customFormat="1"/>
+    <row r="49" s="30" customFormat="1"/>
+    <row r="50" s="30" customFormat="1"/>
+    <row r="51" s="30" customFormat="1"/>
+    <row r="52" s="30" customFormat="1"/>
+    <row r="53" s="30" customFormat="1"/>
+    <row r="54" s="30" customFormat="1"/>
+    <row r="55" s="30" customFormat="1"/>
+    <row r="56" s="30" customFormat="1"/>
+    <row r="57" s="30" customFormat="1"/>
+    <row r="58" s="30" customFormat="1"/>
+    <row r="59" s="30" customFormat="1"/>
+    <row r="60" s="30" customFormat="1"/>
+    <row r="61" s="30" customFormat="1"/>
+    <row r="62" s="30" customFormat="1"/>
+    <row r="63" s="30" customFormat="1"/>
+    <row r="64" s="30" customFormat="1"/>
+    <row r="65" s="30" customFormat="1"/>
+    <row r="66" s="30" customFormat="1"/>
+    <row r="67" s="30" customFormat="1"/>
+    <row r="68" s="30" customFormat="1"/>
+    <row r="69" s="30" customFormat="1"/>
+    <row r="70" s="30" customFormat="1"/>
+    <row r="71" s="30" customFormat="1"/>
+    <row r="72" s="30" customFormat="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -22941,7 +23541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -24452,7 +25052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -24893,7 +25493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -25143,7 +25743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -25499,7 +26099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -25877,7 +26477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -26504,7 +27104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -28048,7 +28648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -28477,7 +29077,713 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBB9CD7-BB22-0049-A38F-216801BD89CE}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="60.1640625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A1" s="76" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="22" t="s">
+        <v>5593</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2" s="487" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="26" t="s">
+        <v>5594</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="D3" s="488" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>5595</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" s="489" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>5596</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="484" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="22" t="s">
+        <v>5638</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="487" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="26" t="s">
+        <v>5639</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="488" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="24" t="s">
+        <v>5640</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="489" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>5641</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" s="484" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>5642</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="484" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="22" t="s">
+        <v>5643</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="D11" s="487" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>5644</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" s="488" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="24" t="s">
+        <v>5645</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" s="489" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>5646</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D14" s="484" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A15" s="22" t="s">
+        <v>5647</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="487" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A16" s="26" t="s">
+        <v>5648</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="488" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
+      <c r="A17" s="24" t="s">
+        <v>5649</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="D17" s="489" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>5650</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D18" s="484" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="30" customFormat="1" ht="16"/>
+    <row r="20" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="76" t="s">
+        <v>5589</v>
+      </c>
+      <c r="B20" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="29" customFormat="1" ht="15" customHeight="1">
+      <c r="A21" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
+      <c r="A22" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
+      <c r="A23" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
+      <c r="A24" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" s="113"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="113"/>
+    </row>
+    <row r="26" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="30" customFormat="1" ht="16"/>
+    <row r="37" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
+      <c r="A37" s="76" t="s">
+        <v>5590</v>
+      </c>
+      <c r="B37" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
+      <c r="A38" s="28" t="s">
+        <v>5591</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
+      <c r="A39" s="28" t="s">
+        <v>5592</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B40" s="113"/>
+      <c r="C40" s="113"/>
+      <c r="D40" s="113"/>
+    </row>
+    <row r="41" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A41" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A42" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A44" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A45" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A47" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A48" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A49" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A50" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="29" customFormat="1">
+      <c r="C51" s="78"/>
+    </row>
+    <row r="52" spans="1:4" s="29" customFormat="1">
+      <c r="C52" s="78"/>
+    </row>
+    <row r="53" spans="1:4" s="29" customFormat="1">
+      <c r="C53" s="78"/>
+    </row>
+    <row r="54" spans="1:4" s="29" customFormat="1">
+      <c r="C54" s="78"/>
+    </row>
+    <row r="55" spans="1:4" s="29" customFormat="1">
+      <c r="C55" s="78"/>
+    </row>
+    <row r="56" spans="1:4" s="29" customFormat="1">
+      <c r="C56" s="78"/>
+    </row>
+    <row r="57" spans="1:4" s="29" customFormat="1">
+      <c r="C57" s="78"/>
+    </row>
+    <row r="58" spans="1:4" s="29" customFormat="1">
+      <c r="C58" s="78"/>
+    </row>
+    <row r="59" spans="1:4" s="29" customFormat="1">
+      <c r="C59" s="78"/>
+    </row>
+    <row r="60" spans="1:4" s="29" customFormat="1">
+      <c r="C60" s="78"/>
+    </row>
+    <row r="61" spans="1:4" s="29" customFormat="1">
+      <c r="C61" s="78"/>
+    </row>
+    <row r="62" spans="1:4" s="29" customFormat="1">
+      <c r="C62" s="78"/>
+    </row>
+    <row r="63" spans="1:4" s="29" customFormat="1">
+      <c r="C63" s="78"/>
+    </row>
+    <row r="64" spans="1:4" s="29" customFormat="1">
+      <c r="C64" s="78"/>
+    </row>
+    <row r="65" spans="3:3" s="29" customFormat="1">
+      <c r="C65" s="78"/>
+    </row>
+    <row r="66" spans="3:3" s="29" customFormat="1">
+      <c r="C66" s="78"/>
+    </row>
+    <row r="67" spans="3:3" s="29" customFormat="1">
+      <c r="C67" s="78"/>
+    </row>
+    <row r="68" spans="3:3" s="29" customFormat="1">
+      <c r="C68" s="78"/>
+    </row>
+    <row r="69" spans="3:3" s="29" customFormat="1">
+      <c r="C69" s="78"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -31441,713 +32747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBB9CD7-BB22-0049-A38F-216801BD89CE}">
-  <dimension ref="A1:D69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="60.1640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="76" t="s">
-        <v>296</v>
-      </c>
-      <c r="B1" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>5593</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="D2" s="487" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="26" t="s">
-        <v>5594</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="488" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>5595</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="D4" s="489" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>5596</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" s="484" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>5638</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="D6" s="487" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="26" t="s">
-        <v>5639</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="D7" s="488" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="24" t="s">
-        <v>5640</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="D8" s="489" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>5641</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D9" s="484" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>5642</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D10" s="484" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="22" t="s">
-        <v>5643</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="D11" s="487" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="26" t="s">
-        <v>5644</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="D12" s="488" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="24" t="s">
-        <v>5645</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="489" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>5646</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D14" s="484" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="22" t="s">
-        <v>5647</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="D15" s="487" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="26" t="s">
-        <v>5648</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="D16" s="488" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="24" t="s">
-        <v>5649</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="D17" s="489" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>5650</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D18" s="484" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="30" customFormat="1" ht="16"/>
-    <row r="20" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="76" t="s">
-        <v>5589</v>
-      </c>
-      <c r="B20" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="70" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="29" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>348</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>352</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>356</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>358</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>360</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B25" s="113"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="113"/>
-    </row>
-    <row r="26" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="30" customFormat="1" ht="16"/>
-    <row r="37" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
-      <c r="A37" s="76" t="s">
-        <v>5590</v>
-      </c>
-      <c r="B37" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" s="70" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>5591</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>364</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="30" customFormat="1" ht="17" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>5592</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="D39" s="28" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B40" s="113"/>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
-    </row>
-    <row r="41" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A41" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A42" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A44" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A45" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A47" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A48" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A49" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A50" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" s="29" customFormat="1">
-      <c r="C51" s="78"/>
-    </row>
-    <row r="52" spans="1:4" s="29" customFormat="1">
-      <c r="C52" s="78"/>
-    </row>
-    <row r="53" spans="1:4" s="29" customFormat="1">
-      <c r="C53" s="78"/>
-    </row>
-    <row r="54" spans="1:4" s="29" customFormat="1">
-      <c r="C54" s="78"/>
-    </row>
-    <row r="55" spans="1:4" s="29" customFormat="1">
-      <c r="C55" s="78"/>
-    </row>
-    <row r="56" spans="1:4" s="29" customFormat="1">
-      <c r="C56" s="78"/>
-    </row>
-    <row r="57" spans="1:4" s="29" customFormat="1">
-      <c r="C57" s="78"/>
-    </row>
-    <row r="58" spans="1:4" s="29" customFormat="1">
-      <c r="C58" s="78"/>
-    </row>
-    <row r="59" spans="1:4" s="29" customFormat="1">
-      <c r="C59" s="78"/>
-    </row>
-    <row r="60" spans="1:4" s="29" customFormat="1">
-      <c r="C60" s="78"/>
-    </row>
-    <row r="61" spans="1:4" s="29" customFormat="1">
-      <c r="C61" s="78"/>
-    </row>
-    <row r="62" spans="1:4" s="29" customFormat="1">
-      <c r="C62" s="78"/>
-    </row>
-    <row r="63" spans="1:4" s="29" customFormat="1">
-      <c r="C63" s="78"/>
-    </row>
-    <row r="64" spans="1:4" s="29" customFormat="1">
-      <c r="C64" s="78"/>
-    </row>
-    <row r="65" spans="3:3" s="29" customFormat="1">
-      <c r="C65" s="78"/>
-    </row>
-    <row r="66" spans="3:3" s="29" customFormat="1">
-      <c r="C66" s="78"/>
-    </row>
-    <row r="67" spans="3:3" s="29" customFormat="1">
-      <c r="C67" s="78"/>
-    </row>
-    <row r="68" spans="3:3" s="29" customFormat="1">
-      <c r="C68" s="78"/>
-    </row>
-    <row r="69" spans="3:3" s="29" customFormat="1">
-      <c r="C69" s="78"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A2:F87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -32410,7 +33010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -32813,7 +33413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
@@ -33725,7 +34325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:XFD117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
@@ -51323,7 +51923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -51875,7 +52475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C284"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -54872,7 +55472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -56349,7 +56949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -56607,7 +57207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:D236"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -59391,2304 +59991,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
-  <dimension ref="A1:D169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="52.83203125" style="136" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="136" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.1640625" style="136" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="136" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="136"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="77" customFormat="1">
-      <c r="A1" s="68" t="s">
-        <v>2043</v>
-      </c>
-      <c r="B1" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="182" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="202" customFormat="1">
-      <c r="A2" s="201" t="s">
-        <v>4920</v>
-      </c>
-      <c r="B2" s="201" t="s">
-        <v>4921</v>
-      </c>
-      <c r="C2" s="201" t="s">
-        <v>4922</v>
-      </c>
-      <c r="D2" s="555" t="s">
-        <v>4923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="216" customFormat="1">
-      <c r="A3" s="215" t="s">
-        <v>4924</v>
-      </c>
-      <c r="B3" s="215" t="s">
-        <v>4925</v>
-      </c>
-      <c r="C3" s="215" t="s">
-        <v>4926</v>
-      </c>
-      <c r="D3" s="556" t="s">
-        <v>4927</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="217" customFormat="1">
-      <c r="A4" s="218" t="s">
-        <v>4928</v>
-      </c>
-      <c r="B4" s="218" t="s">
-        <v>4929</v>
-      </c>
-      <c r="C4" s="218" t="s">
-        <v>4930</v>
-      </c>
-      <c r="D4" s="557" t="s">
-        <v>4931</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="204" customFormat="1">
-      <c r="A5" s="203" t="s">
-        <v>4932</v>
-      </c>
-      <c r="B5" s="203" t="s">
-        <v>4933</v>
-      </c>
-      <c r="C5" s="203" t="s">
-        <v>4934</v>
-      </c>
-      <c r="D5" s="558" t="s">
-        <v>4935</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="219" customFormat="1">
-      <c r="A6" s="220" t="s">
-        <v>4936</v>
-      </c>
-      <c r="B6" s="220" t="s">
-        <v>4937</v>
-      </c>
-      <c r="C6" s="220" t="s">
-        <v>4938</v>
-      </c>
-      <c r="D6" s="559" t="s">
-        <v>4939</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="208" customFormat="1">
-      <c r="A7" s="207" t="s">
-        <v>4940</v>
-      </c>
-      <c r="B7" s="207" t="s">
-        <v>4941</v>
-      </c>
-      <c r="C7" s="207" t="s">
-        <v>4942</v>
-      </c>
-      <c r="D7" s="560" t="s">
-        <v>4943</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="175" customFormat="1">
-      <c r="A8" s="51" t="s">
-        <v>4944</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>4945</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>4946</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>4947</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="212" customFormat="1">
-      <c r="A9" s="211" t="s">
-        <v>4948</v>
-      </c>
-      <c r="B9" s="211" t="s">
-        <v>4949</v>
-      </c>
-      <c r="C9" s="211" t="s">
-        <v>4950</v>
-      </c>
-      <c r="D9" s="561" t="s">
-        <v>4951</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="213" customFormat="1">
-      <c r="A10" s="213" t="s">
-        <v>4952</v>
-      </c>
-      <c r="B10" s="213" t="s">
-        <v>4953</v>
-      </c>
-      <c r="C10" s="214" t="s">
-        <v>4954</v>
-      </c>
-      <c r="D10" s="562" t="s">
-        <v>4955</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="205" customFormat="1">
-      <c r="A11" s="205" t="s">
-        <v>4956</v>
-      </c>
-      <c r="B11" s="205" t="s">
-        <v>4957</v>
-      </c>
-      <c r="C11" s="206" t="s">
-        <v>4958</v>
-      </c>
-      <c r="D11" s="563" t="s">
-        <v>4959</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="202" customFormat="1">
-      <c r="A12" s="202" t="s">
-        <v>4960</v>
-      </c>
-      <c r="B12" s="202" t="s">
-        <v>4961</v>
-      </c>
-      <c r="C12" s="201" t="s">
-        <v>4962</v>
-      </c>
-      <c r="D12" s="555" t="s">
-        <v>4963</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="216" customFormat="1">
-      <c r="A13" s="216" t="s">
-        <v>4964</v>
-      </c>
-      <c r="B13" s="216" t="s">
-        <v>4965</v>
-      </c>
-      <c r="C13" s="215" t="s">
-        <v>4966</v>
-      </c>
-      <c r="D13" s="556" t="s">
-        <v>4967</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="217" customFormat="1">
-      <c r="A14" s="217" t="s">
-        <v>4968</v>
-      </c>
-      <c r="B14" s="217" t="s">
-        <v>4969</v>
-      </c>
-      <c r="C14" s="218" t="s">
-        <v>4970</v>
-      </c>
-      <c r="D14" s="557" t="s">
-        <v>4971</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="204" customFormat="1">
-      <c r="A15" s="204" t="s">
-        <v>4972</v>
-      </c>
-      <c r="B15" s="204" t="s">
-        <v>4973</v>
-      </c>
-      <c r="C15" s="203" t="s">
-        <v>4974</v>
-      </c>
-      <c r="D15" s="558" t="s">
-        <v>4975</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="219" customFormat="1">
-      <c r="A16" s="219" t="s">
-        <v>4976</v>
-      </c>
-      <c r="B16" s="219" t="s">
-        <v>4977</v>
-      </c>
-      <c r="C16" s="220" t="s">
-        <v>4978</v>
-      </c>
-      <c r="D16" s="559" t="s">
-        <v>4979</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="208" customFormat="1">
-      <c r="A17" s="208" t="s">
-        <v>4980</v>
-      </c>
-      <c r="B17" s="208" t="s">
-        <v>4981</v>
-      </c>
-      <c r="C17" s="207" t="s">
-        <v>4982</v>
-      </c>
-      <c r="D17" s="560" t="s">
-        <v>4983</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="175" customFormat="1">
-      <c r="A18" s="175" t="s">
-        <v>4984</v>
-      </c>
-      <c r="B18" s="175" t="s">
-        <v>4985</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>4986</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>4987</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="212" customFormat="1">
-      <c r="A19" s="212" t="s">
-        <v>4988</v>
-      </c>
-      <c r="B19" s="212" t="s">
-        <v>4989</v>
-      </c>
-      <c r="C19" s="211" t="s">
-        <v>4990</v>
-      </c>
-      <c r="D19" s="561" t="s">
-        <v>4991</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="213" customFormat="1">
-      <c r="A20" s="213" t="s">
-        <v>4992</v>
-      </c>
-      <c r="B20" s="213" t="s">
-        <v>4993</v>
-      </c>
-      <c r="C20" s="214" t="s">
-        <v>4994</v>
-      </c>
-      <c r="D20" s="562" t="s">
-        <v>4995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="205" customFormat="1">
-      <c r="A21" s="205" t="s">
-        <v>4996</v>
-      </c>
-      <c r="B21" s="205" t="s">
-        <v>4997</v>
-      </c>
-      <c r="C21" s="206" t="s">
-        <v>4998</v>
-      </c>
-      <c r="D21" s="563" t="s">
-        <v>4999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="202" customFormat="1">
-      <c r="A22" s="202" t="s">
-        <v>5000</v>
-      </c>
-      <c r="B22" s="202" t="s">
-        <v>5001</v>
-      </c>
-      <c r="C22" s="201" t="s">
-        <v>5002</v>
-      </c>
-      <c r="D22" s="555" t="s">
-        <v>5003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="216" customFormat="1">
-      <c r="A23" s="216" t="s">
-        <v>5004</v>
-      </c>
-      <c r="B23" s="216" t="s">
-        <v>5005</v>
-      </c>
-      <c r="C23" s="215" t="s">
-        <v>5006</v>
-      </c>
-      <c r="D23" s="556" t="s">
-        <v>5007</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="217" customFormat="1">
-      <c r="A24" s="217" t="s">
-        <v>5008</v>
-      </c>
-      <c r="B24" s="217" t="s">
-        <v>5009</v>
-      </c>
-      <c r="C24" s="218" t="s">
-        <v>5010</v>
-      </c>
-      <c r="D24" s="557" t="s">
-        <v>5011</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="204" customFormat="1">
-      <c r="A25" s="204" t="s">
-        <v>5012</v>
-      </c>
-      <c r="B25" s="204" t="s">
-        <v>5013</v>
-      </c>
-      <c r="C25" s="203" t="s">
-        <v>5014</v>
-      </c>
-      <c r="D25" s="558" t="s">
-        <v>5015</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="219" customFormat="1">
-      <c r="A26" s="219" t="s">
-        <v>5016</v>
-      </c>
-      <c r="B26" s="219" t="s">
-        <v>5017</v>
-      </c>
-      <c r="C26" s="220" t="s">
-        <v>5018</v>
-      </c>
-      <c r="D26" s="559" t="s">
-        <v>5019</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="219" customFormat="1">
-      <c r="A27" s="219" t="s">
-        <v>5020</v>
-      </c>
-      <c r="B27" s="219" t="s">
-        <v>5021</v>
-      </c>
-      <c r="C27" s="220" t="s">
-        <v>5022</v>
-      </c>
-      <c r="D27" s="559" t="s">
-        <v>5023</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="208" customFormat="1">
-      <c r="A28" s="208" t="s">
-        <v>5024</v>
-      </c>
-      <c r="B28" s="208" t="s">
-        <v>5025</v>
-      </c>
-      <c r="C28" s="207" t="s">
-        <v>5026</v>
-      </c>
-      <c r="D28" s="560" t="s">
-        <v>5027</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="175" customFormat="1">
-      <c r="A29" s="175" t="s">
-        <v>5028</v>
-      </c>
-      <c r="B29" s="175" t="s">
-        <v>5029</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>5030</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>5031</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="212" customFormat="1">
-      <c r="A30" s="212" t="s">
-        <v>5032</v>
-      </c>
-      <c r="B30" s="212" t="s">
-        <v>5033</v>
-      </c>
-      <c r="C30" s="211" t="s">
-        <v>5034</v>
-      </c>
-      <c r="D30" s="561" t="s">
-        <v>5035</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="213" customFormat="1">
-      <c r="A31" s="213" t="s">
-        <v>5036</v>
-      </c>
-      <c r="B31" s="213" t="s">
-        <v>5037</v>
-      </c>
-      <c r="C31" s="214" t="s">
-        <v>5038</v>
-      </c>
-      <c r="D31" s="562" t="s">
-        <v>5039</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="205" customFormat="1">
-      <c r="A32" s="205" t="s">
-        <v>5040</v>
-      </c>
-      <c r="B32" s="205" t="s">
-        <v>5041</v>
-      </c>
-      <c r="C32" s="206" t="s">
-        <v>5042</v>
-      </c>
-      <c r="D32" s="563" t="s">
-        <v>5043</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="77" customFormat="1">
-      <c r="A33" s="68"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="68"/>
-      <c r="D33" s="182"/>
-    </row>
-    <row r="34" spans="1:4" s="77" customFormat="1">
-      <c r="A34" s="68" t="s">
-        <v>2189</v>
-      </c>
-      <c r="B34" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="182" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="208" customFormat="1">
-      <c r="A35" s="207" t="s">
-        <v>5044</v>
-      </c>
-      <c r="B35" s="207" t="s">
-        <v>5045</v>
-      </c>
-      <c r="C35" s="207" t="s">
-        <v>5046</v>
-      </c>
-      <c r="D35" s="560" t="s">
-        <v>5047</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="208" customFormat="1">
-      <c r="A36" s="209" t="s">
-        <v>5048</v>
-      </c>
-      <c r="B36" s="210" t="s">
-        <v>5049</v>
-      </c>
-      <c r="C36" s="207" t="s">
-        <v>5050</v>
-      </c>
-      <c r="D36" s="207" t="s">
-        <v>5051</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="175" customFormat="1">
-      <c r="A37" s="51" t="s">
-        <v>5052</v>
-      </c>
-      <c r="B37" s="51" t="s">
-        <v>5053</v>
-      </c>
-      <c r="C37" s="51" t="s">
-        <v>5054</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>5055</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="175" customFormat="1">
-      <c r="A38" s="51" t="s">
-        <v>5056</v>
-      </c>
-      <c r="B38" s="51" t="s">
-        <v>5057</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>5058</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>5059</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="212" customFormat="1">
-      <c r="A39" s="211" t="s">
-        <v>5060</v>
-      </c>
-      <c r="B39" s="211" t="s">
-        <v>5061</v>
-      </c>
-      <c r="C39" s="211" t="s">
-        <v>5062</v>
-      </c>
-      <c r="D39" s="561" t="s">
-        <v>5063</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="212" customFormat="1">
-      <c r="A40" s="211" t="s">
-        <v>5064</v>
-      </c>
-      <c r="B40" s="211" t="s">
-        <v>5065</v>
-      </c>
-      <c r="C40" s="211" t="s">
-        <v>5066</v>
-      </c>
-      <c r="D40" s="561" t="s">
-        <v>5067</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" s="213" customFormat="1">
-      <c r="A41" s="214" t="s">
-        <v>5068</v>
-      </c>
-      <c r="B41" s="214" t="s">
-        <v>5069</v>
-      </c>
-      <c r="C41" s="214" t="s">
-        <v>5070</v>
-      </c>
-      <c r="D41" s="562" t="s">
-        <v>5071</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="213" customFormat="1">
-      <c r="A42" s="214" t="s">
-        <v>5072</v>
-      </c>
-      <c r="B42" s="214" t="s">
-        <v>5073</v>
-      </c>
-      <c r="C42" s="214" t="s">
-        <v>5074</v>
-      </c>
-      <c r="D42" s="562" t="s">
-        <v>5075</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" s="205" customFormat="1">
-      <c r="A43" s="206" t="s">
-        <v>5076</v>
-      </c>
-      <c r="B43" s="206" t="s">
-        <v>5077</v>
-      </c>
-      <c r="C43" s="206" t="s">
-        <v>5078</v>
-      </c>
-      <c r="D43" s="563" t="s">
-        <v>5079</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" s="205" customFormat="1">
-      <c r="A44" s="206" t="s">
-        <v>5080</v>
-      </c>
-      <c r="B44" s="206" t="s">
-        <v>5081</v>
-      </c>
-      <c r="C44" s="206" t="s">
-        <v>5082</v>
-      </c>
-      <c r="D44" s="563" t="s">
-        <v>5083</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" s="204" customFormat="1">
-      <c r="A45" s="204" t="s">
-        <v>5084</v>
-      </c>
-      <c r="B45" s="204" t="s">
-        <v>5085</v>
-      </c>
-      <c r="C45" s="203" t="s">
-        <v>5086</v>
-      </c>
-      <c r="D45" s="558" t="s">
-        <v>5087</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" s="204" customFormat="1">
-      <c r="A46" s="204" t="s">
-        <v>5088</v>
-      </c>
-      <c r="B46" s="204" t="s">
-        <v>5089</v>
-      </c>
-      <c r="C46" s="203" t="s">
-        <v>5090</v>
-      </c>
-      <c r="D46" s="558" t="s">
-        <v>5091</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" s="202" customFormat="1">
-      <c r="A47" s="202" t="s">
-        <v>5092</v>
-      </c>
-      <c r="B47" s="202" t="s">
-        <v>5093</v>
-      </c>
-      <c r="C47" s="201" t="s">
-        <v>5094</v>
-      </c>
-      <c r="D47" s="555" t="s">
-        <v>5095</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" s="202" customFormat="1">
-      <c r="A48" s="202" t="s">
-        <v>5096</v>
-      </c>
-      <c r="B48" s="202" t="s">
-        <v>5097</v>
-      </c>
-      <c r="C48" s="201" t="s">
-        <v>5098</v>
-      </c>
-      <c r="D48" s="555" t="s">
-        <v>5099</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" s="217" customFormat="1">
-      <c r="A49" s="217" t="s">
-        <v>5100</v>
-      </c>
-      <c r="B49" s="217" t="s">
-        <v>5101</v>
-      </c>
-      <c r="C49" s="218" t="s">
-        <v>5102</v>
-      </c>
-      <c r="D49" s="557" t="s">
-        <v>5103</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" s="217" customFormat="1">
-      <c r="A50" s="217" t="s">
-        <v>5104</v>
-      </c>
-      <c r="B50" s="217" t="s">
-        <v>5105</v>
-      </c>
-      <c r="C50" s="218" t="s">
-        <v>5106</v>
-      </c>
-      <c r="D50" s="557" t="s">
-        <v>5107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" s="204" customFormat="1">
-      <c r="A51" s="204" t="s">
-        <v>5108</v>
-      </c>
-      <c r="B51" s="204" t="s">
-        <v>5109</v>
-      </c>
-      <c r="C51" s="203" t="s">
-        <v>5110</v>
-      </c>
-      <c r="D51" s="558" t="s">
-        <v>5111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" s="204" customFormat="1">
-      <c r="A52" s="204" t="s">
-        <v>5112</v>
-      </c>
-      <c r="B52" s="204" t="s">
-        <v>5113</v>
-      </c>
-      <c r="C52" s="203" t="s">
-        <v>5114</v>
-      </c>
-      <c r="D52" s="558" t="s">
-        <v>5115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" s="202" customFormat="1">
-      <c r="A53" s="202" t="s">
-        <v>5116</v>
-      </c>
-      <c r="B53" s="202" t="s">
-        <v>5117</v>
-      </c>
-      <c r="C53" s="201" t="s">
-        <v>5118</v>
-      </c>
-      <c r="D53" s="555" t="s">
-        <v>5119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" s="202" customFormat="1">
-      <c r="A54" s="202" t="s">
-        <v>5120</v>
-      </c>
-      <c r="B54" s="202" t="s">
-        <v>5121</v>
-      </c>
-      <c r="C54" s="201" t="s">
-        <v>5122</v>
-      </c>
-      <c r="D54" s="555" t="s">
-        <v>5123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" s="217" customFormat="1">
-      <c r="A55" s="217" t="s">
-        <v>5124</v>
-      </c>
-      <c r="B55" s="217" t="s">
-        <v>5125</v>
-      </c>
-      <c r="C55" s="218" t="s">
-        <v>5126</v>
-      </c>
-      <c r="D55" s="557" t="s">
-        <v>5127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" s="217" customFormat="1">
-      <c r="A56" s="217" t="s">
-        <v>5128</v>
-      </c>
-      <c r="B56" s="217" t="s">
-        <v>5129</v>
-      </c>
-      <c r="C56" s="218" t="s">
-        <v>5130</v>
-      </c>
-      <c r="D56" s="557" t="s">
-        <v>5131</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" s="208" customFormat="1">
-      <c r="A57" s="208" t="s">
-        <v>5132</v>
-      </c>
-      <c r="B57" s="208" t="s">
-        <v>5133</v>
-      </c>
-      <c r="C57" s="207" t="s">
-        <v>5134</v>
-      </c>
-      <c r="D57" s="560" t="s">
-        <v>5135</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" s="208" customFormat="1">
-      <c r="A58" s="208" t="s">
-        <v>5136</v>
-      </c>
-      <c r="B58" s="208" t="s">
-        <v>5137</v>
-      </c>
-      <c r="C58" s="207" t="s">
-        <v>5138</v>
-      </c>
-      <c r="D58" s="560" t="s">
-        <v>5139</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" s="175" customFormat="1">
-      <c r="A59" s="175" t="s">
-        <v>5140</v>
-      </c>
-      <c r="B59" s="175" t="s">
-        <v>5141</v>
-      </c>
-      <c r="C59" s="51" t="s">
-        <v>5142</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>5143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" s="175" customFormat="1">
-      <c r="A60" s="175" t="s">
-        <v>5144</v>
-      </c>
-      <c r="B60" s="175" t="s">
-        <v>5145</v>
-      </c>
-      <c r="C60" s="51" t="s">
-        <v>5146</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>5147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" s="212" customFormat="1">
-      <c r="A61" s="212" t="s">
-        <v>5148</v>
-      </c>
-      <c r="B61" s="212" t="s">
-        <v>5149</v>
-      </c>
-      <c r="C61" s="211" t="s">
-        <v>5150</v>
-      </c>
-      <c r="D61" s="561" t="s">
-        <v>5151</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" s="212" customFormat="1">
-      <c r="A62" s="212" t="s">
-        <v>5152</v>
-      </c>
-      <c r="B62" s="212" t="s">
-        <v>5153</v>
-      </c>
-      <c r="C62" s="211" t="s">
-        <v>5154</v>
-      </c>
-      <c r="D62" s="561" t="s">
-        <v>5155</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" s="213" customFormat="1">
-      <c r="A63" s="213" t="s">
-        <v>5156</v>
-      </c>
-      <c r="B63" s="213" t="s">
-        <v>5157</v>
-      </c>
-      <c r="C63" s="214" t="s">
-        <v>5158</v>
-      </c>
-      <c r="D63" s="562" t="s">
-        <v>5159</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" s="213" customFormat="1">
-      <c r="A64" s="213" t="s">
-        <v>5160</v>
-      </c>
-      <c r="B64" s="213" t="s">
-        <v>5161</v>
-      </c>
-      <c r="C64" s="214" t="s">
-        <v>5162</v>
-      </c>
-      <c r="D64" s="562" t="s">
-        <v>5163</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" s="205" customFormat="1">
-      <c r="A65" s="205" t="s">
-        <v>5164</v>
-      </c>
-      <c r="B65" s="205" t="s">
-        <v>5165</v>
-      </c>
-      <c r="C65" s="206" t="s">
-        <v>5166</v>
-      </c>
-      <c r="D65" s="563" t="s">
-        <v>5167</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" s="205" customFormat="1">
-      <c r="A66" s="205" t="s">
-        <v>5168</v>
-      </c>
-      <c r="B66" s="205" t="s">
-        <v>5169</v>
-      </c>
-      <c r="C66" s="206" t="s">
-        <v>5170</v>
-      </c>
-      <c r="D66" s="563" t="s">
-        <v>5171</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" s="204" customFormat="1">
-      <c r="A67" s="204" t="s">
-        <v>5172</v>
-      </c>
-      <c r="B67" s="204" t="s">
-        <v>5173</v>
-      </c>
-      <c r="C67" s="203" t="s">
-        <v>5174</v>
-      </c>
-      <c r="D67" s="558" t="s">
-        <v>5175</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" s="204" customFormat="1">
-      <c r="A68" s="204" t="s">
-        <v>5176</v>
-      </c>
-      <c r="B68" s="204" t="s">
-        <v>5177</v>
-      </c>
-      <c r="C68" s="203" t="s">
-        <v>5178</v>
-      </c>
-      <c r="D68" s="558" t="s">
-        <v>5179</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" s="202" customFormat="1">
-      <c r="A69" s="202" t="s">
-        <v>5180</v>
-      </c>
-      <c r="B69" s="202" t="s">
-        <v>5181</v>
-      </c>
-      <c r="C69" s="201" t="s">
-        <v>5182</v>
-      </c>
-      <c r="D69" s="555" t="s">
-        <v>5183</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" s="202" customFormat="1">
-      <c r="A70" s="202" t="s">
-        <v>5184</v>
-      </c>
-      <c r="B70" s="202" t="s">
-        <v>5185</v>
-      </c>
-      <c r="C70" s="201" t="s">
-        <v>5186</v>
-      </c>
-      <c r="D70" s="555" t="s">
-        <v>5187</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" s="217" customFormat="1">
-      <c r="A71" s="217" t="s">
-        <v>5188</v>
-      </c>
-      <c r="B71" s="217" t="s">
-        <v>5189</v>
-      </c>
-      <c r="C71" s="218" t="s">
-        <v>5190</v>
-      </c>
-      <c r="D71" s="557" t="s">
-        <v>5191</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" s="217" customFormat="1">
-      <c r="A72" s="217" t="s">
-        <v>5192</v>
-      </c>
-      <c r="B72" s="217" t="s">
-        <v>5193</v>
-      </c>
-      <c r="C72" s="218" t="s">
-        <v>5194</v>
-      </c>
-      <c r="D72" s="557" t="s">
-        <v>5195</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" s="208" customFormat="1">
-      <c r="A73" s="208" t="s">
-        <v>5196</v>
-      </c>
-      <c r="B73" s="208" t="s">
-        <v>5197</v>
-      </c>
-      <c r="C73" s="207" t="s">
-        <v>5198</v>
-      </c>
-      <c r="D73" s="560" t="s">
-        <v>5199</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" s="208" customFormat="1">
-      <c r="A74" s="208" t="s">
-        <v>5200</v>
-      </c>
-      <c r="B74" s="208" t="s">
-        <v>5201</v>
-      </c>
-      <c r="C74" s="207" t="s">
-        <v>5202</v>
-      </c>
-      <c r="D74" s="560" t="s">
-        <v>5203</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" s="175" customFormat="1">
-      <c r="A75" s="175" t="s">
-        <v>5204</v>
-      </c>
-      <c r="B75" s="175" t="s">
-        <v>5205</v>
-      </c>
-      <c r="C75" s="51" t="s">
-        <v>5206</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>5207</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" s="175" customFormat="1">
-      <c r="A76" s="175" t="s">
-        <v>5208</v>
-      </c>
-      <c r="B76" s="175" t="s">
-        <v>5209</v>
-      </c>
-      <c r="C76" s="51" t="s">
-        <v>5210</v>
-      </c>
-      <c r="D76" s="17" t="s">
-        <v>5211</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" s="212" customFormat="1">
-      <c r="A77" s="212" t="s">
-        <v>5212</v>
-      </c>
-      <c r="B77" s="212" t="s">
-        <v>5213</v>
-      </c>
-      <c r="C77" s="211" t="s">
-        <v>5214</v>
-      </c>
-      <c r="D77" s="561" t="s">
-        <v>5215</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" s="212" customFormat="1">
-      <c r="A78" s="212" t="s">
-        <v>5216</v>
-      </c>
-      <c r="B78" s="212" t="s">
-        <v>5217</v>
-      </c>
-      <c r="C78" s="211" t="s">
-        <v>5218</v>
-      </c>
-      <c r="D78" s="561" t="s">
-        <v>5219</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" s="213" customFormat="1">
-      <c r="A79" s="213" t="s">
-        <v>5220</v>
-      </c>
-      <c r="B79" s="213" t="s">
-        <v>5221</v>
-      </c>
-      <c r="C79" s="214" t="s">
-        <v>5222</v>
-      </c>
-      <c r="D79" s="562" t="s">
-        <v>5223</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" s="213" customFormat="1">
-      <c r="A80" s="213" t="s">
-        <v>5224</v>
-      </c>
-      <c r="B80" s="213" t="s">
-        <v>5225</v>
-      </c>
-      <c r="C80" s="214" t="s">
-        <v>5226</v>
-      </c>
-      <c r="D80" s="562" t="s">
-        <v>5227</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" s="205" customFormat="1">
-      <c r="A81" s="205" t="s">
-        <v>5228</v>
-      </c>
-      <c r="B81" s="205" t="s">
-        <v>5229</v>
-      </c>
-      <c r="C81" s="206" t="s">
-        <v>5230</v>
-      </c>
-      <c r="D81" s="563" t="s">
-        <v>5231</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" s="205" customFormat="1">
-      <c r="A82" s="205" t="s">
-        <v>5232</v>
-      </c>
-      <c r="B82" s="205" t="s">
-        <v>5233</v>
-      </c>
-      <c r="C82" s="206" t="s">
-        <v>5234</v>
-      </c>
-      <c r="D82" s="563" t="s">
-        <v>5235</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" s="77" customFormat="1"/>
-    <row r="84" spans="1:4" s="77" customFormat="1">
-      <c r="A84" s="68" t="s">
-        <v>2502</v>
-      </c>
-      <c r="B84" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D84" s="182" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" s="228" customFormat="1">
-      <c r="A85" s="227" t="s">
-        <v>2503</v>
-      </c>
-      <c r="B85" s="227" t="s">
-        <v>5236</v>
-      </c>
-      <c r="C85" s="227" t="s">
-        <v>5237</v>
-      </c>
-      <c r="D85" s="528" t="s">
-        <v>5238</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" s="222" customFormat="1">
-      <c r="A86" s="221" t="s">
-        <v>5239</v>
-      </c>
-      <c r="B86" s="221" t="s">
-        <v>5240</v>
-      </c>
-      <c r="C86" s="221" t="s">
-        <v>5241</v>
-      </c>
-      <c r="D86" s="564" t="s">
-        <v>5242</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" s="226" customFormat="1">
-      <c r="A87" s="225" t="s">
-        <v>5243</v>
-      </c>
-      <c r="B87" s="225" t="s">
-        <v>5244</v>
-      </c>
-      <c r="C87" s="225" t="s">
-        <v>5245</v>
-      </c>
-      <c r="D87" s="565" t="s">
-        <v>5246</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" s="228" customFormat="1">
-      <c r="A88" s="227" t="s">
-        <v>2515</v>
-      </c>
-      <c r="B88" s="227" t="s">
-        <v>5247</v>
-      </c>
-      <c r="C88" s="227" t="s">
-        <v>5248</v>
-      </c>
-      <c r="D88" s="528" t="s">
-        <v>5249</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" s="222" customFormat="1">
-      <c r="A89" s="221" t="s">
-        <v>5250</v>
-      </c>
-      <c r="B89" s="221" t="s">
-        <v>5251</v>
-      </c>
-      <c r="C89" s="221" t="s">
-        <v>5252</v>
-      </c>
-      <c r="D89" s="564" t="s">
-        <v>5253</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" s="226" customFormat="1">
-      <c r="A90" s="225" t="s">
-        <v>5254</v>
-      </c>
-      <c r="B90" s="225" t="s">
-        <v>5255</v>
-      </c>
-      <c r="C90" s="225" t="s">
-        <v>5256</v>
-      </c>
-      <c r="D90" s="565" t="s">
-        <v>5257</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" s="228" customFormat="1">
-      <c r="A91" s="227" t="s">
-        <v>2527</v>
-      </c>
-      <c r="B91" s="227" t="s">
-        <v>5258</v>
-      </c>
-      <c r="C91" s="227" t="s">
-        <v>5259</v>
-      </c>
-      <c r="D91" s="528" t="s">
-        <v>5260</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" s="228" customFormat="1">
-      <c r="A92" s="227" t="s">
-        <v>2531</v>
-      </c>
-      <c r="B92" s="227" t="s">
-        <v>5261</v>
-      </c>
-      <c r="C92" s="227" t="s">
-        <v>5262</v>
-      </c>
-      <c r="D92" s="528" t="s">
-        <v>5263</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" s="222" customFormat="1">
-      <c r="A93" s="223" t="s">
-        <v>5264</v>
-      </c>
-      <c r="B93" s="224" t="s">
-        <v>5265</v>
-      </c>
-      <c r="C93" s="221" t="s">
-        <v>5266</v>
-      </c>
-      <c r="D93" s="221" t="s">
-        <v>5267</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" s="222" customFormat="1">
-      <c r="A94" s="221" t="s">
-        <v>5268</v>
-      </c>
-      <c r="B94" s="221" t="s">
-        <v>5269</v>
-      </c>
-      <c r="C94" s="221" t="s">
-        <v>5270</v>
-      </c>
-      <c r="D94" s="564" t="s">
-        <v>5271</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" s="226" customFormat="1">
-      <c r="A95" s="225" t="s">
-        <v>5272</v>
-      </c>
-      <c r="B95" s="225" t="s">
-        <v>5273</v>
-      </c>
-      <c r="C95" s="225" t="s">
-        <v>5274</v>
-      </c>
-      <c r="D95" s="565" t="s">
-        <v>5275</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" s="226" customFormat="1">
-      <c r="A96" s="225" t="s">
-        <v>5276</v>
-      </c>
-      <c r="B96" s="225" t="s">
-        <v>5277</v>
-      </c>
-      <c r="C96" s="225" t="s">
-        <v>5278</v>
-      </c>
-      <c r="D96" s="565" t="s">
-        <v>5279</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" s="77" customFormat="1"/>
-    <row r="98" spans="1:4" s="77" customFormat="1">
-      <c r="A98" s="68" t="s">
-        <v>2568</v>
-      </c>
-      <c r="B98" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C98" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D98" s="182" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" s="229" customFormat="1">
-      <c r="A99" s="229" t="s">
-        <v>5280</v>
-      </c>
-      <c r="B99" s="229" t="s">
-        <v>5281</v>
-      </c>
-      <c r="C99" s="230" t="s">
-        <v>5282</v>
-      </c>
-      <c r="D99" s="566" t="s">
-        <v>5283</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" s="229" customFormat="1">
-      <c r="A100" s="229" t="s">
-        <v>5284</v>
-      </c>
-      <c r="B100" s="229" t="s">
-        <v>5285</v>
-      </c>
-      <c r="C100" s="230" t="s">
-        <v>5286</v>
-      </c>
-      <c r="D100" s="566" t="s">
-        <v>5287</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" s="233" customFormat="1">
-      <c r="A101" s="233" t="s">
-        <v>5288</v>
-      </c>
-      <c r="B101" s="233" t="s">
-        <v>5289</v>
-      </c>
-      <c r="C101" s="234" t="s">
-        <v>5290</v>
-      </c>
-      <c r="D101" s="567" t="s">
-        <v>5291</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" s="233" customFormat="1">
-      <c r="A102" s="233" t="s">
-        <v>5292</v>
-      </c>
-      <c r="B102" s="233" t="s">
-        <v>5293</v>
-      </c>
-      <c r="C102" s="234" t="s">
-        <v>5294</v>
-      </c>
-      <c r="D102" s="567" t="s">
-        <v>5295</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" s="231" customFormat="1">
-      <c r="A103" s="231" t="s">
-        <v>5296</v>
-      </c>
-      <c r="B103" s="231" t="s">
-        <v>5297</v>
-      </c>
-      <c r="C103" s="232" t="s">
-        <v>5298</v>
-      </c>
-      <c r="D103" s="568" t="s">
-        <v>5299</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" s="231" customFormat="1">
-      <c r="A104" s="231" t="s">
-        <v>5300</v>
-      </c>
-      <c r="B104" s="231" t="s">
-        <v>5301</v>
-      </c>
-      <c r="C104" s="232" t="s">
-        <v>5302</v>
-      </c>
-      <c r="D104" s="568" t="s">
-        <v>5303</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" s="229" customFormat="1">
-      <c r="A105" s="229" t="s">
-        <v>5304</v>
-      </c>
-      <c r="B105" s="229" t="s">
-        <v>5305</v>
-      </c>
-      <c r="C105" s="230" t="s">
-        <v>5306</v>
-      </c>
-      <c r="D105" s="566" t="s">
-        <v>5307</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" s="229" customFormat="1">
-      <c r="A106" s="229" t="s">
-        <v>5308</v>
-      </c>
-      <c r="B106" s="229" t="s">
-        <v>5309</v>
-      </c>
-      <c r="C106" s="230" t="s">
-        <v>5310</v>
-      </c>
-      <c r="D106" s="566" t="s">
-        <v>5311</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" s="233" customFormat="1">
-      <c r="A107" s="235" t="s">
-        <v>5312</v>
-      </c>
-      <c r="B107" s="236" t="s">
-        <v>5313</v>
-      </c>
-      <c r="C107" s="234" t="s">
-        <v>5314</v>
-      </c>
-      <c r="D107" s="234" t="s">
-        <v>5315</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" s="233" customFormat="1">
-      <c r="A108" s="233" t="s">
-        <v>5316</v>
-      </c>
-      <c r="B108" s="233" t="s">
-        <v>5317</v>
-      </c>
-      <c r="C108" s="234" t="s">
-        <v>5318</v>
-      </c>
-      <c r="D108" s="567" t="s">
-        <v>5319</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" s="231" customFormat="1">
-      <c r="A109" s="231" t="s">
-        <v>5320</v>
-      </c>
-      <c r="B109" s="231" t="s">
-        <v>5321</v>
-      </c>
-      <c r="C109" s="232" t="s">
-        <v>5322</v>
-      </c>
-      <c r="D109" s="568" t="s">
-        <v>5323</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" s="231" customFormat="1">
-      <c r="A110" s="231" t="s">
-        <v>5324</v>
-      </c>
-      <c r="B110" s="231" t="s">
-        <v>5325</v>
-      </c>
-      <c r="C110" s="232" t="s">
-        <v>5326</v>
-      </c>
-      <c r="D110" s="568" t="s">
-        <v>5327</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" s="77" customFormat="1"/>
-    <row r="112" spans="1:4" s="77" customFormat="1">
-      <c r="A112" s="68" t="s">
-        <v>2633</v>
-      </c>
-      <c r="B112" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C112" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D112" s="182" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" s="229" customFormat="1">
-      <c r="A113" s="229" t="s">
-        <v>5328</v>
-      </c>
-      <c r="B113" s="229" t="s">
-        <v>5329</v>
-      </c>
-      <c r="C113" s="230" t="s">
-        <v>5330</v>
-      </c>
-      <c r="D113" s="566" t="s">
-        <v>5331</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" s="229" customFormat="1">
-      <c r="A114" s="229" t="s">
-        <v>5332</v>
-      </c>
-      <c r="B114" s="229" t="s">
-        <v>5333</v>
-      </c>
-      <c r="C114" s="230" t="s">
-        <v>5334</v>
-      </c>
-      <c r="D114" s="566" t="s">
-        <v>5335</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" s="229" customFormat="1">
-      <c r="A115" s="229" t="s">
-        <v>5336</v>
-      </c>
-      <c r="B115" s="229" t="s">
-        <v>5337</v>
-      </c>
-      <c r="C115" s="230" t="s">
-        <v>5338</v>
-      </c>
-      <c r="D115" s="566" t="s">
-        <v>5339</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" s="233" customFormat="1">
-      <c r="A116" s="233" t="s">
-        <v>5340</v>
-      </c>
-      <c r="B116" s="233" t="s">
-        <v>5341</v>
-      </c>
-      <c r="C116" s="234" t="s">
-        <v>5342</v>
-      </c>
-      <c r="D116" s="567" t="s">
-        <v>5343</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" s="233" customFormat="1">
-      <c r="A117" s="233" t="s">
-        <v>5344</v>
-      </c>
-      <c r="B117" s="233" t="s">
-        <v>5345</v>
-      </c>
-      <c r="C117" s="234" t="s">
-        <v>5346</v>
-      </c>
-      <c r="D117" s="567" t="s">
-        <v>5347</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" s="233" customFormat="1">
-      <c r="A118" s="233" t="s">
-        <v>5348</v>
-      </c>
-      <c r="B118" s="233" t="s">
-        <v>5349</v>
-      </c>
-      <c r="C118" s="234" t="s">
-        <v>5350</v>
-      </c>
-      <c r="D118" s="567" t="s">
-        <v>5351</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" s="231" customFormat="1">
-      <c r="A119" s="231" t="s">
-        <v>5352</v>
-      </c>
-      <c r="B119" s="231" t="s">
-        <v>5353</v>
-      </c>
-      <c r="C119" s="232" t="s">
-        <v>5354</v>
-      </c>
-      <c r="D119" s="568" t="s">
-        <v>5355</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" s="231" customFormat="1">
-      <c r="A120" s="231" t="s">
-        <v>5356</v>
-      </c>
-      <c r="B120" s="231" t="s">
-        <v>5357</v>
-      </c>
-      <c r="C120" s="232" t="s">
-        <v>5358</v>
-      </c>
-      <c r="D120" s="568" t="s">
-        <v>5359</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" s="231" customFormat="1">
-      <c r="A121" s="231" t="s">
-        <v>5360</v>
-      </c>
-      <c r="B121" s="231" t="s">
-        <v>5361</v>
-      </c>
-      <c r="C121" s="232" t="s">
-        <v>5362</v>
-      </c>
-      <c r="D121" s="568" t="s">
-        <v>5363</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" s="77" customFormat="1"/>
-    <row r="123" spans="1:4" s="77" customFormat="1">
-      <c r="A123" s="68" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B123" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C123" s="68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D123" s="182" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" s="237" customFormat="1">
-      <c r="A124" s="237" t="s">
-        <v>5364</v>
-      </c>
-      <c r="B124" s="237" t="s">
-        <v>5365</v>
-      </c>
-      <c r="C124" s="238" t="s">
-        <v>5366</v>
-      </c>
-      <c r="D124" s="569" t="s">
-        <v>5367</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" s="237" customFormat="1">
-      <c r="A125" s="237" t="s">
-        <v>5368</v>
-      </c>
-      <c r="B125" s="237" t="s">
-        <v>5369</v>
-      </c>
-      <c r="C125" s="238" t="s">
-        <v>5370</v>
-      </c>
-      <c r="D125" s="569" t="s">
-        <v>5371</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" s="239" customFormat="1">
-      <c r="A126" s="239" t="s">
-        <v>5372</v>
-      </c>
-      <c r="B126" s="239" t="s">
-        <v>5373</v>
-      </c>
-      <c r="C126" s="240" t="s">
-        <v>5374</v>
-      </c>
-      <c r="D126" s="570" t="s">
-        <v>5375</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" s="239" customFormat="1">
-      <c r="A127" s="239" t="s">
-        <v>5376</v>
-      </c>
-      <c r="B127" s="239" t="s">
-        <v>5377</v>
-      </c>
-      <c r="C127" s="240" t="s">
-        <v>5378</v>
-      </c>
-      <c r="D127" s="570" t="s">
-        <v>5379</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" s="241" customFormat="1">
-      <c r="A128" s="241" t="s">
-        <v>5380</v>
-      </c>
-      <c r="B128" s="241" t="s">
-        <v>5381</v>
-      </c>
-      <c r="C128" s="242" t="s">
-        <v>5382</v>
-      </c>
-      <c r="D128" s="571" t="s">
-        <v>5383</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" s="241" customFormat="1">
-      <c r="A129" s="241" t="s">
-        <v>5384</v>
-      </c>
-      <c r="B129" s="241" t="s">
-        <v>5385</v>
-      </c>
-      <c r="C129" s="242" t="s">
-        <v>5386</v>
-      </c>
-      <c r="D129" s="571" t="s">
-        <v>5387</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" s="247" customFormat="1">
-      <c r="A130" s="247" t="s">
-        <v>5388</v>
-      </c>
-      <c r="B130" s="247" t="s">
-        <v>5389</v>
-      </c>
-      <c r="C130" s="248" t="s">
-        <v>5390</v>
-      </c>
-      <c r="D130" s="572" t="s">
-        <v>5391</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" s="247" customFormat="1">
-      <c r="A131" s="247" t="s">
-        <v>5392</v>
-      </c>
-      <c r="B131" s="247" t="s">
-        <v>5393</v>
-      </c>
-      <c r="C131" s="248" t="s">
-        <v>5394</v>
-      </c>
-      <c r="D131" s="572" t="s">
-        <v>5395</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" s="247" customFormat="1">
-      <c r="A132" s="247" t="s">
-        <v>5396</v>
-      </c>
-      <c r="B132" s="247" t="s">
-        <v>5397</v>
-      </c>
-      <c r="C132" s="248" t="s">
-        <v>5398</v>
-      </c>
-      <c r="D132" s="572" t="s">
-        <v>5399</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" s="135" customFormat="1">
-      <c r="A133" s="135" t="s">
-        <v>5400</v>
-      </c>
-      <c r="B133" s="135" t="s">
-        <v>5401</v>
-      </c>
-      <c r="C133" s="80" t="s">
-        <v>5402</v>
-      </c>
-      <c r="D133" s="495" t="s">
-        <v>5403</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" s="135" customFormat="1">
-      <c r="A134" s="135" t="s">
-        <v>5404</v>
-      </c>
-      <c r="B134" s="135" t="s">
-        <v>5405</v>
-      </c>
-      <c r="C134" s="80" t="s">
-        <v>5406</v>
-      </c>
-      <c r="D134" s="495" t="s">
-        <v>5407</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" s="135" customFormat="1">
-      <c r="A135" s="135" t="s">
-        <v>5408</v>
-      </c>
-      <c r="B135" s="135" t="s">
-        <v>5409</v>
-      </c>
-      <c r="C135" s="80" t="s">
-        <v>5410</v>
-      </c>
-      <c r="D135" s="495" t="s">
-        <v>5411</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" s="249" customFormat="1">
-      <c r="A136" s="249" t="s">
-        <v>5412</v>
-      </c>
-      <c r="B136" s="249" t="s">
-        <v>5413</v>
-      </c>
-      <c r="C136" s="250" t="s">
-        <v>5414</v>
-      </c>
-      <c r="D136" s="573" t="s">
-        <v>5415</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" s="249" customFormat="1">
-      <c r="A137" s="249" t="s">
-        <v>5416</v>
-      </c>
-      <c r="B137" s="249" t="s">
-        <v>5417</v>
-      </c>
-      <c r="C137" s="250" t="s">
-        <v>5418</v>
-      </c>
-      <c r="D137" s="573" t="s">
-        <v>5419</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" s="249" customFormat="1">
-      <c r="A138" s="249" t="s">
-        <v>5420</v>
-      </c>
-      <c r="B138" s="249" t="s">
-        <v>5421</v>
-      </c>
-      <c r="C138" s="250" t="s">
-        <v>5422</v>
-      </c>
-      <c r="D138" s="573" t="s">
-        <v>5423</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" s="247" customFormat="1">
-      <c r="A139" s="247" t="s">
-        <v>5424</v>
-      </c>
-      <c r="B139" s="247" t="s">
-        <v>5425</v>
-      </c>
-      <c r="C139" s="248" t="s">
-        <v>5426</v>
-      </c>
-      <c r="D139" s="572" t="s">
-        <v>5427</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" s="247" customFormat="1">
-      <c r="A140" s="247" t="s">
-        <v>5428</v>
-      </c>
-      <c r="B140" s="247" t="s">
-        <v>5429</v>
-      </c>
-      <c r="C140" s="248" t="s">
-        <v>5430</v>
-      </c>
-      <c r="D140" s="572" t="s">
-        <v>5431</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" s="247" customFormat="1">
-      <c r="A141" s="247" t="s">
-        <v>5432</v>
-      </c>
-      <c r="B141" s="247" t="s">
-        <v>5433</v>
-      </c>
-      <c r="C141" s="248" t="s">
-        <v>5434</v>
-      </c>
-      <c r="D141" s="572" t="s">
-        <v>5435</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" s="135" customFormat="1">
-      <c r="A142" s="135" t="s">
-        <v>5436</v>
-      </c>
-      <c r="B142" s="135" t="s">
-        <v>5437</v>
-      </c>
-      <c r="C142" s="80" t="s">
-        <v>5438</v>
-      </c>
-      <c r="D142" s="495" t="s">
-        <v>5439</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" s="135" customFormat="1">
-      <c r="A143" s="135" t="s">
-        <v>5440</v>
-      </c>
-      <c r="B143" s="135" t="s">
-        <v>5441</v>
-      </c>
-      <c r="C143" s="80" t="s">
-        <v>5442</v>
-      </c>
-      <c r="D143" s="495" t="s">
-        <v>5443</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" s="135" customFormat="1">
-      <c r="A144" s="135" t="s">
-        <v>5444</v>
-      </c>
-      <c r="B144" s="135" t="s">
-        <v>5445</v>
-      </c>
-      <c r="C144" s="80" t="s">
-        <v>5446</v>
-      </c>
-      <c r="D144" s="495" t="s">
-        <v>5447</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" s="249" customFormat="1">
-      <c r="A145" s="249" t="s">
-        <v>5448</v>
-      </c>
-      <c r="B145" s="249" t="s">
-        <v>5449</v>
-      </c>
-      <c r="C145" s="250" t="s">
-        <v>5450</v>
-      </c>
-      <c r="D145" s="573" t="s">
-        <v>5451</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" s="249" customFormat="1">
-      <c r="A146" s="249" t="s">
-        <v>5452</v>
-      </c>
-      <c r="B146" s="249" t="s">
-        <v>5453</v>
-      </c>
-      <c r="C146" s="250" t="s">
-        <v>5454</v>
-      </c>
-      <c r="D146" s="573" t="s">
-        <v>5455</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" s="249" customFormat="1">
-      <c r="A147" s="249" t="s">
-        <v>5456</v>
-      </c>
-      <c r="B147" s="249" t="s">
-        <v>5457</v>
-      </c>
-      <c r="C147" s="250" t="s">
-        <v>5458</v>
-      </c>
-      <c r="D147" s="573" t="s">
-        <v>5459</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" s="237" customFormat="1">
-      <c r="A148" s="237" t="s">
-        <v>5460</v>
-      </c>
-      <c r="B148" s="237" t="s">
-        <v>5461</v>
-      </c>
-      <c r="C148" s="238" t="s">
-        <v>5462</v>
-      </c>
-      <c r="D148" s="569" t="s">
-        <v>5463</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" s="237" customFormat="1">
-      <c r="A149" s="237" t="s">
-        <v>5464</v>
-      </c>
-      <c r="B149" s="237" t="s">
-        <v>5465</v>
-      </c>
-      <c r="C149" s="238" t="s">
-        <v>5466</v>
-      </c>
-      <c r="D149" s="569" t="s">
-        <v>5467</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" s="239" customFormat="1">
-      <c r="A150" s="239" t="s">
-        <v>5468</v>
-      </c>
-      <c r="B150" s="239" t="s">
-        <v>5469</v>
-      </c>
-      <c r="C150" s="240" t="s">
-        <v>5470</v>
-      </c>
-      <c r="D150" s="570" t="s">
-        <v>5471</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" s="239" customFormat="1">
-      <c r="A151" s="239" t="s">
-        <v>5472</v>
-      </c>
-      <c r="B151" s="239" t="s">
-        <v>5473</v>
-      </c>
-      <c r="C151" s="240" t="s">
-        <v>5474</v>
-      </c>
-      <c r="D151" s="570" t="s">
-        <v>5475</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" s="241" customFormat="1">
-      <c r="A152" s="241" t="s">
-        <v>5476</v>
-      </c>
-      <c r="B152" s="241" t="s">
-        <v>5477</v>
-      </c>
-      <c r="C152" s="242" t="s">
-        <v>5478</v>
-      </c>
-      <c r="D152" s="571" t="s">
-        <v>5479</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" s="241" customFormat="1">
-      <c r="A153" s="241" t="s">
-        <v>5480</v>
-      </c>
-      <c r="B153" s="241" t="s">
-        <v>5481</v>
-      </c>
-      <c r="C153" s="242" t="s">
-        <v>5482</v>
-      </c>
-      <c r="D153" s="571" t="s">
-        <v>5483</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" s="245" customFormat="1">
-      <c r="A154" s="245" t="s">
-        <v>5484</v>
-      </c>
-      <c r="B154" s="245" t="s">
-        <v>5485</v>
-      </c>
-      <c r="C154" s="246" t="s">
-        <v>5486</v>
-      </c>
-      <c r="D154" s="574" t="s">
-        <v>5487</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" s="245" customFormat="1">
-      <c r="A155" s="245" t="s">
-        <v>5488</v>
-      </c>
-      <c r="B155" s="245" t="s">
-        <v>5489</v>
-      </c>
-      <c r="C155" s="246" t="s">
-        <v>5490</v>
-      </c>
-      <c r="D155" s="574" t="s">
-        <v>5491</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" s="243" customFormat="1">
-      <c r="A156" s="243" t="s">
-        <v>5492</v>
-      </c>
-      <c r="B156" s="243" t="s">
-        <v>5493</v>
-      </c>
-      <c r="C156" s="244" t="s">
-        <v>5494</v>
-      </c>
-      <c r="D156" s="575" t="s">
-        <v>5495</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" s="243" customFormat="1">
-      <c r="A157" s="243" t="s">
-        <v>5496</v>
-      </c>
-      <c r="B157" s="243" t="s">
-        <v>5497</v>
-      </c>
-      <c r="C157" s="244" t="s">
-        <v>5498</v>
-      </c>
-      <c r="D157" s="575" t="s">
-        <v>5499</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" s="245" customFormat="1">
-      <c r="A158" s="245" t="s">
-        <v>5500</v>
-      </c>
-      <c r="B158" s="245" t="s">
-        <v>5501</v>
-      </c>
-      <c r="C158" s="246" t="s">
-        <v>5502</v>
-      </c>
-      <c r="D158" s="574" t="s">
-        <v>5503</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" s="245" customFormat="1">
-      <c r="A159" s="245" t="s">
-        <v>5504</v>
-      </c>
-      <c r="B159" s="245" t="s">
-        <v>5505</v>
-      </c>
-      <c r="C159" s="246" t="s">
-        <v>5506</v>
-      </c>
-      <c r="D159" s="574" t="s">
-        <v>5507</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" s="243" customFormat="1">
-      <c r="A160" s="243" t="s">
-        <v>5508</v>
-      </c>
-      <c r="B160" s="243" t="s">
-        <v>5509</v>
-      </c>
-      <c r="C160" s="244" t="s">
-        <v>5510</v>
-      </c>
-      <c r="D160" s="575" t="s">
-        <v>5511</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" s="243" customFormat="1">
-      <c r="A161" s="243" t="s">
-        <v>5512</v>
-      </c>
-      <c r="B161" s="243" t="s">
-        <v>5513</v>
-      </c>
-      <c r="C161" s="244" t="s">
-        <v>5514</v>
-      </c>
-      <c r="D161" s="575" t="s">
-        <v>5515</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" s="252" customFormat="1">
-      <c r="A162" s="251" t="s">
-        <v>2755</v>
-      </c>
-      <c r="B162" s="251" t="s">
-        <v>5516</v>
-      </c>
-      <c r="C162" s="251" t="s">
-        <v>5517</v>
-      </c>
-      <c r="D162" s="576" t="s">
-        <v>5518</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" s="252" customFormat="1">
-      <c r="A163" s="251" t="s">
-        <v>2759</v>
-      </c>
-      <c r="B163" s="251" t="s">
-        <v>5519</v>
-      </c>
-      <c r="C163" s="251" t="s">
-        <v>5520</v>
-      </c>
-      <c r="D163" s="576" t="s">
-        <v>5521</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" s="252" customFormat="1">
-      <c r="A164" s="251" t="s">
-        <v>2763</v>
-      </c>
-      <c r="B164" s="251" t="s">
-        <v>5522</v>
-      </c>
-      <c r="C164" s="251" t="s">
-        <v>5523</v>
-      </c>
-      <c r="D164" s="576" t="s">
-        <v>5524</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" s="254" customFormat="1">
-      <c r="A165" s="253" t="s">
-        <v>2839</v>
-      </c>
-      <c r="B165" s="253" t="s">
-        <v>5525</v>
-      </c>
-      <c r="C165" s="253" t="s">
-        <v>5526</v>
-      </c>
-      <c r="D165" s="577" t="s">
-        <v>5527</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" s="254" customFormat="1">
-      <c r="A166" s="253" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B166" s="253" t="s">
-        <v>5528</v>
-      </c>
-      <c r="C166" s="253" t="s">
-        <v>5529</v>
-      </c>
-      <c r="D166" s="577" t="s">
-        <v>5530</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" s="254" customFormat="1">
-      <c r="A167" s="254" t="s">
-        <v>2847</v>
-      </c>
-      <c r="B167" s="254" t="s">
-        <v>5531</v>
-      </c>
-      <c r="C167" s="253" t="s">
-        <v>5532</v>
-      </c>
-      <c r="D167" s="577" t="s">
-        <v>5533</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" s="77" customFormat="1"/>
-    <row r="169" spans="1:4" s="77" customFormat="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -61978,6 +60280,2304 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
+  <dimension ref="A1:D169"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="52.83203125" style="136" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="136" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.1640625" style="136" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="136" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="136"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="77" customFormat="1">
+      <c r="A1" s="68" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="202" customFormat="1">
+      <c r="A2" s="201" t="s">
+        <v>4920</v>
+      </c>
+      <c r="B2" s="201" t="s">
+        <v>4921</v>
+      </c>
+      <c r="C2" s="201" t="s">
+        <v>4922</v>
+      </c>
+      <c r="D2" s="555" t="s">
+        <v>4923</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="216" customFormat="1">
+      <c r="A3" s="215" t="s">
+        <v>4924</v>
+      </c>
+      <c r="B3" s="215" t="s">
+        <v>4925</v>
+      </c>
+      <c r="C3" s="215" t="s">
+        <v>4926</v>
+      </c>
+      <c r="D3" s="556" t="s">
+        <v>4927</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="217" customFormat="1">
+      <c r="A4" s="218" t="s">
+        <v>4928</v>
+      </c>
+      <c r="B4" s="218" t="s">
+        <v>4929</v>
+      </c>
+      <c r="C4" s="218" t="s">
+        <v>4930</v>
+      </c>
+      <c r="D4" s="557" t="s">
+        <v>4931</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="204" customFormat="1">
+      <c r="A5" s="203" t="s">
+        <v>4932</v>
+      </c>
+      <c r="B5" s="203" t="s">
+        <v>4933</v>
+      </c>
+      <c r="C5" s="203" t="s">
+        <v>4934</v>
+      </c>
+      <c r="D5" s="558" t="s">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="219" customFormat="1">
+      <c r="A6" s="220" t="s">
+        <v>4936</v>
+      </c>
+      <c r="B6" s="220" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C6" s="220" t="s">
+        <v>4938</v>
+      </c>
+      <c r="D6" s="559" t="s">
+        <v>4939</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="208" customFormat="1">
+      <c r="A7" s="207" t="s">
+        <v>4940</v>
+      </c>
+      <c r="B7" s="207" t="s">
+        <v>4941</v>
+      </c>
+      <c r="C7" s="207" t="s">
+        <v>4942</v>
+      </c>
+      <c r="D7" s="560" t="s">
+        <v>4943</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="175" customFormat="1">
+      <c r="A8" s="51" t="s">
+        <v>4944</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>4945</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>4946</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="212" customFormat="1">
+      <c r="A9" s="211" t="s">
+        <v>4948</v>
+      </c>
+      <c r="B9" s="211" t="s">
+        <v>4949</v>
+      </c>
+      <c r="C9" s="211" t="s">
+        <v>4950</v>
+      </c>
+      <c r="D9" s="561" t="s">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="213" customFormat="1">
+      <c r="A10" s="213" t="s">
+        <v>4952</v>
+      </c>
+      <c r="B10" s="213" t="s">
+        <v>4953</v>
+      </c>
+      <c r="C10" s="214" t="s">
+        <v>4954</v>
+      </c>
+      <c r="D10" s="562" t="s">
+        <v>4955</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="205" customFormat="1">
+      <c r="A11" s="205" t="s">
+        <v>4956</v>
+      </c>
+      <c r="B11" s="205" t="s">
+        <v>4957</v>
+      </c>
+      <c r="C11" s="206" t="s">
+        <v>4958</v>
+      </c>
+      <c r="D11" s="563" t="s">
+        <v>4959</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="202" customFormat="1">
+      <c r="A12" s="202" t="s">
+        <v>4960</v>
+      </c>
+      <c r="B12" s="202" t="s">
+        <v>4961</v>
+      </c>
+      <c r="C12" s="201" t="s">
+        <v>4962</v>
+      </c>
+      <c r="D12" s="555" t="s">
+        <v>4963</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="216" customFormat="1">
+      <c r="A13" s="216" t="s">
+        <v>4964</v>
+      </c>
+      <c r="B13" s="216" t="s">
+        <v>4965</v>
+      </c>
+      <c r="C13" s="215" t="s">
+        <v>4966</v>
+      </c>
+      <c r="D13" s="556" t="s">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="217" customFormat="1">
+      <c r="A14" s="217" t="s">
+        <v>4968</v>
+      </c>
+      <c r="B14" s="217" t="s">
+        <v>4969</v>
+      </c>
+      <c r="C14" s="218" t="s">
+        <v>4970</v>
+      </c>
+      <c r="D14" s="557" t="s">
+        <v>4971</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="204" customFormat="1">
+      <c r="A15" s="204" t="s">
+        <v>4972</v>
+      </c>
+      <c r="B15" s="204" t="s">
+        <v>4973</v>
+      </c>
+      <c r="C15" s="203" t="s">
+        <v>4974</v>
+      </c>
+      <c r="D15" s="558" t="s">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="219" customFormat="1">
+      <c r="A16" s="219" t="s">
+        <v>4976</v>
+      </c>
+      <c r="B16" s="219" t="s">
+        <v>4977</v>
+      </c>
+      <c r="C16" s="220" t="s">
+        <v>4978</v>
+      </c>
+      <c r="D16" s="559" t="s">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="208" customFormat="1">
+      <c r="A17" s="208" t="s">
+        <v>4980</v>
+      </c>
+      <c r="B17" s="208" t="s">
+        <v>4981</v>
+      </c>
+      <c r="C17" s="207" t="s">
+        <v>4982</v>
+      </c>
+      <c r="D17" s="560" t="s">
+        <v>4983</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="175" customFormat="1">
+      <c r="A18" s="175" t="s">
+        <v>4984</v>
+      </c>
+      <c r="B18" s="175" t="s">
+        <v>4985</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>4986</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>4987</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="212" customFormat="1">
+      <c r="A19" s="212" t="s">
+        <v>4988</v>
+      </c>
+      <c r="B19" s="212" t="s">
+        <v>4989</v>
+      </c>
+      <c r="C19" s="211" t="s">
+        <v>4990</v>
+      </c>
+      <c r="D19" s="561" t="s">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="213" customFormat="1">
+      <c r="A20" s="213" t="s">
+        <v>4992</v>
+      </c>
+      <c r="B20" s="213" t="s">
+        <v>4993</v>
+      </c>
+      <c r="C20" s="214" t="s">
+        <v>4994</v>
+      </c>
+      <c r="D20" s="562" t="s">
+        <v>4995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="205" customFormat="1">
+      <c r="A21" s="205" t="s">
+        <v>4996</v>
+      </c>
+      <c r="B21" s="205" t="s">
+        <v>4997</v>
+      </c>
+      <c r="C21" s="206" t="s">
+        <v>4998</v>
+      </c>
+      <c r="D21" s="563" t="s">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="202" customFormat="1">
+      <c r="A22" s="202" t="s">
+        <v>5000</v>
+      </c>
+      <c r="B22" s="202" t="s">
+        <v>5001</v>
+      </c>
+      <c r="C22" s="201" t="s">
+        <v>5002</v>
+      </c>
+      <c r="D22" s="555" t="s">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="216" customFormat="1">
+      <c r="A23" s="216" t="s">
+        <v>5004</v>
+      </c>
+      <c r="B23" s="216" t="s">
+        <v>5005</v>
+      </c>
+      <c r="C23" s="215" t="s">
+        <v>5006</v>
+      </c>
+      <c r="D23" s="556" t="s">
+        <v>5007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="217" customFormat="1">
+      <c r="A24" s="217" t="s">
+        <v>5008</v>
+      </c>
+      <c r="B24" s="217" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C24" s="218" t="s">
+        <v>5010</v>
+      </c>
+      <c r="D24" s="557" t="s">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="204" customFormat="1">
+      <c r="A25" s="204" t="s">
+        <v>5012</v>
+      </c>
+      <c r="B25" s="204" t="s">
+        <v>5013</v>
+      </c>
+      <c r="C25" s="203" t="s">
+        <v>5014</v>
+      </c>
+      <c r="D25" s="558" t="s">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="219" customFormat="1">
+      <c r="A26" s="219" t="s">
+        <v>5016</v>
+      </c>
+      <c r="B26" s="219" t="s">
+        <v>5017</v>
+      </c>
+      <c r="C26" s="220" t="s">
+        <v>5018</v>
+      </c>
+      <c r="D26" s="559" t="s">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="219" customFormat="1">
+      <c r="A27" s="219" t="s">
+        <v>5020</v>
+      </c>
+      <c r="B27" s="219" t="s">
+        <v>5021</v>
+      </c>
+      <c r="C27" s="220" t="s">
+        <v>5022</v>
+      </c>
+      <c r="D27" s="559" t="s">
+        <v>5023</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="208" customFormat="1">
+      <c r="A28" s="208" t="s">
+        <v>5024</v>
+      </c>
+      <c r="B28" s="208" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C28" s="207" t="s">
+        <v>5026</v>
+      </c>
+      <c r="D28" s="560" t="s">
+        <v>5027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="175" customFormat="1">
+      <c r="A29" s="175" t="s">
+        <v>5028</v>
+      </c>
+      <c r="B29" s="175" t="s">
+        <v>5029</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>5030</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>5031</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="212" customFormat="1">
+      <c r="A30" s="212" t="s">
+        <v>5032</v>
+      </c>
+      <c r="B30" s="212" t="s">
+        <v>5033</v>
+      </c>
+      <c r="C30" s="211" t="s">
+        <v>5034</v>
+      </c>
+      <c r="D30" s="561" t="s">
+        <v>5035</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="213" customFormat="1">
+      <c r="A31" s="213" t="s">
+        <v>5036</v>
+      </c>
+      <c r="B31" s="213" t="s">
+        <v>5037</v>
+      </c>
+      <c r="C31" s="214" t="s">
+        <v>5038</v>
+      </c>
+      <c r="D31" s="562" t="s">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="205" customFormat="1">
+      <c r="A32" s="205" t="s">
+        <v>5040</v>
+      </c>
+      <c r="B32" s="205" t="s">
+        <v>5041</v>
+      </c>
+      <c r="C32" s="206" t="s">
+        <v>5042</v>
+      </c>
+      <c r="D32" s="563" t="s">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="77" customFormat="1">
+      <c r="A33" s="68"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="182"/>
+    </row>
+    <row r="34" spans="1:4" s="77" customFormat="1">
+      <c r="A34" s="68" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B34" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="208" customFormat="1">
+      <c r="A35" s="207" t="s">
+        <v>5044</v>
+      </c>
+      <c r="B35" s="207" t="s">
+        <v>5045</v>
+      </c>
+      <c r="C35" s="207" t="s">
+        <v>5046</v>
+      </c>
+      <c r="D35" s="560" t="s">
+        <v>5047</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="208" customFormat="1">
+      <c r="A36" s="209" t="s">
+        <v>5048</v>
+      </c>
+      <c r="B36" s="210" t="s">
+        <v>5049</v>
+      </c>
+      <c r="C36" s="207" t="s">
+        <v>5050</v>
+      </c>
+      <c r="D36" s="207" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="175" customFormat="1">
+      <c r="A37" s="51" t="s">
+        <v>5052</v>
+      </c>
+      <c r="B37" s="51" t="s">
+        <v>5053</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>5054</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="175" customFormat="1">
+      <c r="A38" s="51" t="s">
+        <v>5056</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>5057</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>5058</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="212" customFormat="1">
+      <c r="A39" s="211" t="s">
+        <v>5060</v>
+      </c>
+      <c r="B39" s="211" t="s">
+        <v>5061</v>
+      </c>
+      <c r="C39" s="211" t="s">
+        <v>5062</v>
+      </c>
+      <c r="D39" s="561" t="s">
+        <v>5063</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="212" customFormat="1">
+      <c r="A40" s="211" t="s">
+        <v>5064</v>
+      </c>
+      <c r="B40" s="211" t="s">
+        <v>5065</v>
+      </c>
+      <c r="C40" s="211" t="s">
+        <v>5066</v>
+      </c>
+      <c r="D40" s="561" t="s">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="213" customFormat="1">
+      <c r="A41" s="214" t="s">
+        <v>5068</v>
+      </c>
+      <c r="B41" s="214" t="s">
+        <v>5069</v>
+      </c>
+      <c r="C41" s="214" t="s">
+        <v>5070</v>
+      </c>
+      <c r="D41" s="562" t="s">
+        <v>5071</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="213" customFormat="1">
+      <c r="A42" s="214" t="s">
+        <v>5072</v>
+      </c>
+      <c r="B42" s="214" t="s">
+        <v>5073</v>
+      </c>
+      <c r="C42" s="214" t="s">
+        <v>5074</v>
+      </c>
+      <c r="D42" s="562" t="s">
+        <v>5075</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="205" customFormat="1">
+      <c r="A43" s="206" t="s">
+        <v>5076</v>
+      </c>
+      <c r="B43" s="206" t="s">
+        <v>5077</v>
+      </c>
+      <c r="C43" s="206" t="s">
+        <v>5078</v>
+      </c>
+      <c r="D43" s="563" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" s="205" customFormat="1">
+      <c r="A44" s="206" t="s">
+        <v>5080</v>
+      </c>
+      <c r="B44" s="206" t="s">
+        <v>5081</v>
+      </c>
+      <c r="C44" s="206" t="s">
+        <v>5082</v>
+      </c>
+      <c r="D44" s="563" t="s">
+        <v>5083</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="204" customFormat="1">
+      <c r="A45" s="204" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B45" s="204" t="s">
+        <v>5085</v>
+      </c>
+      <c r="C45" s="203" t="s">
+        <v>5086</v>
+      </c>
+      <c r="D45" s="558" t="s">
+        <v>5087</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="204" customFormat="1">
+      <c r="A46" s="204" t="s">
+        <v>5088</v>
+      </c>
+      <c r="B46" s="204" t="s">
+        <v>5089</v>
+      </c>
+      <c r="C46" s="203" t="s">
+        <v>5090</v>
+      </c>
+      <c r="D46" s="558" t="s">
+        <v>5091</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="202" customFormat="1">
+      <c r="A47" s="202" t="s">
+        <v>5092</v>
+      </c>
+      <c r="B47" s="202" t="s">
+        <v>5093</v>
+      </c>
+      <c r="C47" s="201" t="s">
+        <v>5094</v>
+      </c>
+      <c r="D47" s="555" t="s">
+        <v>5095</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="202" customFormat="1">
+      <c r="A48" s="202" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B48" s="202" t="s">
+        <v>5097</v>
+      </c>
+      <c r="C48" s="201" t="s">
+        <v>5098</v>
+      </c>
+      <c r="D48" s="555" t="s">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" s="217" customFormat="1">
+      <c r="A49" s="217" t="s">
+        <v>5100</v>
+      </c>
+      <c r="B49" s="217" t="s">
+        <v>5101</v>
+      </c>
+      <c r="C49" s="218" t="s">
+        <v>5102</v>
+      </c>
+      <c r="D49" s="557" t="s">
+        <v>5103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="217" customFormat="1">
+      <c r="A50" s="217" t="s">
+        <v>5104</v>
+      </c>
+      <c r="B50" s="217" t="s">
+        <v>5105</v>
+      </c>
+      <c r="C50" s="218" t="s">
+        <v>5106</v>
+      </c>
+      <c r="D50" s="557" t="s">
+        <v>5107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" s="204" customFormat="1">
+      <c r="A51" s="204" t="s">
+        <v>5108</v>
+      </c>
+      <c r="B51" s="204" t="s">
+        <v>5109</v>
+      </c>
+      <c r="C51" s="203" t="s">
+        <v>5110</v>
+      </c>
+      <c r="D51" s="558" t="s">
+        <v>5111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" s="204" customFormat="1">
+      <c r="A52" s="204" t="s">
+        <v>5112</v>
+      </c>
+      <c r="B52" s="204" t="s">
+        <v>5113</v>
+      </c>
+      <c r="C52" s="203" t="s">
+        <v>5114</v>
+      </c>
+      <c r="D52" s="558" t="s">
+        <v>5115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" s="202" customFormat="1">
+      <c r="A53" s="202" t="s">
+        <v>5116</v>
+      </c>
+      <c r="B53" s="202" t="s">
+        <v>5117</v>
+      </c>
+      <c r="C53" s="201" t="s">
+        <v>5118</v>
+      </c>
+      <c r="D53" s="555" t="s">
+        <v>5119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" s="202" customFormat="1">
+      <c r="A54" s="202" t="s">
+        <v>5120</v>
+      </c>
+      <c r="B54" s="202" t="s">
+        <v>5121</v>
+      </c>
+      <c r="C54" s="201" t="s">
+        <v>5122</v>
+      </c>
+      <c r="D54" s="555" t="s">
+        <v>5123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" s="217" customFormat="1">
+      <c r="A55" s="217" t="s">
+        <v>5124</v>
+      </c>
+      <c r="B55" s="217" t="s">
+        <v>5125</v>
+      </c>
+      <c r="C55" s="218" t="s">
+        <v>5126</v>
+      </c>
+      <c r="D55" s="557" t="s">
+        <v>5127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" s="217" customFormat="1">
+      <c r="A56" s="217" t="s">
+        <v>5128</v>
+      </c>
+      <c r="B56" s="217" t="s">
+        <v>5129</v>
+      </c>
+      <c r="C56" s="218" t="s">
+        <v>5130</v>
+      </c>
+      <c r="D56" s="557" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" s="208" customFormat="1">
+      <c r="A57" s="208" t="s">
+        <v>5132</v>
+      </c>
+      <c r="B57" s="208" t="s">
+        <v>5133</v>
+      </c>
+      <c r="C57" s="207" t="s">
+        <v>5134</v>
+      </c>
+      <c r="D57" s="560" t="s">
+        <v>5135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" s="208" customFormat="1">
+      <c r="A58" s="208" t="s">
+        <v>5136</v>
+      </c>
+      <c r="B58" s="208" t="s">
+        <v>5137</v>
+      </c>
+      <c r="C58" s="207" t="s">
+        <v>5138</v>
+      </c>
+      <c r="D58" s="560" t="s">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" s="175" customFormat="1">
+      <c r="A59" s="175" t="s">
+        <v>5140</v>
+      </c>
+      <c r="B59" s="175" t="s">
+        <v>5141</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>5142</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>5143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" s="175" customFormat="1">
+      <c r="A60" s="175" t="s">
+        <v>5144</v>
+      </c>
+      <c r="B60" s="175" t="s">
+        <v>5145</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>5146</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>5147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" s="212" customFormat="1">
+      <c r="A61" s="212" t="s">
+        <v>5148</v>
+      </c>
+      <c r="B61" s="212" t="s">
+        <v>5149</v>
+      </c>
+      <c r="C61" s="211" t="s">
+        <v>5150</v>
+      </c>
+      <c r="D61" s="561" t="s">
+        <v>5151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" s="212" customFormat="1">
+      <c r="A62" s="212" t="s">
+        <v>5152</v>
+      </c>
+      <c r="B62" s="212" t="s">
+        <v>5153</v>
+      </c>
+      <c r="C62" s="211" t="s">
+        <v>5154</v>
+      </c>
+      <c r="D62" s="561" t="s">
+        <v>5155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" s="213" customFormat="1">
+      <c r="A63" s="213" t="s">
+        <v>5156</v>
+      </c>
+      <c r="B63" s="213" t="s">
+        <v>5157</v>
+      </c>
+      <c r="C63" s="214" t="s">
+        <v>5158</v>
+      </c>
+      <c r="D63" s="562" t="s">
+        <v>5159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" s="213" customFormat="1">
+      <c r="A64" s="213" t="s">
+        <v>5160</v>
+      </c>
+      <c r="B64" s="213" t="s">
+        <v>5161</v>
+      </c>
+      <c r="C64" s="214" t="s">
+        <v>5162</v>
+      </c>
+      <c r="D64" s="562" t="s">
+        <v>5163</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="205" customFormat="1">
+      <c r="A65" s="205" t="s">
+        <v>5164</v>
+      </c>
+      <c r="B65" s="205" t="s">
+        <v>5165</v>
+      </c>
+      <c r="C65" s="206" t="s">
+        <v>5166</v>
+      </c>
+      <c r="D65" s="563" t="s">
+        <v>5167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="205" customFormat="1">
+      <c r="A66" s="205" t="s">
+        <v>5168</v>
+      </c>
+      <c r="B66" s="205" t="s">
+        <v>5169</v>
+      </c>
+      <c r="C66" s="206" t="s">
+        <v>5170</v>
+      </c>
+      <c r="D66" s="563" t="s">
+        <v>5171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="204" customFormat="1">
+      <c r="A67" s="204" t="s">
+        <v>5172</v>
+      </c>
+      <c r="B67" s="204" t="s">
+        <v>5173</v>
+      </c>
+      <c r="C67" s="203" t="s">
+        <v>5174</v>
+      </c>
+      <c r="D67" s="558" t="s">
+        <v>5175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" s="204" customFormat="1">
+      <c r="A68" s="204" t="s">
+        <v>5176</v>
+      </c>
+      <c r="B68" s="204" t="s">
+        <v>5177</v>
+      </c>
+      <c r="C68" s="203" t="s">
+        <v>5178</v>
+      </c>
+      <c r="D68" s="558" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" s="202" customFormat="1">
+      <c r="A69" s="202" t="s">
+        <v>5180</v>
+      </c>
+      <c r="B69" s="202" t="s">
+        <v>5181</v>
+      </c>
+      <c r="C69" s="201" t="s">
+        <v>5182</v>
+      </c>
+      <c r="D69" s="555" t="s">
+        <v>5183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" s="202" customFormat="1">
+      <c r="A70" s="202" t="s">
+        <v>5184</v>
+      </c>
+      <c r="B70" s="202" t="s">
+        <v>5185</v>
+      </c>
+      <c r="C70" s="201" t="s">
+        <v>5186</v>
+      </c>
+      <c r="D70" s="555" t="s">
+        <v>5187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" s="217" customFormat="1">
+      <c r="A71" s="217" t="s">
+        <v>5188</v>
+      </c>
+      <c r="B71" s="217" t="s">
+        <v>5189</v>
+      </c>
+      <c r="C71" s="218" t="s">
+        <v>5190</v>
+      </c>
+      <c r="D71" s="557" t="s">
+        <v>5191</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" s="217" customFormat="1">
+      <c r="A72" s="217" t="s">
+        <v>5192</v>
+      </c>
+      <c r="B72" s="217" t="s">
+        <v>5193</v>
+      </c>
+      <c r="C72" s="218" t="s">
+        <v>5194</v>
+      </c>
+      <c r="D72" s="557" t="s">
+        <v>5195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" s="208" customFormat="1">
+      <c r="A73" s="208" t="s">
+        <v>5196</v>
+      </c>
+      <c r="B73" s="208" t="s">
+        <v>5197</v>
+      </c>
+      <c r="C73" s="207" t="s">
+        <v>5198</v>
+      </c>
+      <c r="D73" s="560" t="s">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" s="208" customFormat="1">
+      <c r="A74" s="208" t="s">
+        <v>5200</v>
+      </c>
+      <c r="B74" s="208" t="s">
+        <v>5201</v>
+      </c>
+      <c r="C74" s="207" t="s">
+        <v>5202</v>
+      </c>
+      <c r="D74" s="560" t="s">
+        <v>5203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" s="175" customFormat="1">
+      <c r="A75" s="175" t="s">
+        <v>5204</v>
+      </c>
+      <c r="B75" s="175" t="s">
+        <v>5205</v>
+      </c>
+      <c r="C75" s="51" t="s">
+        <v>5206</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" s="175" customFormat="1">
+      <c r="A76" s="175" t="s">
+        <v>5208</v>
+      </c>
+      <c r="B76" s="175" t="s">
+        <v>5209</v>
+      </c>
+      <c r="C76" s="51" t="s">
+        <v>5210</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>5211</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" s="212" customFormat="1">
+      <c r="A77" s="212" t="s">
+        <v>5212</v>
+      </c>
+      <c r="B77" s="212" t="s">
+        <v>5213</v>
+      </c>
+      <c r="C77" s="211" t="s">
+        <v>5214</v>
+      </c>
+      <c r="D77" s="561" t="s">
+        <v>5215</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="212" customFormat="1">
+      <c r="A78" s="212" t="s">
+        <v>5216</v>
+      </c>
+      <c r="B78" s="212" t="s">
+        <v>5217</v>
+      </c>
+      <c r="C78" s="211" t="s">
+        <v>5218</v>
+      </c>
+      <c r="D78" s="561" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" s="213" customFormat="1">
+      <c r="A79" s="213" t="s">
+        <v>5220</v>
+      </c>
+      <c r="B79" s="213" t="s">
+        <v>5221</v>
+      </c>
+      <c r="C79" s="214" t="s">
+        <v>5222</v>
+      </c>
+      <c r="D79" s="562" t="s">
+        <v>5223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" s="213" customFormat="1">
+      <c r="A80" s="213" t="s">
+        <v>5224</v>
+      </c>
+      <c r="B80" s="213" t="s">
+        <v>5225</v>
+      </c>
+      <c r="C80" s="214" t="s">
+        <v>5226</v>
+      </c>
+      <c r="D80" s="562" t="s">
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" s="205" customFormat="1">
+      <c r="A81" s="205" t="s">
+        <v>5228</v>
+      </c>
+      <c r="B81" s="205" t="s">
+        <v>5229</v>
+      </c>
+      <c r="C81" s="206" t="s">
+        <v>5230</v>
+      </c>
+      <c r="D81" s="563" t="s">
+        <v>5231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" s="205" customFormat="1">
+      <c r="A82" s="205" t="s">
+        <v>5232</v>
+      </c>
+      <c r="B82" s="205" t="s">
+        <v>5233</v>
+      </c>
+      <c r="C82" s="206" t="s">
+        <v>5234</v>
+      </c>
+      <c r="D82" s="563" t="s">
+        <v>5235</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" s="77" customFormat="1"/>
+    <row r="84" spans="1:4" s="77" customFormat="1">
+      <c r="A84" s="68" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B84" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" s="228" customFormat="1">
+      <c r="A85" s="227" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B85" s="227" t="s">
+        <v>5236</v>
+      </c>
+      <c r="C85" s="227" t="s">
+        <v>5237</v>
+      </c>
+      <c r="D85" s="528" t="s">
+        <v>5238</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" s="222" customFormat="1">
+      <c r="A86" s="221" t="s">
+        <v>5239</v>
+      </c>
+      <c r="B86" s="221" t="s">
+        <v>5240</v>
+      </c>
+      <c r="C86" s="221" t="s">
+        <v>5241</v>
+      </c>
+      <c r="D86" s="564" t="s">
+        <v>5242</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" s="226" customFormat="1">
+      <c r="A87" s="225" t="s">
+        <v>5243</v>
+      </c>
+      <c r="B87" s="225" t="s">
+        <v>5244</v>
+      </c>
+      <c r="C87" s="225" t="s">
+        <v>5245</v>
+      </c>
+      <c r="D87" s="565" t="s">
+        <v>5246</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" s="228" customFormat="1">
+      <c r="A88" s="227" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B88" s="227" t="s">
+        <v>5247</v>
+      </c>
+      <c r="C88" s="227" t="s">
+        <v>5248</v>
+      </c>
+      <c r="D88" s="528" t="s">
+        <v>5249</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" s="222" customFormat="1">
+      <c r="A89" s="221" t="s">
+        <v>5250</v>
+      </c>
+      <c r="B89" s="221" t="s">
+        <v>5251</v>
+      </c>
+      <c r="C89" s="221" t="s">
+        <v>5252</v>
+      </c>
+      <c r="D89" s="564" t="s">
+        <v>5253</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" s="226" customFormat="1">
+      <c r="A90" s="225" t="s">
+        <v>5254</v>
+      </c>
+      <c r="B90" s="225" t="s">
+        <v>5255</v>
+      </c>
+      <c r="C90" s="225" t="s">
+        <v>5256</v>
+      </c>
+      <c r="D90" s="565" t="s">
+        <v>5257</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" s="228" customFormat="1">
+      <c r="A91" s="227" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B91" s="227" t="s">
+        <v>5258</v>
+      </c>
+      <c r="C91" s="227" t="s">
+        <v>5259</v>
+      </c>
+      <c r="D91" s="528" t="s">
+        <v>5260</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" s="228" customFormat="1">
+      <c r="A92" s="227" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B92" s="227" t="s">
+        <v>5261</v>
+      </c>
+      <c r="C92" s="227" t="s">
+        <v>5262</v>
+      </c>
+      <c r="D92" s="528" t="s">
+        <v>5263</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="222" customFormat="1">
+      <c r="A93" s="223" t="s">
+        <v>5264</v>
+      </c>
+      <c r="B93" s="224" t="s">
+        <v>5265</v>
+      </c>
+      <c r="C93" s="221" t="s">
+        <v>5266</v>
+      </c>
+      <c r="D93" s="221" t="s">
+        <v>5267</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" s="222" customFormat="1">
+      <c r="A94" s="221" t="s">
+        <v>5268</v>
+      </c>
+      <c r="B94" s="221" t="s">
+        <v>5269</v>
+      </c>
+      <c r="C94" s="221" t="s">
+        <v>5270</v>
+      </c>
+      <c r="D94" s="564" t="s">
+        <v>5271</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="226" customFormat="1">
+      <c r="A95" s="225" t="s">
+        <v>5272</v>
+      </c>
+      <c r="B95" s="225" t="s">
+        <v>5273</v>
+      </c>
+      <c r="C95" s="225" t="s">
+        <v>5274</v>
+      </c>
+      <c r="D95" s="565" t="s">
+        <v>5275</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" s="226" customFormat="1">
+      <c r="A96" s="225" t="s">
+        <v>5276</v>
+      </c>
+      <c r="B96" s="225" t="s">
+        <v>5277</v>
+      </c>
+      <c r="C96" s="225" t="s">
+        <v>5278</v>
+      </c>
+      <c r="D96" s="565" t="s">
+        <v>5279</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="77" customFormat="1"/>
+    <row r="98" spans="1:4" s="77" customFormat="1">
+      <c r="A98" s="68" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B98" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" s="182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" s="229" customFormat="1">
+      <c r="A99" s="229" t="s">
+        <v>5280</v>
+      </c>
+      <c r="B99" s="229" t="s">
+        <v>5281</v>
+      </c>
+      <c r="C99" s="230" t="s">
+        <v>5282</v>
+      </c>
+      <c r="D99" s="566" t="s">
+        <v>5283</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" s="229" customFormat="1">
+      <c r="A100" s="229" t="s">
+        <v>5284</v>
+      </c>
+      <c r="B100" s="229" t="s">
+        <v>5285</v>
+      </c>
+      <c r="C100" s="230" t="s">
+        <v>5286</v>
+      </c>
+      <c r="D100" s="566" t="s">
+        <v>5287</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" s="233" customFormat="1">
+      <c r="A101" s="233" t="s">
+        <v>5288</v>
+      </c>
+      <c r="B101" s="233" t="s">
+        <v>5289</v>
+      </c>
+      <c r="C101" s="234" t="s">
+        <v>5290</v>
+      </c>
+      <c r="D101" s="567" t="s">
+        <v>5291</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" s="233" customFormat="1">
+      <c r="A102" s="233" t="s">
+        <v>5292</v>
+      </c>
+      <c r="B102" s="233" t="s">
+        <v>5293</v>
+      </c>
+      <c r="C102" s="234" t="s">
+        <v>5294</v>
+      </c>
+      <c r="D102" s="567" t="s">
+        <v>5295</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" s="231" customFormat="1">
+      <c r="A103" s="231" t="s">
+        <v>5296</v>
+      </c>
+      <c r="B103" s="231" t="s">
+        <v>5297</v>
+      </c>
+      <c r="C103" s="232" t="s">
+        <v>5298</v>
+      </c>
+      <c r="D103" s="568" t="s">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" s="231" customFormat="1">
+      <c r="A104" s="231" t="s">
+        <v>5300</v>
+      </c>
+      <c r="B104" s="231" t="s">
+        <v>5301</v>
+      </c>
+      <c r="C104" s="232" t="s">
+        <v>5302</v>
+      </c>
+      <c r="D104" s="568" t="s">
+        <v>5303</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" s="229" customFormat="1">
+      <c r="A105" s="229" t="s">
+        <v>5304</v>
+      </c>
+      <c r="B105" s="229" t="s">
+        <v>5305</v>
+      </c>
+      <c r="C105" s="230" t="s">
+        <v>5306</v>
+      </c>
+      <c r="D105" s="566" t="s">
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="229" customFormat="1">
+      <c r="A106" s="229" t="s">
+        <v>5308</v>
+      </c>
+      <c r="B106" s="229" t="s">
+        <v>5309</v>
+      </c>
+      <c r="C106" s="230" t="s">
+        <v>5310</v>
+      </c>
+      <c r="D106" s="566" t="s">
+        <v>5311</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" s="233" customFormat="1">
+      <c r="A107" s="235" t="s">
+        <v>5312</v>
+      </c>
+      <c r="B107" s="236" t="s">
+        <v>5313</v>
+      </c>
+      <c r="C107" s="234" t="s">
+        <v>5314</v>
+      </c>
+      <c r="D107" s="234" t="s">
+        <v>5315</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="233" customFormat="1">
+      <c r="A108" s="233" t="s">
+        <v>5316</v>
+      </c>
+      <c r="B108" s="233" t="s">
+        <v>5317</v>
+      </c>
+      <c r="C108" s="234" t="s">
+        <v>5318</v>
+      </c>
+      <c r="D108" s="567" t="s">
+        <v>5319</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" s="231" customFormat="1">
+      <c r="A109" s="231" t="s">
+        <v>5320</v>
+      </c>
+      <c r="B109" s="231" t="s">
+        <v>5321</v>
+      </c>
+      <c r="C109" s="232" t="s">
+        <v>5322</v>
+      </c>
+      <c r="D109" s="568" t="s">
+        <v>5323</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" s="231" customFormat="1">
+      <c r="A110" s="231" t="s">
+        <v>5324</v>
+      </c>
+      <c r="B110" s="231" t="s">
+        <v>5325</v>
+      </c>
+      <c r="C110" s="232" t="s">
+        <v>5326</v>
+      </c>
+      <c r="D110" s="568" t="s">
+        <v>5327</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" s="77" customFormat="1"/>
+    <row r="112" spans="1:4" s="77" customFormat="1">
+      <c r="A112" s="68" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B112" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" s="229" customFormat="1">
+      <c r="A113" s="229" t="s">
+        <v>5328</v>
+      </c>
+      <c r="B113" s="229" t="s">
+        <v>5329</v>
+      </c>
+      <c r="C113" s="230" t="s">
+        <v>5330</v>
+      </c>
+      <c r="D113" s="566" t="s">
+        <v>5331</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" s="229" customFormat="1">
+      <c r="A114" s="229" t="s">
+        <v>5332</v>
+      </c>
+      <c r="B114" s="229" t="s">
+        <v>5333</v>
+      </c>
+      <c r="C114" s="230" t="s">
+        <v>5334</v>
+      </c>
+      <c r="D114" s="566" t="s">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="229" customFormat="1">
+      <c r="A115" s="229" t="s">
+        <v>5336</v>
+      </c>
+      <c r="B115" s="229" t="s">
+        <v>5337</v>
+      </c>
+      <c r="C115" s="230" t="s">
+        <v>5338</v>
+      </c>
+      <c r="D115" s="566" t="s">
+        <v>5339</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="233" customFormat="1">
+      <c r="A116" s="233" t="s">
+        <v>5340</v>
+      </c>
+      <c r="B116" s="233" t="s">
+        <v>5341</v>
+      </c>
+      <c r="C116" s="234" t="s">
+        <v>5342</v>
+      </c>
+      <c r="D116" s="567" t="s">
+        <v>5343</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" s="233" customFormat="1">
+      <c r="A117" s="233" t="s">
+        <v>5344</v>
+      </c>
+      <c r="B117" s="233" t="s">
+        <v>5345</v>
+      </c>
+      <c r="C117" s="234" t="s">
+        <v>5346</v>
+      </c>
+      <c r="D117" s="567" t="s">
+        <v>5347</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" s="233" customFormat="1">
+      <c r="A118" s="233" t="s">
+        <v>5348</v>
+      </c>
+      <c r="B118" s="233" t="s">
+        <v>5349</v>
+      </c>
+      <c r="C118" s="234" t="s">
+        <v>5350</v>
+      </c>
+      <c r="D118" s="567" t="s">
+        <v>5351</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" s="231" customFormat="1">
+      <c r="A119" s="231" t="s">
+        <v>5352</v>
+      </c>
+      <c r="B119" s="231" t="s">
+        <v>5353</v>
+      </c>
+      <c r="C119" s="232" t="s">
+        <v>5354</v>
+      </c>
+      <c r="D119" s="568" t="s">
+        <v>5355</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="231" customFormat="1">
+      <c r="A120" s="231" t="s">
+        <v>5356</v>
+      </c>
+      <c r="B120" s="231" t="s">
+        <v>5357</v>
+      </c>
+      <c r="C120" s="232" t="s">
+        <v>5358</v>
+      </c>
+      <c r="D120" s="568" t="s">
+        <v>5359</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" s="231" customFormat="1">
+      <c r="A121" s="231" t="s">
+        <v>5360</v>
+      </c>
+      <c r="B121" s="231" t="s">
+        <v>5361</v>
+      </c>
+      <c r="C121" s="232" t="s">
+        <v>5362</v>
+      </c>
+      <c r="D121" s="568" t="s">
+        <v>5363</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" s="77" customFormat="1"/>
+    <row r="123" spans="1:4" s="77" customFormat="1">
+      <c r="A123" s="68" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B123" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="D123" s="182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="237" customFormat="1">
+      <c r="A124" s="237" t="s">
+        <v>5364</v>
+      </c>
+      <c r="B124" s="237" t="s">
+        <v>5365</v>
+      </c>
+      <c r="C124" s="238" t="s">
+        <v>5366</v>
+      </c>
+      <c r="D124" s="569" t="s">
+        <v>5367</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" s="237" customFormat="1">
+      <c r="A125" s="237" t="s">
+        <v>5368</v>
+      </c>
+      <c r="B125" s="237" t="s">
+        <v>5369</v>
+      </c>
+      <c r="C125" s="238" t="s">
+        <v>5370</v>
+      </c>
+      <c r="D125" s="569" t="s">
+        <v>5371</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="239" customFormat="1">
+      <c r="A126" s="239" t="s">
+        <v>5372</v>
+      </c>
+      <c r="B126" s="239" t="s">
+        <v>5373</v>
+      </c>
+      <c r="C126" s="240" t="s">
+        <v>5374</v>
+      </c>
+      <c r="D126" s="570" t="s">
+        <v>5375</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="239" customFormat="1">
+      <c r="A127" s="239" t="s">
+        <v>5376</v>
+      </c>
+      <c r="B127" s="239" t="s">
+        <v>5377</v>
+      </c>
+      <c r="C127" s="240" t="s">
+        <v>5378</v>
+      </c>
+      <c r="D127" s="570" t="s">
+        <v>5379</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="241" customFormat="1">
+      <c r="A128" s="241" t="s">
+        <v>5380</v>
+      </c>
+      <c r="B128" s="241" t="s">
+        <v>5381</v>
+      </c>
+      <c r="C128" s="242" t="s">
+        <v>5382</v>
+      </c>
+      <c r="D128" s="571" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="241" customFormat="1">
+      <c r="A129" s="241" t="s">
+        <v>5384</v>
+      </c>
+      <c r="B129" s="241" t="s">
+        <v>5385</v>
+      </c>
+      <c r="C129" s="242" t="s">
+        <v>5386</v>
+      </c>
+      <c r="D129" s="571" t="s">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="247" customFormat="1">
+      <c r="A130" s="247" t="s">
+        <v>5388</v>
+      </c>
+      <c r="B130" s="247" t="s">
+        <v>5389</v>
+      </c>
+      <c r="C130" s="248" t="s">
+        <v>5390</v>
+      </c>
+      <c r="D130" s="572" t="s">
+        <v>5391</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" s="247" customFormat="1">
+      <c r="A131" s="247" t="s">
+        <v>5392</v>
+      </c>
+      <c r="B131" s="247" t="s">
+        <v>5393</v>
+      </c>
+      <c r="C131" s="248" t="s">
+        <v>5394</v>
+      </c>
+      <c r="D131" s="572" t="s">
+        <v>5395</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" s="247" customFormat="1">
+      <c r="A132" s="247" t="s">
+        <v>5396</v>
+      </c>
+      <c r="B132" s="247" t="s">
+        <v>5397</v>
+      </c>
+      <c r="C132" s="248" t="s">
+        <v>5398</v>
+      </c>
+      <c r="D132" s="572" t="s">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" s="135" customFormat="1">
+      <c r="A133" s="135" t="s">
+        <v>5400</v>
+      </c>
+      <c r="B133" s="135" t="s">
+        <v>5401</v>
+      </c>
+      <c r="C133" s="80" t="s">
+        <v>5402</v>
+      </c>
+      <c r="D133" s="495" t="s">
+        <v>5403</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" s="135" customFormat="1">
+      <c r="A134" s="135" t="s">
+        <v>5404</v>
+      </c>
+      <c r="B134" s="135" t="s">
+        <v>5405</v>
+      </c>
+      <c r="C134" s="80" t="s">
+        <v>5406</v>
+      </c>
+      <c r="D134" s="495" t="s">
+        <v>5407</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" s="135" customFormat="1">
+      <c r="A135" s="135" t="s">
+        <v>5408</v>
+      </c>
+      <c r="B135" s="135" t="s">
+        <v>5409</v>
+      </c>
+      <c r="C135" s="80" t="s">
+        <v>5410</v>
+      </c>
+      <c r="D135" s="495" t="s">
+        <v>5411</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" s="249" customFormat="1">
+      <c r="A136" s="249" t="s">
+        <v>5412</v>
+      </c>
+      <c r="B136" s="249" t="s">
+        <v>5413</v>
+      </c>
+      <c r="C136" s="250" t="s">
+        <v>5414</v>
+      </c>
+      <c r="D136" s="573" t="s">
+        <v>5415</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" s="249" customFormat="1">
+      <c r="A137" s="249" t="s">
+        <v>5416</v>
+      </c>
+      <c r="B137" s="249" t="s">
+        <v>5417</v>
+      </c>
+      <c r="C137" s="250" t="s">
+        <v>5418</v>
+      </c>
+      <c r="D137" s="573" t="s">
+        <v>5419</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" s="249" customFormat="1">
+      <c r="A138" s="249" t="s">
+        <v>5420</v>
+      </c>
+      <c r="B138" s="249" t="s">
+        <v>5421</v>
+      </c>
+      <c r="C138" s="250" t="s">
+        <v>5422</v>
+      </c>
+      <c r="D138" s="573" t="s">
+        <v>5423</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" s="247" customFormat="1">
+      <c r="A139" s="247" t="s">
+        <v>5424</v>
+      </c>
+      <c r="B139" s="247" t="s">
+        <v>5425</v>
+      </c>
+      <c r="C139" s="248" t="s">
+        <v>5426</v>
+      </c>
+      <c r="D139" s="572" t="s">
+        <v>5427</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" s="247" customFormat="1">
+      <c r="A140" s="247" t="s">
+        <v>5428</v>
+      </c>
+      <c r="B140" s="247" t="s">
+        <v>5429</v>
+      </c>
+      <c r="C140" s="248" t="s">
+        <v>5430</v>
+      </c>
+      <c r="D140" s="572" t="s">
+        <v>5431</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" s="247" customFormat="1">
+      <c r="A141" s="247" t="s">
+        <v>5432</v>
+      </c>
+      <c r="B141" s="247" t="s">
+        <v>5433</v>
+      </c>
+      <c r="C141" s="248" t="s">
+        <v>5434</v>
+      </c>
+      <c r="D141" s="572" t="s">
+        <v>5435</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" s="135" customFormat="1">
+      <c r="A142" s="135" t="s">
+        <v>5436</v>
+      </c>
+      <c r="B142" s="135" t="s">
+        <v>5437</v>
+      </c>
+      <c r="C142" s="80" t="s">
+        <v>5438</v>
+      </c>
+      <c r="D142" s="495" t="s">
+        <v>5439</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" s="135" customFormat="1">
+      <c r="A143" s="135" t="s">
+        <v>5440</v>
+      </c>
+      <c r="B143" s="135" t="s">
+        <v>5441</v>
+      </c>
+      <c r="C143" s="80" t="s">
+        <v>5442</v>
+      </c>
+      <c r="D143" s="495" t="s">
+        <v>5443</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" s="135" customFormat="1">
+      <c r="A144" s="135" t="s">
+        <v>5444</v>
+      </c>
+      <c r="B144" s="135" t="s">
+        <v>5445</v>
+      </c>
+      <c r="C144" s="80" t="s">
+        <v>5446</v>
+      </c>
+      <c r="D144" s="495" t="s">
+        <v>5447</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" s="249" customFormat="1">
+      <c r="A145" s="249" t="s">
+        <v>5448</v>
+      </c>
+      <c r="B145" s="249" t="s">
+        <v>5449</v>
+      </c>
+      <c r="C145" s="250" t="s">
+        <v>5450</v>
+      </c>
+      <c r="D145" s="573" t="s">
+        <v>5451</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" s="249" customFormat="1">
+      <c r="A146" s="249" t="s">
+        <v>5452</v>
+      </c>
+      <c r="B146" s="249" t="s">
+        <v>5453</v>
+      </c>
+      <c r="C146" s="250" t="s">
+        <v>5454</v>
+      </c>
+      <c r="D146" s="573" t="s">
+        <v>5455</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" s="249" customFormat="1">
+      <c r="A147" s="249" t="s">
+        <v>5456</v>
+      </c>
+      <c r="B147" s="249" t="s">
+        <v>5457</v>
+      </c>
+      <c r="C147" s="250" t="s">
+        <v>5458</v>
+      </c>
+      <c r="D147" s="573" t="s">
+        <v>5459</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" s="237" customFormat="1">
+      <c r="A148" s="237" t="s">
+        <v>5460</v>
+      </c>
+      <c r="B148" s="237" t="s">
+        <v>5461</v>
+      </c>
+      <c r="C148" s="238" t="s">
+        <v>5462</v>
+      </c>
+      <c r="D148" s="569" t="s">
+        <v>5463</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" s="237" customFormat="1">
+      <c r="A149" s="237" t="s">
+        <v>5464</v>
+      </c>
+      <c r="B149" s="237" t="s">
+        <v>5465</v>
+      </c>
+      <c r="C149" s="238" t="s">
+        <v>5466</v>
+      </c>
+      <c r="D149" s="569" t="s">
+        <v>5467</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" s="239" customFormat="1">
+      <c r="A150" s="239" t="s">
+        <v>5468</v>
+      </c>
+      <c r="B150" s="239" t="s">
+        <v>5469</v>
+      </c>
+      <c r="C150" s="240" t="s">
+        <v>5470</v>
+      </c>
+      <c r="D150" s="570" t="s">
+        <v>5471</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" s="239" customFormat="1">
+      <c r="A151" s="239" t="s">
+        <v>5472</v>
+      </c>
+      <c r="B151" s="239" t="s">
+        <v>5473</v>
+      </c>
+      <c r="C151" s="240" t="s">
+        <v>5474</v>
+      </c>
+      <c r="D151" s="570" t="s">
+        <v>5475</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" s="241" customFormat="1">
+      <c r="A152" s="241" t="s">
+        <v>5476</v>
+      </c>
+      <c r="B152" s="241" t="s">
+        <v>5477</v>
+      </c>
+      <c r="C152" s="242" t="s">
+        <v>5478</v>
+      </c>
+      <c r="D152" s="571" t="s">
+        <v>5479</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" s="241" customFormat="1">
+      <c r="A153" s="241" t="s">
+        <v>5480</v>
+      </c>
+      <c r="B153" s="241" t="s">
+        <v>5481</v>
+      </c>
+      <c r="C153" s="242" t="s">
+        <v>5482</v>
+      </c>
+      <c r="D153" s="571" t="s">
+        <v>5483</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" s="245" customFormat="1">
+      <c r="A154" s="245" t="s">
+        <v>5484</v>
+      </c>
+      <c r="B154" s="245" t="s">
+        <v>5485</v>
+      </c>
+      <c r="C154" s="246" t="s">
+        <v>5486</v>
+      </c>
+      <c r="D154" s="574" t="s">
+        <v>5487</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" s="245" customFormat="1">
+      <c r="A155" s="245" t="s">
+        <v>5488</v>
+      </c>
+      <c r="B155" s="245" t="s">
+        <v>5489</v>
+      </c>
+      <c r="C155" s="246" t="s">
+        <v>5490</v>
+      </c>
+      <c r="D155" s="574" t="s">
+        <v>5491</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" s="243" customFormat="1">
+      <c r="A156" s="243" t="s">
+        <v>5492</v>
+      </c>
+      <c r="B156" s="243" t="s">
+        <v>5493</v>
+      </c>
+      <c r="C156" s="244" t="s">
+        <v>5494</v>
+      </c>
+      <c r="D156" s="575" t="s">
+        <v>5495</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" s="243" customFormat="1">
+      <c r="A157" s="243" t="s">
+        <v>5496</v>
+      </c>
+      <c r="B157" s="243" t="s">
+        <v>5497</v>
+      </c>
+      <c r="C157" s="244" t="s">
+        <v>5498</v>
+      </c>
+      <c r="D157" s="575" t="s">
+        <v>5499</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" s="245" customFormat="1">
+      <c r="A158" s="245" t="s">
+        <v>5500</v>
+      </c>
+      <c r="B158" s="245" t="s">
+        <v>5501</v>
+      </c>
+      <c r="C158" s="246" t="s">
+        <v>5502</v>
+      </c>
+      <c r="D158" s="574" t="s">
+        <v>5503</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" s="245" customFormat="1">
+      <c r="A159" s="245" t="s">
+        <v>5504</v>
+      </c>
+      <c r="B159" s="245" t="s">
+        <v>5505</v>
+      </c>
+      <c r="C159" s="246" t="s">
+        <v>5506</v>
+      </c>
+      <c r="D159" s="574" t="s">
+        <v>5507</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" s="243" customFormat="1">
+      <c r="A160" s="243" t="s">
+        <v>5508</v>
+      </c>
+      <c r="B160" s="243" t="s">
+        <v>5509</v>
+      </c>
+      <c r="C160" s="244" t="s">
+        <v>5510</v>
+      </c>
+      <c r="D160" s="575" t="s">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" s="243" customFormat="1">
+      <c r="A161" s="243" t="s">
+        <v>5512</v>
+      </c>
+      <c r="B161" s="243" t="s">
+        <v>5513</v>
+      </c>
+      <c r="C161" s="244" t="s">
+        <v>5514</v>
+      </c>
+      <c r="D161" s="575" t="s">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" s="252" customFormat="1">
+      <c r="A162" s="251" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B162" s="251" t="s">
+        <v>5516</v>
+      </c>
+      <c r="C162" s="251" t="s">
+        <v>5517</v>
+      </c>
+      <c r="D162" s="576" t="s">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" s="252" customFormat="1">
+      <c r="A163" s="251" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B163" s="251" t="s">
+        <v>5519</v>
+      </c>
+      <c r="C163" s="251" t="s">
+        <v>5520</v>
+      </c>
+      <c r="D163" s="576" t="s">
+        <v>5521</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" s="252" customFormat="1">
+      <c r="A164" s="251" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B164" s="251" t="s">
+        <v>5522</v>
+      </c>
+      <c r="C164" s="251" t="s">
+        <v>5523</v>
+      </c>
+      <c r="D164" s="576" t="s">
+        <v>5524</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" s="254" customFormat="1">
+      <c r="A165" s="253" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B165" s="253" t="s">
+        <v>5525</v>
+      </c>
+      <c r="C165" s="253" t="s">
+        <v>5526</v>
+      </c>
+      <c r="D165" s="577" t="s">
+        <v>5527</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" s="254" customFormat="1">
+      <c r="A166" s="253" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B166" s="253" t="s">
+        <v>5528</v>
+      </c>
+      <c r="C166" s="253" t="s">
+        <v>5529</v>
+      </c>
+      <c r="D166" s="577" t="s">
+        <v>5530</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" s="254" customFormat="1">
+      <c r="A167" s="254" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B167" s="254" t="s">
+        <v>5531</v>
+      </c>
+      <c r="C167" s="253" t="s">
+        <v>5532</v>
+      </c>
+      <c r="D167" s="577" t="s">
+        <v>5533</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" s="77" customFormat="1"/>
+    <row r="169" spans="1:4" s="77" customFormat="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -62179,7 +62779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79153F45-F302-4C4D-B6DB-B7D860C69033}">
   <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
@@ -63204,6 +63804,549 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F2AEAB-CC28-B34C-BE37-0FB1E798C0E6}">
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A1" s="76" t="s">
+        <v>5754</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="612" t="s">
+        <v>5796</v>
+      </c>
+      <c r="B2" s="612" t="s">
+        <v>5756</v>
+      </c>
+      <c r="C2" s="612" t="s">
+        <v>5757</v>
+      </c>
+      <c r="D2" s="613" t="s">
+        <v>5803</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5759</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5758</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>5804</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="612" t="s">
+        <v>5797</v>
+      </c>
+      <c r="B4" s="613" t="s">
+        <v>5763</v>
+      </c>
+      <c r="C4" s="613" t="s">
+        <v>5762</v>
+      </c>
+      <c r="D4" s="613" t="s">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5760</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5761</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>5819</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="612" t="s">
+        <v>5798</v>
+      </c>
+      <c r="B6" s="612" t="s">
+        <v>5767</v>
+      </c>
+      <c r="C6" s="612" t="s">
+        <v>5766</v>
+      </c>
+      <c r="D6" s="613" t="s">
+        <v>5809</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5764</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5765</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>5806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="612" t="s">
+        <v>5799</v>
+      </c>
+      <c r="B8" s="613" t="s">
+        <v>5771</v>
+      </c>
+      <c r="C8" s="613" t="s">
+        <v>5770</v>
+      </c>
+      <c r="D8" s="613" t="s">
+        <v>5811</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>5800</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5768</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5769</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>5821</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="612" t="s">
+        <v>5801</v>
+      </c>
+      <c r="B10" s="612" t="s">
+        <v>5772</v>
+      </c>
+      <c r="C10" s="612" t="s">
+        <v>5773</v>
+      </c>
+      <c r="D10" s="613" t="s">
+        <v>5818</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>5802</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5775</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5774</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>5815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+    </row>
+    <row r="13" spans="1:4" s="580" customFormat="1" ht="17" customHeight="1">
+      <c r="A13" s="578" t="s">
+        <v>5633</v>
+      </c>
+      <c r="B13" s="579" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="579" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="579" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A14" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="D14" s="481" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="D15" s="481" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>547</v>
+      </c>
+      <c r="D16" s="481" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>5614</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="481" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="581" customFormat="1" ht="15" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>5604</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D18" s="481" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="30" customFormat="1"/>
+    <row r="20" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="76" t="s">
+        <v>5755</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A21" s="612" t="s">
+        <v>5796</v>
+      </c>
+      <c r="B21" s="612" t="s">
+        <v>5778</v>
+      </c>
+      <c r="C21" s="613" t="s">
+        <v>5779</v>
+      </c>
+      <c r="D21" s="613" t="s">
+        <v>5813</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>5776</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>5777</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>5814</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="612" t="s">
+        <v>5797</v>
+      </c>
+      <c r="B23" s="613" t="s">
+        <v>5782</v>
+      </c>
+      <c r="C23" s="612" t="s">
+        <v>5783</v>
+      </c>
+      <c r="D23" s="613" t="s">
+        <v>5807</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>5781</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>5808</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="612" t="s">
+        <v>5798</v>
+      </c>
+      <c r="B25" s="612" t="s">
+        <v>5787</v>
+      </c>
+      <c r="C25" s="612" t="s">
+        <v>5786</v>
+      </c>
+      <c r="D25" s="613" t="s">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>5784</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5785</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>5810</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="612" t="s">
+        <v>5799</v>
+      </c>
+      <c r="B27" s="613" t="s">
+        <v>5791</v>
+      </c>
+      <c r="C27" s="613" t="s">
+        <v>5790</v>
+      </c>
+      <c r="D27" s="613" t="s">
+        <v>5805</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>5800</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>5788</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5789</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>5822</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="613" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="612" t="s">
+        <v>5801</v>
+      </c>
+      <c r="B29" s="612" t="s">
+        <v>5795</v>
+      </c>
+      <c r="C29" s="612" t="s">
+        <v>5794</v>
+      </c>
+      <c r="D29" s="613" t="s">
+        <v>5816</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>5802</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>5792</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5793</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>5820</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" s="113"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="113"/>
+    </row>
+    <row r="32" spans="1:4" s="580" customFormat="1" ht="17" customHeight="1">
+      <c r="A32" s="578" t="s">
+        <v>5633</v>
+      </c>
+      <c r="B32" s="579" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="579" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="579" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="D33" s="481" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="D34" s="481" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>547</v>
+      </c>
+      <c r="D35" s="481" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A36" s="13" t="s">
+        <v>5614</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="481" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="581" customFormat="1" ht="15" customHeight="1">
+      <c r="A37" s="13" t="s">
+        <v>5604</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D37" s="481" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="30" customFormat="1"/>
+    <row r="39" spans="1:4" s="30" customFormat="1"/>
+    <row r="40" spans="1:4" s="30" customFormat="1"/>
+    <row r="41" spans="1:4" s="30" customFormat="1"/>
+    <row r="42" spans="1:4" s="30" customFormat="1"/>
+    <row r="43" spans="1:4" s="30" customFormat="1"/>
+    <row r="44" spans="1:4" s="30" customFormat="1"/>
+    <row r="45" spans="1:4" s="30" customFormat="1"/>
+    <row r="46" spans="1:4" s="30" customFormat="1"/>
+    <row r="47" spans="1:4" s="30" customFormat="1"/>
+    <row r="48" spans="1:4" s="30" customFormat="1"/>
+    <row r="49" s="30" customFormat="1"/>
+    <row r="50" s="30" customFormat="1"/>
+    <row r="51" s="30" customFormat="1"/>
+    <row r="52" s="30" customFormat="1"/>
+    <row r="53" s="30" customFormat="1"/>
+    <row r="54" s="30" customFormat="1"/>
+    <row r="55" s="30" customFormat="1"/>
+    <row r="56" s="30" customFormat="1"/>
+    <row r="57" s="30" customFormat="1"/>
+    <row r="58" s="30" customFormat="1"/>
+    <row r="59" s="30" customFormat="1"/>
+    <row r="60" s="30" customFormat="1"/>
+    <row r="61" s="30" customFormat="1"/>
+    <row r="62" s="30" customFormat="1"/>
+    <row r="63" s="30" customFormat="1"/>
+    <row r="64" s="30" customFormat="1"/>
+    <row r="65" s="30" customFormat="1"/>
+    <row r="66" s="30" customFormat="1"/>
+    <row r="67" s="30" customFormat="1"/>
+    <row r="68" s="30" customFormat="1"/>
+    <row r="69" s="30" customFormat="1"/>
+    <row r="70" s="30" customFormat="1"/>
+    <row r="71" s="30" customFormat="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -63802,7 +64945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -65268,7 +66411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -66582,7 +67725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -66956,373 +68099,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="76" t="s">
-        <v>5753</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="68" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="316" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="315" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B3" s="315" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C3" s="316" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D3" s="316" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="316" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="315" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B5" s="315" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C5" s="316" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D5" s="316" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="317" customFormat="1" ht="17" customHeight="1">
-      <c r="A7" s="315" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B7" s="315" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C7" s="316" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D7" s="316" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="44" customFormat="1" ht="17" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="317" customFormat="1" ht="17" customHeight="1">
-      <c r="A9" s="315" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B9" s="316" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C9" s="316" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D9" s="316" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B10" s="113"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-    </row>
-    <row r="11" spans="1:4" s="580" customFormat="1" ht="17" customHeight="1">
-      <c r="A11" s="578" t="s">
-        <v>5633</v>
-      </c>
-      <c r="B11" s="579" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="579" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="579" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>5614</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="481" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="273" customFormat="1" ht="17" customHeight="1">
-      <c r="A13" s="272" t="s">
-        <v>5722</v>
-      </c>
-      <c r="B13" s="272" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="272" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="482" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>5717</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="481" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>5612</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C15" s="53" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D15" s="279" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>5613</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C16" s="53" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D16" s="279" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="581" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>5604</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>549</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="D17" s="481" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>542</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="D18" s="481" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="336" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="335" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B19" s="335" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C19" s="335" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D19" s="335" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="338" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="337" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B20" s="337" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C20" s="337" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D20" s="337" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="340" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="339" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B21" s="339" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C21" s="339" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D21" s="339" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="342" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="341" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B22" s="341" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C22" s="341" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D22" s="341" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="30" customFormat="1"/>
-    <row r="24" spans="1:4" s="30" customFormat="1"/>
-    <row r="25" spans="1:4" s="30" customFormat="1"/>
-    <row r="26" spans="1:4" s="30" customFormat="1"/>
-    <row r="27" spans="1:4" s="30" customFormat="1"/>
-    <row r="28" spans="1:4" s="30" customFormat="1"/>
-    <row r="29" spans="1:4" s="30" customFormat="1"/>
-    <row r="30" spans="1:4" s="30" customFormat="1"/>
-    <row r="31" spans="1:4" s="30" customFormat="1"/>
-    <row r="32" spans="1:4" s="30" customFormat="1"/>
-    <row r="33" s="30" customFormat="1"/>
-    <row r="34" s="30" customFormat="1"/>
-    <row r="35" s="30" customFormat="1"/>
-    <row r="36" s="30" customFormat="1"/>
-    <row r="37" s="30" customFormat="1"/>
-    <row r="38" s="30" customFormat="1"/>
-    <row r="39" s="30" customFormat="1"/>
-    <row r="40" s="30" customFormat="1"/>
-    <row r="41" s="30" customFormat="1"/>
-    <row r="42" s="30" customFormat="1"/>
-    <row r="43" s="30" customFormat="1"/>
-    <row r="44" s="30" customFormat="1"/>
-    <row r="45" s="30" customFormat="1"/>
-    <row r="46" s="30" customFormat="1"/>
-    <row r="47" s="30" customFormat="1"/>
-    <row r="48" s="30" customFormat="1"/>
-    <row r="49" s="30" customFormat="1"/>
-    <row r="50" s="30" customFormat="1"/>
-    <row r="51" s="30" customFormat="1"/>
-    <row r="52" s="30" customFormat="1"/>
-    <row r="53" s="30" customFormat="1"/>
-    <row r="54" s="30" customFormat="1"/>
-    <row r="55" s="30" customFormat="1"/>
-    <row r="56" s="30" customFormat="1"/>
-    <row r="57" s="30" customFormat="1"/>
-    <row r="58" s="30" customFormat="1"/>
-    <row r="59" s="30" customFormat="1"/>
-    <row r="60" s="30" customFormat="1"/>
-    <row r="61" s="30" customFormat="1"/>
-    <row r="62" s="30" customFormat="1"/>
-    <row r="63" s="30" customFormat="1"/>
-    <row r="64" s="30" customFormat="1"/>
-    <row r="65" s="30" customFormat="1"/>
-    <row r="66" s="30" customFormat="1"/>
-    <row r="67" s="30" customFormat="1"/>
-    <row r="68" s="30" customFormat="1"/>
-    <row r="69" s="30" customFormat="1"/>
-    <row r="70" s="30" customFormat="1"/>
-    <row r="71" s="30" customFormat="1"/>
-    <row r="72" s="30" customFormat="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>
--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/EnterpriseAssistant/WebReferencias 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DA029B-C0E1-0B45-B142-37D6944B398B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF51001B-8AF7-2745-A8CD-E7B12698CAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17220" yWindow="760" windowWidth="16980" windowHeight="21480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13020" yWindow="760" windowWidth="27940" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8067" uniqueCount="5880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8191" uniqueCount="5929">
   <si>
     <t>40mm Aluminium GPS</t>
   </si>
@@ -17703,6 +17703,153 @@
   </si>
   <si>
     <t>152.151.29253</t>
+  </si>
+  <si>
+    <t>Pro 14” M5 Pro PROLED XDR</t>
+  </si>
+  <si>
+    <t>Pro 14” M5 Max PROLED XDR</t>
+  </si>
+  <si>
+    <t>Pro 16,2” M5 Pro</t>
+  </si>
+  <si>
+    <t>Pro 16,3” M5 Pro PROLED XDR</t>
+  </si>
+  <si>
+    <t>Pro 16,2” M5 Max</t>
+  </si>
+  <si>
+    <t>Pro 16,3” M5 Max PROLED XDR</t>
+  </si>
+  <si>
+    <t>0195951195513</t>
+  </si>
+  <si>
+    <t>MJ2G4Y/A</t>
+  </si>
+  <si>
+    <t>MJ2K4Y/A</t>
+  </si>
+  <si>
+    <t>0195951196923</t>
+  </si>
+  <si>
+    <t>0195951644578</t>
+  </si>
+  <si>
+    <t>MMF54Y/A</t>
+  </si>
+  <si>
+    <t>MMF64Y/A</t>
+  </si>
+  <si>
+    <t>0195951645049</t>
+  </si>
+  <si>
+    <t>0195951197869</t>
+  </si>
+  <si>
+    <t>MJ2M4Y/A</t>
+  </si>
+  <si>
+    <t>MJ2J4Y/A</t>
+  </si>
+  <si>
+    <t>0195951196459</t>
+  </si>
+  <si>
+    <t>0195951198392</t>
+  </si>
+  <si>
+    <t>MJ2W4Y/A</t>
+  </si>
+  <si>
+    <t>0195951199801</t>
+  </si>
+  <si>
+    <t>MJ304Y/A</t>
+  </si>
+  <si>
+    <t>48GB/18CPU/20GPU/Silver</t>
+  </si>
+  <si>
+    <t>0195951645537</t>
+  </si>
+  <si>
+    <t>MMF94Y/A</t>
+  </si>
+  <si>
+    <t>MMFA4Y/A</t>
+  </si>
+  <si>
+    <t>0195951646008</t>
+  </si>
+  <si>
+    <t>0195951198866</t>
+  </si>
+  <si>
+    <t>MJ2X4Y/A</t>
+  </si>
+  <si>
+    <t>0195951200279</t>
+  </si>
+  <si>
+    <t>MJ314Y/A</t>
+  </si>
+  <si>
+    <t>0195951199337</t>
+  </si>
+  <si>
+    <t>MJ2Y4Y/A</t>
+  </si>
+  <si>
+    <t>MJ334Y/A</t>
+  </si>
+  <si>
+    <t>0195951200743</t>
+  </si>
+  <si>
+    <t>152.154.28382</t>
+  </si>
+  <si>
+    <t>152.154.28390</t>
+  </si>
+  <si>
+    <t>152.154.28408</t>
+  </si>
+  <si>
+    <t>152.154.28416</t>
+  </si>
+  <si>
+    <t>152.154.28432</t>
+  </si>
+  <si>
+    <t>152.154.28424</t>
+  </si>
+  <si>
+    <t>152.154.28457</t>
+  </si>
+  <si>
+    <t>152.154.28440</t>
+  </si>
+  <si>
+    <t>152.154.28465</t>
+  </si>
+  <si>
+    <t>152.154.28473</t>
+  </si>
+  <si>
+    <t>152.154.28499</t>
+  </si>
+  <si>
+    <t>152.154.28481</t>
+  </si>
+  <si>
+    <t>152.154.28507</t>
+  </si>
+  <si>
+    <t>152.154.28515</t>
   </si>
 </sst>
 </file>
@@ -20895,7 +21042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="60.1640625" style="15" customWidth="1"/>
@@ -21982,7 +22129,7 @@
     </row>
     <row r="85" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="76" t="s">
-        <v>261</v>
+        <v>5880</v>
       </c>
       <c r="B85" s="70" t="s">
         <v>1</v>
@@ -21996,30 +22143,30 @@
     </row>
     <row r="86" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>263</v>
+        <v>5888</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D86" s="17" t="s">
-        <v>265</v>
+        <v>5916</v>
+      </c>
+      <c r="D86" s="486" t="s">
+        <v>5889</v>
       </c>
     </row>
     <row r="87" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>267</v>
+        <v>5887</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>269</v>
+        <v>5915</v>
+      </c>
+      <c r="D87" s="484" t="s">
+        <v>5886</v>
       </c>
     </row>
     <row r="88" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
@@ -22027,13 +22174,13 @@
         <v>270</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>271</v>
+        <v>5892</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>273</v>
+        <v>5918</v>
+      </c>
+      <c r="D88" s="486" t="s">
+        <v>5893</v>
       </c>
     </row>
     <row r="89" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22041,13 +22188,13 @@
         <v>274</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>275</v>
+        <v>5891</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>277</v>
+        <v>5917</v>
+      </c>
+      <c r="D89" s="484" t="s">
+        <v>5890</v>
       </c>
     </row>
     <row r="90" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
@@ -22060,125 +22207,125 @@
     </row>
     <row r="91" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>5679</v>
+        <v>5580</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>279</v>
+        <v>162</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>280</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="5" t="s">
+        <v>5678</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A93" s="5" t="s">
         <v>5597</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B93" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C93" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="D93" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="93" spans="1:4" s="29" customFormat="1">
-      <c r="C93" s="78"/>
-    </row>
-    <row r="94" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
-      <c r="A94" s="76" t="s">
-        <v>281</v>
-      </c>
-      <c r="B94" s="70" t="s">
+    <row r="94" spans="1:4" s="29" customFormat="1">
+      <c r="C94" s="78"/>
+    </row>
+    <row r="95" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A95" s="76" t="s">
+        <v>5881</v>
+      </c>
+      <c r="B95" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C94" s="70" t="s">
+      <c r="C95" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D94" s="70" t="s">
+      <c r="D95" s="70" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
-      <c r="A95" s="1" t="s">
+    <row r="96" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A96" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D95" s="17" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A96" s="2" t="s">
+      <c r="B96" s="1" t="s">
+        <v>5895</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>5919</v>
+      </c>
+      <c r="D96" s="486" t="s">
+        <v>5894</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A97" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D96" s="18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
-      <c r="A97" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D97" s="17" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A98" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D98" s="484" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A99" s="4" t="s">
+      <c r="B97" s="2" t="s">
+        <v>5896</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>5920</v>
+      </c>
+      <c r="D97" s="484" t="s">
+        <v>5897</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A98" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B99" s="113"/>
-      <c r="C99" s="113"/>
-      <c r="D99" s="113"/>
+      <c r="B98" s="113"/>
+      <c r="C98" s="113"/>
+      <c r="D98" s="113"/>
+    </row>
+    <row r="99" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A99" s="5" t="s">
+        <v>5580</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="100" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
       <c r="A100" s="5" t="s">
-        <v>5679</v>
+        <v>5678</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="101" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
@@ -22198,62 +22345,427 @@
     <row r="102" spans="1:4" s="29" customFormat="1">
       <c r="C102" s="78"/>
     </row>
-    <row r="103" spans="1:4" s="29" customFormat="1">
-      <c r="C103" s="78"/>
-    </row>
-    <row r="104" spans="1:4" s="29" customFormat="1">
-      <c r="C104" s="78"/>
-    </row>
-    <row r="105" spans="1:4" s="29" customFormat="1">
-      <c r="C105" s="78"/>
-    </row>
-    <row r="106" spans="1:4" s="29" customFormat="1">
-      <c r="C106" s="78"/>
-    </row>
-    <row r="107" spans="1:4" s="29" customFormat="1">
-      <c r="C107" s="78"/>
-    </row>
-    <row r="108" spans="1:4" s="29" customFormat="1">
-      <c r="C108" s="78"/>
+    <row r="103" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A103" s="76" t="s">
+        <v>5882</v>
+      </c>
+      <c r="B103" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A105" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A106" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B106" s="113"/>
+      <c r="C106" s="113"/>
+      <c r="D106" s="113"/>
+    </row>
+    <row r="107" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A107" s="5" t="s">
+        <v>5679</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A108" s="5" t="s">
+        <v>5597</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="109" spans="1:4" s="29" customFormat="1">
       <c r="C109" s="78"/>
     </row>
-    <row r="110" spans="1:4" s="29" customFormat="1">
-      <c r="C110" s="78"/>
-    </row>
-    <row r="111" spans="1:4" s="29" customFormat="1">
-      <c r="C111" s="78"/>
-    </row>
-    <row r="112" spans="1:4" s="29" customFormat="1">
-      <c r="C112" s="78"/>
-    </row>
-    <row r="113" spans="3:3" s="29" customFormat="1">
-      <c r="C113" s="78"/>
-    </row>
-    <row r="114" spans="3:3" s="29" customFormat="1">
-      <c r="C114" s="78"/>
-    </row>
-    <row r="115" spans="3:3" s="29" customFormat="1">
-      <c r="C115" s="78"/>
-    </row>
-    <row r="116" spans="3:3" s="29" customFormat="1">
+    <row r="110" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A110" s="76" t="s">
+        <v>5884</v>
+      </c>
+      <c r="B110" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A112" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A113" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B113" s="113"/>
+      <c r="C113" s="113"/>
+      <c r="D113" s="113"/>
+    </row>
+    <row r="114" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A114" s="5" t="s">
+        <v>5679</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A115" s="5" t="s">
+        <v>5597</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="29" customFormat="1">
       <c r="C116" s="78"/>
     </row>
-    <row r="117" spans="3:3" s="29" customFormat="1">
-      <c r="C117" s="78"/>
-    </row>
-    <row r="118" spans="3:3" s="29" customFormat="1">
-      <c r="C118" s="78"/>
-    </row>
-    <row r="119" spans="3:3" s="29" customFormat="1">
-      <c r="C119" s="78"/>
-    </row>
-    <row r="120" spans="3:3" s="29" customFormat="1">
-      <c r="C120" s="78"/>
-    </row>
-    <row r="121" spans="3:3" s="29" customFormat="1">
-      <c r="C121" s="78"/>
+    <row r="117" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A117" s="76" t="s">
+        <v>5883</v>
+      </c>
+      <c r="B117" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>5901</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>5921</v>
+      </c>
+      <c r="D118" s="17" t="s">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A119" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>5899</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>5922</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>5898</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A120" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>5905</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>5924</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>5906</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A121" s="2" t="s">
+        <v>5902</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>5904</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>5923</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>5903</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A122" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B122" s="113"/>
+      <c r="C122" s="113"/>
+      <c r="D122" s="113"/>
+    </row>
+    <row r="123" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A123" s="5" t="s">
+        <v>5679</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A124" s="5" t="s">
+        <v>5597</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" s="29" customFormat="1">
+      <c r="C125" s="78"/>
+    </row>
+    <row r="126" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A126" s="76" t="s">
+        <v>5885</v>
+      </c>
+      <c r="B126" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A127" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>5910</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>5925</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>5909</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A128" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>5908</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>5926</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>5907</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A129" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>5913</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>5928</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>5914</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A130" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>5912</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>5927</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>5911</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
+      <c r="A131" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B131" s="113"/>
+      <c r="C131" s="113"/>
+      <c r="D131" s="113"/>
+    </row>
+    <row r="132" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A132" s="5" t="s">
+        <v>5679</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" s="14" customFormat="1" ht="15" customHeight="1">
+      <c r="A133" s="5" t="s">
+        <v>5597</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" s="29" customFormat="1">
+      <c r="C134" s="78"/>
+    </row>
+    <row r="135" spans="1:4" s="29" customFormat="1">
+      <c r="C135" s="78"/>
+    </row>
+    <row r="136" spans="1:4" s="29" customFormat="1">
+      <c r="C136" s="78"/>
+    </row>
+    <row r="137" spans="1:4" s="29" customFormat="1">
+      <c r="C137" s="78"/>
+    </row>
+    <row r="138" spans="1:4" s="29" customFormat="1">
+      <c r="C138" s="78"/>
+    </row>
+    <row r="139" spans="1:4" s="29" customFormat="1">
+      <c r="C139" s="78"/>
+    </row>
+    <row r="140" spans="1:4" s="29" customFormat="1">
+      <c r="C140" s="78"/>
+    </row>
+    <row r="141" spans="1:4" s="29" customFormat="1">
+      <c r="C141" s="78"/>
+    </row>
+    <row r="142" spans="1:4" s="29" customFormat="1">
+      <c r="C142" s="78"/>
+    </row>
+    <row r="143" spans="1:4" s="29" customFormat="1">
+      <c r="C143" s="78"/>
+    </row>
+    <row r="144" spans="1:4" s="29" customFormat="1">
+      <c r="C144" s="78"/>
+    </row>
+    <row r="145" spans="3:3" s="29" customFormat="1">
+      <c r="C145" s="78"/>
+    </row>
+    <row r="146" spans="3:3" s="29" customFormat="1">
+      <c r="C146" s="78"/>
+    </row>
+    <row r="147" spans="3:3" s="29" customFormat="1">
+      <c r="C147" s="78"/>
+    </row>
+    <row r="148" spans="3:3" s="29" customFormat="1">
+      <c r="C148" s="78"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34128,7 +34640,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:XFD125"/>
+  <dimension ref="A1:XFD140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="42.6640625" style="15" bestFit="1" customWidth="1"/>
@@ -51810,14 +52322,125 @@
     <row r="122" spans="1:4" s="29" customFormat="1">
       <c r="C122" s="78"/>
     </row>
-    <row r="123" spans="1:4" s="29" customFormat="1">
-      <c r="C123" s="78"/>
-    </row>
-    <row r="124" spans="1:4" s="29" customFormat="1">
-      <c r="C124" s="78"/>
-    </row>
-    <row r="125" spans="1:4" s="29" customFormat="1">
-      <c r="C125" s="78"/>
+    <row r="123" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A123" s="76" t="s">
+        <v>261</v>
+      </c>
+      <c r="B123" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D123" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D124" s="17" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A125" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="29" customFormat="1">
+      <c r="C126" s="78"/>
+    </row>
+    <row r="127" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
+      <c r="A127" s="76" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D127" s="70" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
+      <c r="A128" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="A129" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D129" s="484" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="29" customFormat="1">
+      <c r="C130" s="78"/>
+    </row>
+    <row r="131" spans="1:4" s="29" customFormat="1">
+      <c r="C131" s="78"/>
+    </row>
+    <row r="132" spans="1:4" s="29" customFormat="1">
+      <c r="C132" s="78"/>
+    </row>
+    <row r="133" spans="1:4" s="29" customFormat="1">
+      <c r="C133" s="78"/>
+    </row>
+    <row r="134" spans="1:4" s="29" customFormat="1">
+      <c r="C134" s="78"/>
+    </row>
+    <row r="135" spans="1:4" s="29" customFormat="1">
+      <c r="C135" s="78"/>
+    </row>
+    <row r="136" spans="1:4" s="29" customFormat="1">
+      <c r="C136" s="78"/>
+    </row>
+    <row r="137" spans="1:4" s="29" customFormat="1">
+      <c r="C137" s="78"/>
+    </row>
+    <row r="138" spans="1:4" s="29" customFormat="1">
+      <c r="C138" s="78"/>
+    </row>
+    <row r="139" spans="1:4" s="29" customFormat="1">
+      <c r="C139" s="78"/>
+    </row>
+    <row r="140" spans="1:4" s="29" customFormat="1">
+      <c r="C140" s="78"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvm/EnterpriseAssistant/WebReferencias 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF51001B-8AF7-2745-A8CD-E7B12698CAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D5B564-DCEC-B44C-A125-B72FE49482AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13020" yWindow="760" windowWidth="27940" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6260" yWindow="760" windowWidth="27940" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mac - MacBook" sheetId="1" r:id="rId1"/>
@@ -17705,24 +17705,12 @@
     <t>152.151.29253</t>
   </si>
   <si>
-    <t>Pro 14” M5 Pro PROLED XDR</t>
-  </si>
-  <si>
-    <t>Pro 14” M5 Max PROLED XDR</t>
-  </si>
-  <si>
     <t>Pro 16,2” M5 Pro</t>
   </si>
   <si>
-    <t>Pro 16,3” M5 Pro PROLED XDR</t>
-  </si>
-  <si>
     <t>Pro 16,2” M5 Max</t>
   </si>
   <si>
-    <t>Pro 16,3” M5 Max PROLED XDR</t>
-  </si>
-  <si>
     <t>0195951195513</t>
   </si>
   <si>
@@ -17850,6 +17838,18 @@
   </si>
   <si>
     <t>152.154.28515</t>
+  </si>
+  <si>
+    <t>Pro 14” M5 Pro PROLED</t>
+  </si>
+  <si>
+    <t>Pro 14” M5 Max PROLED</t>
+  </si>
+  <si>
+    <t>Pro 16,3” M5 Pro PROLED</t>
+  </si>
+  <si>
+    <t>Pro 16,3” M5 Max PROLED</t>
   </si>
 </sst>
 </file>
@@ -22129,7 +22129,7 @@
     </row>
     <row r="85" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="76" t="s">
-        <v>5880</v>
+        <v>5925</v>
       </c>
       <c r="B85" s="70" t="s">
         <v>1</v>
@@ -22146,13 +22146,13 @@
         <v>233</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>5888</v>
+        <v>5884</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>5916</v>
+        <v>5912</v>
       </c>
       <c r="D86" s="486" t="s">
-        <v>5889</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="87" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22160,13 +22160,13 @@
         <v>237</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>5887</v>
+        <v>5883</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>5915</v>
+        <v>5911</v>
       </c>
       <c r="D87" s="484" t="s">
-        <v>5886</v>
+        <v>5882</v>
       </c>
     </row>
     <row r="88" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
@@ -22174,13 +22174,13 @@
         <v>270</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>5892</v>
+        <v>5888</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>5918</v>
+        <v>5914</v>
       </c>
       <c r="D88" s="486" t="s">
-        <v>5893</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="89" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22188,13 +22188,13 @@
         <v>274</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>5891</v>
+        <v>5887</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>5917</v>
+        <v>5913</v>
       </c>
       <c r="D89" s="484" t="s">
-        <v>5890</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="90" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
@@ -22252,7 +22252,7 @@
     </row>
     <row r="95" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="76" t="s">
-        <v>5881</v>
+        <v>5926</v>
       </c>
       <c r="B95" s="70" t="s">
         <v>1</v>
@@ -22269,13 +22269,13 @@
         <v>253</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>5895</v>
+        <v>5891</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>5919</v>
+        <v>5915</v>
       </c>
       <c r="D96" s="486" t="s">
-        <v>5894</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="97" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22283,13 +22283,13 @@
         <v>257</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5896</v>
+        <v>5892</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>5920</v>
+        <v>5916</v>
       </c>
       <c r="D97" s="484" t="s">
-        <v>5897</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="98" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
@@ -22347,7 +22347,7 @@
     </row>
     <row r="103" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="76" t="s">
-        <v>5882</v>
+        <v>5880</v>
       </c>
       <c r="B103" s="70" t="s">
         <v>1</v>
@@ -22428,7 +22428,7 @@
     </row>
     <row r="110" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="76" t="s">
-        <v>5884</v>
+        <v>5881</v>
       </c>
       <c r="B110" s="70" t="s">
         <v>1</v>
@@ -22509,7 +22509,7 @@
     </row>
     <row r="117" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A117" s="76" t="s">
-        <v>5883</v>
+        <v>5927</v>
       </c>
       <c r="B117" s="70" t="s">
         <v>1</v>
@@ -22526,13 +22526,13 @@
         <v>262</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>5901</v>
+        <v>5897</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>5921</v>
+        <v>5917</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>5900</v>
+        <v>5896</v>
       </c>
     </row>
     <row r="119" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22540,13 +22540,13 @@
         <v>266</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>5899</v>
+        <v>5895</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>5922</v>
+        <v>5918</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>5898</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="120" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
@@ -22554,27 +22554,27 @@
         <v>270</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>5905</v>
+        <v>5901</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>5924</v>
+        <v>5920</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>5906</v>
+        <v>5902</v>
       </c>
     </row>
     <row r="121" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>5902</v>
+        <v>5898</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>5904</v>
+        <v>5900</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>5923</v>
+        <v>5919</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>5903</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="122" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
@@ -22618,7 +22618,7 @@
     </row>
     <row r="126" spans="1:4" s="19" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="76" t="s">
-        <v>5885</v>
+        <v>5928</v>
       </c>
       <c r="B126" s="70" t="s">
         <v>1</v>
@@ -22635,13 +22635,13 @@
         <v>253</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>5910</v>
+        <v>5906</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>5925</v>
+        <v>5921</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>5909</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="128" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22649,13 +22649,13 @@
         <v>257</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>5908</v>
+        <v>5904</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>5926</v>
+        <v>5922</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>5907</v>
+        <v>5903</v>
       </c>
     </row>
     <row r="129" spans="1:4" s="8" customFormat="1" ht="15" customHeight="1">
@@ -22663,13 +22663,13 @@
         <v>288</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>5913</v>
+        <v>5909</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>5928</v>
+        <v>5924</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>5914</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="130" spans="1:4" s="9" customFormat="1" ht="15" customHeight="1">
@@ -22677,13 +22677,13 @@
         <v>292</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>5912</v>
+        <v>5908</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>5927</v>
+        <v>5923</v>
       </c>
       <c r="D130" s="18" t="s">
-        <v>5911</v>
+        <v>5907</v>
       </c>
     </row>
     <row r="131" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1">
